--- a/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,3169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:FE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_10</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_10</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_11</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_11</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_12</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GMOMNJbs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>conde diego</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ryjofHOu</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>kiko</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>G8VcNrxU</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bailly eric</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AkMslDtA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>albiol raul</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>vVh7yy15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>cardona sergi</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>8fnHDvMe</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>santos yeremi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>z7YvfLZ8</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>parejo daniel</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>KK4TPIBj</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>comesana santi</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bmeQTB92</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>baena alex</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>UwfDD083</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>moreno gerard</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>tYV4tvqr</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>groeneveld arnaut</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>SYy8ZHN9</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>oblak jan</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>CMGUADgt</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>azpilicueta cesar</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2JsUqijl</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>witsel axel</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>8GVQFgH4</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>le normand robin</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>z3D5zvbD</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>llorente marcos</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>AaZiGJ9E</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>barrios pablo</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>v9hLv1xJ</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>koke</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>vTPgNn01</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>lino samuel</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>zekFd0M8</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>mandava reinildo</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>OxCa1jdT</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>griezmann antoine</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>QwqgNkTP</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>sorloth alexander</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>ATAVnRY7</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>akhomach ilias</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>O68UwVgl</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>alvarez iker</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>p6rsDQvN</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>gueye pape</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>S6QWzDng</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>kambwala willy</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>bwHQNPyE</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>navarro pablo</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>j3Hk0qEj</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>pepe nicolas</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>jVHfHxGn</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>perez ayoze</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Kjmmf9C3</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>sola arnau</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>rLsgetTF</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>terrats ramon</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>bBHauDIC</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>alvarez julian</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>McWkid34</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>correa angel</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>AZ6TTjDC</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>de paul rodrigo</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>t8GDN709</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>galan javier</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>IgRLzKhM</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>gimenez jose</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0rBkNdYp</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>gomis aleman antonio</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>QTc0qeb2</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>kostis ilias</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>SxjadbLU</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>moldovan horatiu</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>M3TzoLot</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>molina nahuel</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>2iQMPvBg</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>riquelme rodrigo</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>IJTJu41i</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>simeone giuliano</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>tzhSwObR</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>vermeeren arthur</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>j3Hk0qEj</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>pepe nicolas</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>j3Hk0qEj</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>pepe nicolas</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>UwfDD083</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>moreno gerard</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>p6rsDQvN</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>gueye pape</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>p6rsDQvN</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>gueye pape</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>bmeQTB92</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>baena alex</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>ATAVnRY7</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>akhomach ilias</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>ATAVnRY7</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>akhomach ilias</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>8fnHDvMe</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>santos yeremi</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>jVHfHxGn</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>perez ayoze</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>jVHfHxGn</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>perez ayoze</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>tYV4tvqr</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>groeneveld arnaut</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>rLsgetTF</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>terrats ramon</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>rLsgetTF</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>terrats ramon</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>z7YvfLZ8</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>parejo daniel</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>IgRLzKhM</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>gimenez jose</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>IgRLzKhM</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>gimenez jose</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>2JsUqijl</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>witsel axel</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>McWkid34</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>correa angel</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>McWkid34</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>correa angel</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>QwqgNkTP</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>sorloth alexander</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>M3TzoLot</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>molina nahuel</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>M3TzoLot</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>molina nahuel</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>zekFd0M8</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>mandava reinildo</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>AZ6TTjDC</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>de paul rodrigo</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>AZ6TTjDC</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>de paul rodrigo</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>v9hLv1xJ</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>koke</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>bBHauDIC</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>alvarez julian</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>bBHauDIC</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>alvarez julian</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>OxCa1jdT</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>griezmann antoine</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>KxSmFSum</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>alfonso pedraza</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>OQY4TKul</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>marcos paulo</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr"/>
+      <c r="FA2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="inlineStr"/>
+      <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>jyH8E81E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>hein karl</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4zgv0hGk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>perez luis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6NytetE5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>sanchez javier</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>G6IFcpHK</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>boyomos flavien enzo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2g3Pa3qH</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>rosa lucas</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SCxfo9Zu</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>kike</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>EZg4jPUF</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>comert eray</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>f7bNFe72</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>amallah selim</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>42y06OiE</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ndiaye amath</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>YqtgOOMN</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>sylla mamadou</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>zw8vYjwk</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>moro raul</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>vuAlEqes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>garcia joan</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>n7ISbL3j</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>tejero alvaro</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>z9FaGS78</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>el hilali omar</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>v1bRsEDN</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>gomez sergi</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>IsOwrMdM</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>cabrera leandro</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>YDxiIlER</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>romero carlos</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>EsMMVFh3</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>milla pere</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>QPoHzbRQ</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>gragera jose</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>6o8Nnmm1</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>lozano pol</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>hph7e3vc</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>veliz alejo</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Cl8Ia7Q9</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>puado javi</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>MBmNyYIa</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>biuk stipe</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>bcJKuoR6</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>chuki</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0n8qUmN8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>de la hoz cesar</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>dfLinARB</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>juric stanko</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>UHqRA6g4</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>iglesias koke</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>nBtLrBRF</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>machis darwin</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>dEgxh8oM</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>marcos andre</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>EN3EbULf</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>meseguer victor</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>d2r4nUzc</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>aulet arnau</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>fyEdYgal</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>aguado alvaro</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>jcshWJpG</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>bauza rafel</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>Sj35PsHd</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>calero fernando</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>86UW3kYK</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>cardona irvin</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>jRx96X5h</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>fortuno angel</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>KSNZwPAG</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>carreras jofe</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>UuiJcUMl</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>kral alex</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>n9R1WQ3p</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>olivan brian</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>27U3P9mT</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>pacheco fernando</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>ILCGOm9n</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>roca antoniu</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>b9FNePlR</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>sadik omar</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>x0TzcxX6</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>sanchez salvi</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>dfLinARB</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>juric stanko</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>dfLinARB</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>juric stanko</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>6NytetE5</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>sanchez javier</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>vkmiDN8F</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>sanchez ivan</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>vkmiDN8F</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>sanchez ivan</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>42y06OiE</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>ndiaye amath</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>EN3EbULf</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>meseguer victor</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>EN3EbULf</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>meseguer victor</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>f7bNFe72</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>amallah selim</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>bcJKuoR6</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>chuki</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>bcJKuoR6</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>chuki</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>SCxfo9Zu</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>kike</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>8S0B28YJ</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>torres david</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>8S0B28YJ</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>torres david</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>EZg4jPUF</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>comert eray</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>86UW3kYK</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>cardona irvin</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>86UW3kYK</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>cardona irvin</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>EsMMVFh3</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>milla pere</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>UuiJcUMl</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>kral alex</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>UuiJcUMl</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>kral alex</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>6o8Nnmm1</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>lozano pol</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>ILCGOm9n</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>roca antoniu</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>ILCGOm9n</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>roca antoniu</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>hph7e3vc</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>veliz alejo</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>KSNZwPAG</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>carreras jofe</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>KSNZwPAG</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>carreras jofe</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>n7ISbL3j</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>tejero alvaro</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>fyEdYgal</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>aguado alvaro</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>fyEdYgal</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>aguado alvaro</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>QPoHzbRQ</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>gragera jose</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t>bygTWQzR</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
+          <t>anuar</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>j5SMgGHu</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t>ferreira andre</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>Crwqppk9</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>kenedy</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr">
+        <is>
+          <t>SChm1pCo</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t>exposito edu</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t>AJg8NPiE</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
+          <t>ruiz raul chasco</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>vkmiDN8F</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>sanchez ivan</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>8S0B28YJ</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>torres david</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IZqoAH3k</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0KsY9323</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>martin dani</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SQi6oCZp</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>garcia victor</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Aa9VBz0p</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>dumic dario</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O2QaMQfb</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>sebastian inigo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>OE8ypMGf</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>mateu marc</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>WzjfmHbs</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>chapela ivan</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>nqRME05G</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ortuno diaz sergio</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>nTh80kX9</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>timor david</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>SCL2q4g1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>jorquera joel</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>dQNNg6WM</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>quintana nacho</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Agghrm2F</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ortuno juanto</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>63syan4K</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>nadal tomeu</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Of2PA2Td</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>mellot jeremy</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>AupfG8yP</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>juande</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>MHMBJsTD</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>leon jose</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>MeRdZHGT</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>guerrero adrian</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>ngNLVMtM</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>rubio waldo</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>bXfFubxl</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>bodiger yann</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>zwpagAwR</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>corredera alex</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>zXy8vKe2</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>cruz luismi</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>vmSOV0qD</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>mesa maikel</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>MZYiJsf5</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>rodriguez angel</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>6TptgFVm</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>bernal alex</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>ldjKikv4</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>camarasa victor</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>IsNRKVtG</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>poloni derick</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>fP50jBbo</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>gamez francisco</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>zaB6bU4A</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>dominguez alan godoy</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>plLDgpFg</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>grigore ricardo</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>Mg4L621f</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>mackay ian</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>fRUEYwjU</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>monsalve nacho</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>U3NEfc8n</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>montes christian</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>YDX3HtAo</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>gonzalez ruben</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>WOsowK7D</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>cantero alejandro</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>tpszulN9</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>diarra youssouf</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>zc8vwd36</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>gallego enric</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>KfbbZ1xQ</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>gaya josep</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>G87TNXSP</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>gonzalez sergio</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>4OJxMhNq</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>manjam alassan</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>MiNhvPQS</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>medrano fernando</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>zHabrrS4</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>padilla sergio</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>UqQAKe7t</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>david rodriguez ramos</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>nHp3CHac</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>senhadji yanis</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>t4ZOn0H3</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>teto</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>6TptgFVm</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>bernal alex</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>6TptgFVm</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>bernal alex</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>Agghrm2F</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>ortuno juanto</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>U3NEfc8n</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>montes christian</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>U3NEfc8n</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>montes christian</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>WzjfmHbs</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>chapela ivan</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>zaB6bU4A</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>dominguez alan godoy</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>zaB6bU4A</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>dominguez alan godoy</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>SCL2q4g1</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>jorquera joel</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>fRUEYwjU</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>monsalve nacho</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>fRUEYwjU</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>monsalve nacho</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>dQNNg6WM</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>quintana nacho</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>fP50jBbo</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>gamez francisco</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>fP50jBbo</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>gamez francisco</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>SQi6oCZp</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>garcia victor</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>MiNhvPQS</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>medrano fernando</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>MiNhvPQS</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>medrano fernando</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>MeRdZHGT</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>guerrero adrian</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>G87TNXSP</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>gonzalez sergio</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>G87TNXSP</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>gonzalez sergio</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>bXfFubxl</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>bodiger yann</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>tpszulN9</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>diarra youssouf</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>tpszulN9</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>diarra youssouf</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>zwpagAwR</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>corredera alex</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>WOsowK7D</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>cantero alejandro</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>WOsowK7D</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>cantero alejandro</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>ngNLVMtM</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>rubio waldo</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>zc8vwd36</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>gallego enric</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>zc8vwd36</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>gallego enric</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>MZYiJsf5</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>rodriguez angel</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>ph2LnYwp</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>ogbuehi sixtus</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>AD0qhhph</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>ropero unai</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr"/>
+      <c r="FE4" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ10"/>
+  <dimension ref="A1:FQ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,1111 +1001,1103 @@
       </c>
       <c r="DL1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_13</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_13</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_14</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_14</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_15</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_15</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_12</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_12</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_home_12</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_home_12</t>
-        </is>
-      </c>
       <c r="FP1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_6</t>
+          <t>id_player_miss_home_5</t>
         </is>
       </c>
       <c r="FQ1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_6</t>
+          <t>player_name_miss_home_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>byxc46yl</t>
+          <t>lMLBCMLN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ter stegen marc andre</t>
+          <t>sivera antonio</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>v36QVRPu</t>
+          <t>WAG63va3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>kounde jules</t>
+          <t>tenaglia nahuel</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UgTrNwCF</t>
+          <t>Gp35on1c</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cubarsi pau</t>
+          <t>abqar abdelkebir</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AHeWolAk</t>
+          <t>h4BWTxSF</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>martinez inigo</t>
+          <t>sedlar aleksandar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6c0CXHVM</t>
+          <t>b3mITAJa</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>balde alejandro</t>
+          <t>sanchez manuel</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>pf3IOiFD</t>
+          <t>bRBNu8DM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bernal marc</t>
+          <t>vicente carlos</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>baBG8QuI</t>
+          <t>hMjEwTOg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>pedri</t>
+          <t>guevara ander</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>lAt3vEub</t>
+          <t>MTG8l3Dq</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>yamal lamine</t>
+          <t>blanco antonio</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>xtBsDPam</t>
+          <t>zZJGkBEQ</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>raphinha</t>
+          <t>conechny tomas</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AVAVLaLt</t>
+          <t>Kneifk5H</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>torres ferran</t>
+          <t>stoichkov</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>MVC8zHZD</t>
+          <t>GfoivbEm</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>lewandowski robert</t>
+          <t>kike</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4d3bB6Wo</t>
+          <t>GErUsMSq</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>padilla alex</t>
+          <t>silva rui</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>rkIhAwQO</t>
+          <t>vFNb1rQ5</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>lekue inigo</t>
+          <t>sabaly youssouf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>x2fvXYO7</t>
+          <t>8K4WA9Gh</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vivian daniel</t>
+          <t>bartra marc</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>nev6Da3D</t>
+          <t>2XJ8qBI1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>alvarez yeray</t>
+          <t>llorente diego</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>OCA7UnaC</t>
+          <t>8EqrjqCF</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>berchiche yuri</t>
+          <t>rodriguez ricardo</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>t2Srcdis</t>
+          <t>jmbMzvQa</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>prados benat</t>
+          <t>carvalho william</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>CSIEND11</t>
+          <t>0SJZRycC</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>vesga mikel</t>
+          <t>roca marc</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>nuQn903r</t>
+          <t>CfghB0gf</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>berenguer alejandro</t>
+          <t>fornals pablo</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>hpZLKZVC</t>
+          <t>xG1QmowQ</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>sancet ohian</t>
+          <t>fekir nabil</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Cp7lcVjJ</t>
+          <t>0vLnUdTa</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>williams nico</t>
+          <t>juanmi</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>W4HzaGVn</t>
+          <t>jLOnYYdH</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>williams inaki</t>
+          <t>aitor rubal</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>IZm6H2pp</t>
+          <t>K4275W3e</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>astralaga aranguren ander</t>
+          <t>benavidez carlos</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>tAhLmeJb</t>
+          <t>Op7pPJv2</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>casado marc</t>
+          <t>diarra moussa</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>OClkc0eN</t>
+          <t>WhV8JXPD</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>dominguez sergi</t>
+          <t>guridi jon</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0l4CHjYp</t>
+          <t>dnvBgOsP</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>fort hector</t>
+          <t>martin carlos</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>AyxD3I5C</t>
+          <t>KtWwVS3K</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>garcia eric</t>
+          <t>novoa ramos hugo</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2c2ipETG</t>
+          <t>AcqRuf0b</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>marin fermin</t>
+          <t>owono jesus</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>nBVu0v9a</t>
+          <t>baSksbWn</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>martin gerard</t>
+          <t>pica adrian</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>M1W3ZQSs</t>
+          <t>0Oxc76wG</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>pena inaki</t>
+          <t>rebbach abderrahmane</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4WR4dTws</t>
+          <t>MLlf8c4E</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>torre carral pablo</t>
+          <t>rodriguez adrian</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>tjU5LW2F</t>
+          <t>r9HfBE6F</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>valle gomez alex</t>
+          <t>romero luka</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>QkMhPUdc</t>
+          <t>C4Qtc3iO</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>delgado pau victor</t>
+          <t>villalibre asier</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2iBBeOy8</t>
+          <t>CEm70uDg</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>agirrezabala julen</t>
+          <t>adrian</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>UuKvqHl9</t>
+          <t>4rf7A6PR</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>ares djalo malcom adu</t>
+          <t>altimira sergi</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>fR7uJqwO</t>
+          <t>UchGKR53</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>boiro adama</t>
+          <t>chimy avila</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>ljCE2GoH</t>
+          <t>pxq49QlK</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>de marcos oscar</t>
+          <t>bellerin hector</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>I71fjzT2</t>
+          <t>rZziaoTk</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>eguiluz unai</t>
+          <t>diao assane</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>tACTByTR</t>
+          <t>YRiVcQ3T</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>gastesi oier</t>
+          <t>ez abde</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>b9174gL1</t>
+          <t>CCyECQae</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>gomez unai</t>
+          <t>gonzalez manu</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>KEaIS3qg</t>
+          <t>v5Xtt1xa</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>espinoza andoni</t>
+          <t>johnny cardoso</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>bTKd7PI5</t>
+          <t>jmkzeFcs</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>guruzeta gorka</t>
+          <t>losada iker</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>jyzWX8yk</t>
+          <t>dpUJtnsM</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>herrera ander</t>
+          <t>natan</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>hOdEyz15</t>
+          <t>l6FMek3E</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>jauregizar mikel</t>
+          <t>perraud romain</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>nDleV6a5</t>
+          <t>Ik7xMDsb</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>javier marton</t>
+          <t>rodri</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>2c2ipETG</t>
+          <t>r9HfBE6F</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>marin fermin</t>
+          <t>romero luka</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>2c2ipETG</t>
+          <t>r9HfBE6F</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>marin fermin</t>
+          <t>romero luka</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>AVAVLaLt</t>
+          <t>zZJGkBEQ</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>torres ferran</t>
+          <t>conechny tomas</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>AyxD3I5C</t>
+          <t>dnvBgOsP</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>garcia eric</t>
+          <t>martin carlos</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>AyxD3I5C</t>
+          <t>dnvBgOsP</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>garcia eric</t>
+          <t>martin carlos</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>pf3IOiFD</t>
+          <t>Kneifk5H</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>bernal marc</t>
+          <t>stoichkov</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>QkMhPUdc</t>
+          <t>K4275W3e</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>delgado pau victor</t>
+          <t>benavidez carlos</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>QkMhPUdc</t>
+          <t>K4275W3e</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>delgado pau victor</t>
+          <t>benavidez carlos</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>lAt3vEub</t>
+          <t>hMjEwTOg</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>yamal lamine</t>
+          <t>guevara ander</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>nBVu0v9a</t>
+          <t>WhV8JXPD</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>martin gerard</t>
+          <t>guridi jon</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>nBVu0v9a</t>
+          <t>WhV8JXPD</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>martin gerard</t>
+          <t>guridi jon</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>6c0CXHVM</t>
+          <t>GfoivbEm</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>balde alejandro</t>
+          <t>kike</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>b9174gL1</t>
+          <t>Op7pPJv2</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>gomez unai</t>
+          <t>diarra moussa</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>b9174gL1</t>
+          <t>Op7pPJv2</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>gomez unai</t>
+          <t>diarra moussa</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>hpZLKZVC</t>
+          <t>bRBNu8DM</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>sancet ohian</t>
+          <t>vicente carlos</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>hOdEyz15</t>
+          <t>l6FMek3E</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>jauregizar mikel</t>
+          <t>perraud romain</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>hOdEyz15</t>
+          <t>l6FMek3E</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>jauregizar mikel</t>
+          <t>perraud romain</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>CSIEND11</t>
+          <t>8EqrjqCF</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>vesga mikel</t>
+          <t>rodriguez ricardo</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>UuKvqHl9</t>
+          <t>YRiVcQ3T</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>ares djalo malcom adu</t>
+          <t>ez abde</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>UuKvqHl9</t>
+          <t>YRiVcQ3T</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>ares djalo malcom adu</t>
+          <t>ez abde</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>nuQn903r</t>
+          <t>0vLnUdTa</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>berenguer alejandro</t>
+          <t>juanmi</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>bTKd7PI5</t>
+          <t>UchGKR53</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>guruzeta gorka</t>
+          <t>chimy avila</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>bTKd7PI5</t>
+          <t>UchGKR53</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>guruzeta gorka</t>
+          <t>chimy avila</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>W4HzaGVn</t>
+          <t>jLOnYYdH</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>williams inaki</t>
+          <t>aitor rubal</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>jyzWX8yk</t>
+          <t>Ik7xMDsb</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>herrera ander</t>
+          <t>rodri</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>jyzWX8yk</t>
+          <t>Ik7xMDsb</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>herrera ander</t>
+          <t>rodri</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>t2Srcdis</t>
+          <t>CfghB0gf</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>prados benat</t>
+          <t>fornals pablo</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>ShxiZhJI</t>
+          <t>dpUJtnsM</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>christensen andreas</t>
+          <t>natan</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>A1F3rz9c</t>
+          <t>dpUJtnsM</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>de jong frenkie</t>
+          <t>natan</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>dUPVnxzP</t>
+          <t>8K4WA9Gh</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>fati ansu</t>
+          <t>bartra marc</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>xrV9v8CU</t>
+          <t>vZ3QJXBc</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>gavi</t>
+          <t>bakambu cedric</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>hxVl8TRJ</t>
+          <t>f7TcxoGd</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>djalo alvaro</t>
+          <t>garreta felix marti</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>ChK2eOCj</t>
+          <t>ULLmpdEb</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>paredes aitor</t>
+          <t>isco</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>AqAnv17H</t>
+          <t>by4YfNNK</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>inigo ruiz</t>
+          <t>mendy nobel</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>nPdiENxr</t>
+          <t>SEXE75E5</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>serrano nico</t>
-        </is>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>Ao9Vw3hi</t>
-        </is>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>simon unai</t>
-        </is>
-      </c>
+          <t>vieites francisco</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
       <c r="FH2" t="inlineStr"/>
       <c r="FI2" t="inlineStr"/>
       <c r="FJ2" t="inlineStr"/>
@@ -2120,793 +2112,809 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YDyOrTQO</t>
+          <t>tAaD36mt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>herrera sergio</t>
+          <t>soriano juan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>rPdVeI18</t>
+          <t>6B7YK1Tu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>areso jesus</t>
+          <t>rosier valentin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vqO0hBvp</t>
+          <t>UkvndELE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>catena alejandro</t>
+          <t>arambarri aritz</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>b7V04HCM</t>
+          <t>6Nmx29Pj</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>herrando jorge</t>
+          <t>gonzalez sergio</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4rC8UP44</t>
+          <t>6NFqRQVg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>bertones abel</t>
+          <t>hernandez javi</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>KCtH4oIT</t>
+          <t>OAPggVhT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>moncayola jon</t>
+          <t>brasanac darko</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6y9ES72S</t>
+          <t>SbettZSO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>torro lucas</t>
+          <t>neyou noupa yvan</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SlzBPHAH</t>
+          <t>2cPwbh8J</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>oroz aimar</t>
+          <t>raba daniel</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Gpc9AB61</t>
+          <t>E3s5eF5I</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>garcia ruben</t>
+          <t>cisse seydouba</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>IeVXGQOi</t>
+          <t>WWNny3e7</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>budimir ante</t>
+          <t>rodriguez oscar</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>hQyTbdVL</t>
+          <t>6yaQrJGS</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>zaragoza bryan</t>
+          <t>de la fuente miguel</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>ID9k7lap</t>
+          <t>25zBQ1q4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>greif dominik</t>
+          <t>cillessen jasper</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>KvHXl88g</t>
+          <t>fBI7cV4b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>maffeo pablo</t>
+          <t>alex suarez</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>pbb8dhGG</t>
+          <t>AerDGNDO</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>valjent martin</t>
+          <t>mckenna scott</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>p8RSvp74</t>
+          <t>Cz3awDFR</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>raillo antonio</t>
+          <t>marmol mika</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>drRlRNNC</t>
+          <t>xlaNl83K</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>mojica johan</t>
+          <t>munoz alex</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>On7NYLWr</t>
+          <t>lQJaaIBC</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>darder sergi</t>
+          <t>munoz javier</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>vJSVZFpR</t>
+          <t>OKNQawg3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>mascarell omar</t>
+          <t>kirian</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>AXPRNqQn</t>
+          <t>SjTBQO7b</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>costa samuel</t>
+          <t>park marvin</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>lrscbe6I</t>
+          <t>b5g6gWjn</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>asano takuma</t>
+          <t>moleiro alberto</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>CjwNDgqi</t>
+          <t>fapXP9VS</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>muriqi vedat</t>
+          <t>ramirez sandro</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>n7jmYVFc</t>
+          <t>rNFSg6i4</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>rodriguez daniel</t>
+          <t>mcburnie oliver</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>ObepFC6G</t>
+          <t>4AaiuZpF</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>benito iker</t>
+          <t>altimira adria</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fmw1xiyC</t>
+          <t>zk34NV3A</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>alvin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>WWHLyhpR</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>chicco julian</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>E5Et3VgM</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
           <t>cruz juan</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>htdKMO9m</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>fernandez aitor</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2HT2pDXL</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>de haro raul</t>
-        </is>
-      </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>KShEvv1N</t>
+          <t>pO8Jn4Xm</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>garcia unai</t>
+          <t>dmitrovic marko</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8b86g1el</t>
+          <t>0QAeQWxE</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>gomez moi</t>
+          <t>franquesa enric</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>xOWXxrsi</t>
+          <t>EeUtTZld</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>ibanez pablo</t>
+          <t>garcia campos diego</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>nBYFHtta</t>
+          <t>pIpdGy2U</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>martinez calvo javier</t>
+          <t>lopez roberto</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>ncU1c1uo</t>
+          <t>CKYnnUEo</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>munoz iker</t>
+          <t>munir el haddadi</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>x8pmKbnD</t>
+          <t>AufokyHE</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>stamatakis dimitrios</t>
+          <t>porozo jackson</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>tCpvIBRC</t>
+          <t>EwStt8o4</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>vidal nacho</t>
+          <t>saenz jorge</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>ABXxQRR6</t>
+          <t>A16UgbkJ</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>arias copete jose manuel</t>
+          <t>bassinga aboubacar</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>xUwdHPXa</t>
+          <t>KE0WWa1e</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>domenech marc</t>
+          <t>campana jose</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>vNpXFtuQ</t>
+          <t>AkH99Ojn</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>larin cyle</t>
+          <t>cardona marc</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>hCPqc747</t>
+          <t>UaHeoBot</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>lato toni</t>
+          <t>fuster manuel</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>bkeWsRZc</t>
+          <t>jTdCpLmR</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>luna daniel</t>
+          <t>gil ivan</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>nerrfVfR</t>
+          <t>xrJQVv9C</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>morlanes manu</t>
+          <t>herzog juanma</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>lx119mnI</t>
+          <t>nw5d39V0</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>cuellar ivan</t>
+          <t>horkas dinko</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>zB1s0lKl</t>
+          <t>px36Cwpj</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>prats abdon</t>
+          <t>loiodice enzo</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>pIgzAKRr</t>
+          <t>r92RZve6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>roman leonardo</t>
+          <t>mata jaime</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>feNCiQzT</t>
+          <t>pjIG0H3d</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>salas jan</t>
+          <t>ramirez benito</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>pSceH9EI</t>
+          <t>hSNXqigO</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>sanchez antonio</t>
+          <t>sinkgraven daley</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>fToJY0qQ</t>
+          <t>tYi46reg</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>van der heyden siebe</t>
+          <t>viti</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>8b86g1el</t>
+          <t>6qPig05P</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>gomez moi</t>
+          <t>tapia renato</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>8b86g1el</t>
+          <t>6qPig05P</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>gomez moi</t>
+          <t>tapia renato</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>Gpc9AB61</t>
+          <t>OAPggVhT</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>garcia ruben</t>
+          <t>brasanac darko</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>ncU1c1uo</t>
+          <t>E5Et3VgM</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>munoz iker</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>ncU1c1uo</t>
+          <t>E5Et3VgM</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>munoz iker</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>SlzBPHAH</t>
+          <t>2cPwbh8J</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>oroz aimar</t>
+          <t>raba daniel</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>2HT2pDXL</t>
+          <t>EeUtTZld</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>de haro raul</t>
+          <t>garcia campos diego</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>2HT2pDXL</t>
+          <t>EeUtTZld</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>de haro raul</t>
+          <t>garcia campos diego</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>IeVXGQOi</t>
+          <t>6yaQrJGS</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>budimir ante</t>
+          <t>de la fuente miguel</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>tCpvIBRC</t>
+          <t>0QAeQWxE</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>vidal nacho</t>
+          <t>franquesa enric</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>tCpvIBRC</t>
+          <t>0QAeQWxE</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>vidal nacho</t>
+          <t>franquesa enric</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>rPdVeI18</t>
+          <t>E3s5eF5I</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>areso jesus</t>
+          <t>cisse seydouba</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>nerrfVfR</t>
+          <t>4AaiuZpF</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>morlanes manu</t>
+          <t>altimira adria</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>nerrfVfR</t>
+          <t>4AaiuZpF</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>morlanes manu</t>
+          <t>altimira adria</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>vJSVZFpR</t>
+          <t>WWNny3e7</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>mascarell omar</t>
+          <t>rodriguez oscar</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>vNpXFtuQ</t>
+          <t>tYi46reg</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>larin cyle</t>
+          <t>viti</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>vNpXFtuQ</t>
+          <t>tYi46reg</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>larin cyle</t>
+          <t>viti</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>lrscbe6I</t>
+          <t>fBI7cV4b</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>asano takuma</t>
+          <t>alex suarez</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>pSceH9EI</t>
+          <t>px36Cwpj</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>sanchez antonio</t>
+          <t>loiodice enzo</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>pSceH9EI</t>
+          <t>px36Cwpj</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>sanchez antonio</t>
+          <t>loiodice enzo</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>n7jmYVFc</t>
+          <t>b5g6gWjn</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>rodriguez daniel</t>
+          <t>moleiro alberto</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>zB1s0lKl</t>
+          <t>pjIG0H3d</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>prats abdon</t>
+          <t>ramirez benito</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>zB1s0lKl</t>
+          <t>pjIG0H3d</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>prats abdon</t>
+          <t>ramirez benito</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>On7NYLWr</t>
+          <t>SjTBQO7b</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>darder sergi</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
-      <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="inlineStr"/>
-      <c r="EN3" t="inlineStr"/>
-      <c r="EO3" t="inlineStr"/>
+          <t>park marvin</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>r92RZve6</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>mata jaime</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>r92RZve6</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>mata jaime</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>xlaNl83K</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>munoz alex</t>
+        </is>
+      </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>8psoD6vm</t>
+          <t>UaHeoBot</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>arnaiz jose</t>
+          <t>fuster manuel</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>KxtC5I27</t>
+          <t>UaHeoBot</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>barja enrique</t>
+          <t>fuster manuel</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>hvSbhBpg</t>
+          <t>OKNQawg3</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
         <is>
-          <t>pena ruben</t>
-        </is>
-      </c>
-      <c r="EV3" t="inlineStr"/>
-      <c r="EW3" t="inlineStr"/>
+          <t>kirian</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>fgqxKdwL</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>gonzalez fabio</t>
+        </is>
+      </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>Ew10Xoy6</t>
+          <t>6qyeYCYO</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>llabres javier</t>
+          <t>januzaj adnan</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>jRBXx0H4</t>
+          <t>St8XPCaD</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>morey mateu</t>
+          <t>pejino</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr"/>
       <c r="FC3" t="inlineStr"/>
       <c r="FD3" t="inlineStr"/>
       <c r="FE3" t="inlineStr"/>
-      <c r="FF3" t="inlineStr"/>
-      <c r="FG3" t="inlineStr"/>
-      <c r="FH3" t="inlineStr">
-        <is>
-          <t>xOWXxrsi</t>
-        </is>
-      </c>
-      <c r="FI3" t="inlineStr">
-        <is>
-          <t>ibanez pablo</t>
-        </is>
-      </c>
-      <c r="FJ3" t="inlineStr">
-        <is>
-          <t>xOWXxrsi</t>
-        </is>
-      </c>
-      <c r="FK3" t="inlineStr">
-        <is>
-          <t>ibanez pablo</t>
-        </is>
-      </c>
-      <c r="FL3" t="inlineStr">
-        <is>
-          <t>ncU1c1uo</t>
-        </is>
-      </c>
-      <c r="FM3" t="inlineStr">
-        <is>
-          <t>munoz iker</t>
-        </is>
-      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
+          <t>6qPig05P</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr">
+        <is>
+          <t>tapia renato</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr"/>
+      <c r="FI3" t="inlineStr"/>
+      <c r="FJ3" t="inlineStr"/>
+      <c r="FK3" t="inlineStr"/>
+      <c r="FL3" t="inlineStr"/>
+      <c r="FM3" t="inlineStr"/>
       <c r="FN3" t="inlineStr"/>
       <c r="FO3" t="inlineStr"/>
       <c r="FP3" t="inlineStr"/>
@@ -2915,2353 +2923,2329 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UJ9btoDi</t>
+          <t>MVExOq3n</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nyland orjan</t>
+          <t>courtois thibaut</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dE2MbgQ4</t>
+          <t>rZh5FTHE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>carmona jose angel</t>
+          <t>carvajal daniel</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>YgxuEfvL</t>
+          <t>zX2Rm9YG</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>bade loic</t>
+          <t>militao eder</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6uf4Y1d2</t>
+          <t>rZHXvTho</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>rooms kike</t>
+          <t>rudiger antonio</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>t4j4NUO8</t>
+          <t>tURBbW9S</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>pedrosa adria</t>
+          <t>fran garcia</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CtN0gVgf</t>
+          <t>nscfER6B</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>sanchez juanlu</t>
+          <t>valverde federico</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>bmJjJR1B</t>
+          <t>QkiZum3e</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>agoume lucien</t>
+          <t>tchouameni aurelien</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>hSbvVwW7</t>
+          <t>zPUyR5Up</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>niguez saul</t>
+          <t>rodrygo</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>08a9jhm9</t>
+          <t>CUU9qDpb</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>lukebakio dodi</t>
+          <t>guler arda</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>OK0Lcg44</t>
+          <t>CbwQ4Mws</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>romero isaac</t>
+          <t>vinicius junior</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2s2ATpKI</t>
+          <t>Wn6E2SED</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>ocampos lucas</t>
+          <t>mbappe kylian</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>GMOMNJbs</t>
+          <t>jyH8E81E</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>conde diego</t>
+          <t>hein karl</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ryjofHOu</t>
+          <t>4zgv0hGk</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>kiko</t>
+          <t>perez luis</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>S6QWzDng</t>
+          <t>EZg4jPUF</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>kambwala willy</t>
+          <t>comert eray</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>G8VcNrxU</t>
+          <t>G6IFcpHK</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>bailly eric</t>
+          <t>boyomos flavien enzo</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>vVh7yy15</t>
+          <t>2g3Pa3qH</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>cardona sergi</t>
+          <t>rosa lucas</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>ATAVnRY7</t>
+          <t>SCxfo9Zu</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>akhomach ilias</t>
+          <t>kike</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>p6rsDQvN</t>
+          <t>dfLinARB</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>gueye pape</t>
+          <t>juric stanko</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>KK4TPIBj</t>
+          <t>vkmiDN8F</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>comesana santi</t>
+          <t>sanchez ivan</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>bmeQTB92</t>
+          <t>EN3EbULf</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>baena alex</t>
+          <t>meseguer victor</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>j3Hk0qEj</t>
+          <t>nBtLrBRF</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>pepe nicolas</t>
+          <t>machis darwin</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>tYV4tvqr</t>
+          <t>dEgxh8oM</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>groeneveld arnaut</t>
+          <t>marcos andre</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>8zvngfOe</t>
+          <t>zPYmze7F</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>ejuke chidera</t>
+          <t>ceballos dani</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>tfywn0Ad</t>
+          <t>nm2Qvnyk</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>fernandez alvaro</t>
+          <t>diaz brahim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>SKLFEpf6</t>
+          <t>bXHrpEJ4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>gudelj nemanja</t>
+          <t>endrick</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>zRYlzwwb</t>
+          <t>Is0aEgM6</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>idumbo muzambo stanis</t>
+          <t>perez francisco javier gonzalez</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>dIaES012</t>
+          <t>pEjBDsSH</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>iheanacho kelechi</t>
+          <t>lucas</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>fefkCPrH</t>
+          <t>0S7ye9jr</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>lokonga sambi</t>
+          <t>lunin andriy</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>OOFwBfsT</t>
+          <t>bZWyoJnA</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>marcao</t>
+          <t>modric luka</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>rN9tdN16</t>
+          <t>dIvLWqXc</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>montiel gonzalo</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>hWt5ZIrn</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>navas jesus</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>zHxpGqc8</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>kouassi nianzou</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>GOkrxtHi</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>peque</t>
-        </is>
-      </c>
+          <t>naveros jacobo</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>AkMslDtA</t>
+          <t>f7bNFe72</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>albiol raul</t>
+          <t>amallah selim</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>KYQuxWEL</t>
+          <t>bcJKuoR6</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>barry thierno</t>
+          <t>chuki</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>EL0WleP6</t>
+          <t>0n8qUmN8</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>costa logan</t>
+          <t>de la hoz cesar</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>WShuFWRi</t>
+          <t>j5SMgGHu</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>junior reis</t>
+          <t>ferreira andre</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>UwfDD083</t>
+          <t>UHqRA6g4</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>moreno gerard</t>
+          <t>iglesias koke</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>bwHQNPyE</t>
+          <t>IXreUcCq</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>navarro pablo</t>
+          <t>martin mario</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>z7YvfLZ8</t>
+          <t>zw8vYjwk</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>parejo daniel</t>
+          <t>moro raul</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>jVHfHxGn</t>
+          <t>42y06OiE</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>perez ayoze</t>
+          <t>ndiaye amath</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>8fnHDvMe</t>
+          <t>AJg8NPiE</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>santos yeremi</t>
+          <t>ruiz raul chasco</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>Kjmmf9C3</t>
+          <t>6NytetE5</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>sola arnau</t>
+          <t>sanchez javier</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>rLsgetTF</t>
+          <t>YqtgOOMN</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>terrats ramon</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
+          <t>sylla mamadou</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>8S0B28YJ</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>torres david</t>
+        </is>
+      </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>tUNr1qOE</t>
+          <t>bZWyoJnA</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>sow djibril</t>
+          <t>modric luka</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>tUNr1qOE</t>
+          <t>bZWyoJnA</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>sow djibril</t>
+          <t>modric luka</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>08a9jhm9</t>
+          <t>zPUyR5Up</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>lukebakio dodi</t>
+          <t>rodrygo</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>8zvngfOe</t>
+          <t>nm2Qvnyk</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>ejuke chidera</t>
+          <t>diaz brahim</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>8zvngfOe</t>
+          <t>nm2Qvnyk</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>ejuke chidera</t>
+          <t>diaz brahim</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>CtN0gVgf</t>
+          <t>CUU9qDpb</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>sanchez juanlu</t>
+          <t>guler arda</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>OOFwBfsT</t>
+          <t>zPYmze7F</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>marcao</t>
+          <t>ceballos dani</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>OOFwBfsT</t>
+          <t>zPYmze7F</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>marcao</t>
+          <t>ceballos dani</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>6uf4Y1d2</t>
+          <t>CbwQ4Mws</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>rooms kike</t>
+          <t>vinicius junior</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
         <is>
-          <t>dIaES012</t>
+          <t>bXHrpEJ4</t>
         </is>
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>iheanacho kelechi</t>
+          <t>endrick</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>dIaES012</t>
+          <t>bXHrpEJ4</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>iheanacho kelechi</t>
+          <t>endrick</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>OK0Lcg44</t>
+          <t>Wn6E2SED</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>romero isaac</t>
-        </is>
-      </c>
-      <c r="DL4" t="inlineStr">
-        <is>
-          <t>KYQuxWEL</t>
-        </is>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>barry thierno</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>KYQuxWEL</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>barry thierno</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>j3Hk0qEj</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>pepe nicolas</t>
-        </is>
-      </c>
+          <t>mbappe kylian</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>jVHfHxGn</t>
+          <t>zw8vYjwk</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>perez ayoze</t>
+          <t>moro raul</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>jVHfHxGn</t>
+          <t>zw8vYjwk</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
         <is>
-          <t>perez ayoze</t>
+          <t>moro raul</t>
         </is>
       </c>
       <c r="DV4" t="inlineStr">
         <is>
-          <t>tYV4tvqr</t>
+          <t>nBtLrBRF</t>
         </is>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>groeneveld arnaut</t>
+          <t>machis darwin</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>8fnHDvMe</t>
+          <t>f7bNFe72</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>santos yeremi</t>
+          <t>amallah selim</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
         <is>
-          <t>8fnHDvMe</t>
+          <t>f7bNFe72</t>
         </is>
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>santos yeremi</t>
+          <t>amallah selim</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
         <is>
-          <t>ATAVnRY7</t>
+          <t>EN3EbULf</t>
         </is>
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>akhomach ilias</t>
+          <t>meseguer victor</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>z7YvfLZ8</t>
+          <t>YqtgOOMN</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>parejo daniel</t>
+          <t>sylla mamadou</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>z7YvfLZ8</t>
+          <t>YqtgOOMN</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>parejo daniel</t>
+          <t>sylla mamadou</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>KK4TPIBj</t>
+          <t>dEgxh8oM</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>comesana santi</t>
+          <t>marcos andre</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>AkMslDtA</t>
+          <t>IXreUcCq</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>albiol raul</t>
+          <t>martin mario</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>AkMslDtA</t>
+          <t>IXreUcCq</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
         <is>
-          <t>albiol raul</t>
+          <t>martin mario</t>
         </is>
       </c>
       <c r="EN4" t="inlineStr">
         <is>
-          <t>G8VcNrxU</t>
+          <t>dfLinARB</t>
         </is>
       </c>
       <c r="EO4" t="inlineStr">
         <is>
-          <t>bailly eric</t>
+          <t>juric stanko</t>
         </is>
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>nmjvsTy0</t>
+          <t>42y06OiE</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>jordan joan</t>
+          <t>ndiaye amath</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
         <is>
-          <t>Aexbrioc</t>
+          <t>42y06OiE</t>
         </is>
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>suso</t>
-        </is>
-      </c>
-      <c r="ET4" t="inlineStr"/>
-      <c r="EU4" t="inlineStr"/>
-      <c r="EV4" t="inlineStr"/>
-      <c r="EW4" t="inlineStr"/>
-      <c r="EX4" t="inlineStr">
-        <is>
-          <t>KxSmFSum</t>
-        </is>
-      </c>
-      <c r="EY4" t="inlineStr">
-        <is>
-          <t>alfonso pedraza</t>
-        </is>
-      </c>
-      <c r="EZ4" t="inlineStr">
-        <is>
-          <t>vcqiFPHQ</t>
-        </is>
-      </c>
-      <c r="FA4" t="inlineStr">
-        <is>
-          <t>foyth juan</t>
-        </is>
-      </c>
-      <c r="FB4" t="inlineStr">
-        <is>
-          <t>xWwucZ71</t>
-        </is>
-      </c>
-      <c r="FC4" t="inlineStr">
-        <is>
-          <t>suarez denis</t>
-        </is>
-      </c>
+          <t>ndiaye amath</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>SCxfo9Zu</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t>kike</t>
+        </is>
+      </c>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t>bygTWQzR</t>
+        </is>
+      </c>
+      <c r="EW4" t="inlineStr">
+        <is>
+          <t>anuar</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="inlineStr"/>
+      <c r="FA4" t="inlineStr"/>
+      <c r="FB4" t="inlineStr"/>
+      <c r="FC4" t="inlineStr"/>
       <c r="FD4" t="inlineStr"/>
       <c r="FE4" t="inlineStr"/>
       <c r="FF4" t="inlineStr"/>
       <c r="FG4" t="inlineStr"/>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>hWt5ZIrn</t>
+          <t>hKx3nCTp</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>navas jesus</t>
+          <t>alaba david</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>hWt5ZIrn</t>
+          <t>QNvlPm7s</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
         <is>
-          <t>navas jesus</t>
+          <t>bellingham jude</t>
         </is>
       </c>
       <c r="FL4" t="inlineStr">
         <is>
-          <t>2s2ATpKI</t>
+          <t>6ekYsPfO</t>
         </is>
       </c>
       <c r="FM4" t="inlineStr">
         <is>
-          <t>ocampos lucas</t>
+          <t>camavinga eduardo</t>
         </is>
       </c>
       <c r="FN4" t="inlineStr">
         <is>
-          <t>tUNr1qOE</t>
+          <t>KnytnSKl</t>
         </is>
       </c>
       <c r="FO4" t="inlineStr">
         <is>
-          <t>sow djibril</t>
-        </is>
-      </c>
-      <c r="FP4" t="inlineStr"/>
-      <c r="FQ4" t="inlineStr"/>
+          <t>mendy ferland</t>
+        </is>
+      </c>
+      <c r="FP4" t="inlineStr">
+        <is>
+          <t>WSRdoQ7I</t>
+        </is>
+      </c>
+      <c r="FQ4" t="inlineStr">
+        <is>
+          <t>vallejo jesus</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IRro97ls</t>
+          <t>vuAlEqes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>villar ivan</t>
+          <t>garcia joan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bsZTFhAa</t>
+          <t>z9FaGS78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rodriguez galiano javier</t>
+          <t>el hilali omar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ITqxsbsR</t>
+          <t>8xTCtgln</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jailson</t>
+          <t>kumbulla marash</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>f79qYNc4</t>
+          <t>IsOwrMdM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>dominguez carlos</t>
+          <t>cabrera leandro</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>nyLFv8t3</t>
+          <t>YDxiIlER</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>alvarez hugo</t>
+          <t>romero carlos</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>zykz5SJb</t>
+          <t>KSNZwPAG</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>beltran francisco</t>
+          <t>carreras jofe</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>IR1ghK3I</t>
+          <t>QPoHzbRQ</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>rodriguez damian</t>
+          <t>gragera jose</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>YkHSwt2b</t>
+          <t>UuiJcUMl</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>mingueza oscar</t>
+          <t>kral alex</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>rVBGggAd</t>
+          <t>86UW3kYK</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>aspas iago</t>
+          <t>cardona irvin</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>YgPGkQYi</t>
+          <t>hph7e3vc</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>douvikas anastasios</t>
+          <t>veliz alejo</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>KluZeL4G</t>
+          <t>Cl8Ia7Q9</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>swedberg williot</t>
+          <t>puado javi</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>lxnsUkIc</t>
+          <t>UmDjbtRC</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>mamardashvili giorgi</t>
+          <t>remiro alejandro</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Sv5sgVLE</t>
+          <t>fRSnvKQG</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>correia thierry</t>
+          <t>traore hamari</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>4O15XViB</t>
+          <t>6qVwC9AH</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>mosquera cristhian</t>
+          <t>elustondo aritz</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4UxxcIjS</t>
+          <t>Qk9dJWGB</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>hernadis yarek gasiorowski</t>
+          <t>pacheco jon</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>M5U2cN2q</t>
+          <t>MaufHIJ2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>vazquez jesus</t>
+          <t>lopez javi</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>IXRaCzVt</t>
+          <t>2scm2TO3</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>mir rafael</t>
+          <t>becker sheraldo</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>nosv3azp</t>
+          <t>fNI6Gsdr</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>pepelu</t>
+          <t>zubimendi martin</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2yyy00aj</t>
+          <t>WtVfJtAm</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>guerra javi</t>
+          <t>turrientes benat</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>SGjehmsG</t>
+          <t>fmGvlHVM</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>lopez noguerol diego</t>
+          <t>gomez sergio</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>WO3oyVW7</t>
+          <t>Ey5XjmJt</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>almeida andre</t>
+          <t>mendez brais</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>EP4vWYSf</t>
+          <t>dQ1P695O</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>duro hugo</t>
+          <t>oyarzabal mikel</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>AVpwhNL9</t>
+          <t>fyEdYgal</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>aidoo joseph</t>
+          <t>aguado alvaro</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>n9uHpbM8</t>
+          <t>jcshWJpG</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>bamba jonathan</t>
+          <t>bauza rafel</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>rHUdQZPd</t>
+          <t>Sj35PsHd</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>carreira sergio</t>
+          <t>calero fernando</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>b7lKkJBn</t>
+          <t>jRx96X5h</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>duran pablo</t>
+          <t>fortuno angel</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>IXim7pWh</t>
+          <t>v1bRsEDN</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>gonzalez alfonso</t>
+          <t>gomez sergi</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>Au7zDEEL</t>
+          <t>6o8Nnmm1</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>guaita vicente</t>
+          <t>lozano pol</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0vQciH42</t>
+          <t>EsMMVFh3</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>iglesias borja</t>
+          <t>milla pere</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>8bvxeNAG</t>
+          <t>n9R1WQ3p</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>manquillo javier</t>
+          <t>olivan brian</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>MoAntFV8</t>
+          <t>27U3P9mT</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>kourouma moriba</t>
+          <t>pacheco fernando</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>tGJYwtjh</t>
+          <t>ILCGOm9n</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>sotelo hugo</t>
+          <t>roca antoniu</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>ptNHGRiJ</t>
+          <t>x0TzcxX6</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>starfelt carl</t>
+          <t>sanchez salvi</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2axfsTHA</t>
+          <t>vNTtZiAr</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>dimitrievski stole</t>
+          <t>aranburu jon</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>65F8DTep</t>
+          <t>QLpDwPEJ</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>foulquier dimitri</t>
+          <t>arana egoitz</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>UVDJACJ9</t>
+          <t>OvykMeki</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>gomez daniel</t>
+          <t>gonzalez urko</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>Wpw94bj6</t>
+          <t>fqdLdpc3</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>guillamon hugo</t>
+          <t>kubo takefusa</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>WKSwzS4T</t>
+          <t>0IZE0zuH</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>jimenez raul</t>
+          <t>magunazelaia jon</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>4bjEksiR</t>
+          <t>Ye976xiA</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>mari alberto</t>
+          <t>marin pablo</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>UkN5Fwzd</t>
+          <t>Wr5ZTIf7</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>otorbi david</t>
+          <t>marrero larranaga unai</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>Iefc5Fwo</t>
+          <t>dd9n67gb</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>ozkacar cenk</t>
+          <t>martin jon</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>h8cBI9v2</t>
+          <t>C8QkouJU</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>rioja luis</t>
+          <t>munoz aihen</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>p0AiQXJi</t>
+          <t>O8nKKpaP</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>abajas rodrigo</t>
+          <t>olasagasti jon</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>CIrZ775M</t>
+          <t>UsKF9Yzn</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>tarrega cesar</t>
+          <t>sadiq umar</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>Grc4eSof</t>
+          <t>p6f9CgsE</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>tejon martin</t>
+          <t>sucic luka</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>rHUdQZPd</t>
+          <t>n9R1WQ3p</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>carreira sergio</t>
+          <t>olivan brian</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>rHUdQZPd</t>
+          <t>n9R1WQ3p</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>carreira sergio</t>
+          <t>olivan brian</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>YkHSwt2b</t>
+          <t>86UW3kYK</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>mingueza oscar</t>
+          <t>cardona irvin</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>n9uHpbM8</t>
+          <t>fyEdYgal</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>bamba jonathan</t>
+          <t>aguado alvaro</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>n9uHpbM8</t>
+          <t>fyEdYgal</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>bamba jonathan</t>
+          <t>aguado alvaro</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>KluZeL4G</t>
+          <t>QPoHzbRQ</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>swedberg williot</t>
+          <t>gragera jose</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>0vQciH42</t>
+          <t>ILCGOm9n</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>iglesias borja</t>
+          <t>roca antoniu</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>0vQciH42</t>
+          <t>ILCGOm9n</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>iglesias borja</t>
+          <t>roca antoniu</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>YgPGkQYi</t>
+          <t>KSNZwPAG</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>douvikas anastasios</t>
+          <t>carreras jofe</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>ptNHGRiJ</t>
+          <t>EsMMVFh3</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>starfelt carl</t>
+          <t>milla pere</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>ptNHGRiJ</t>
+          <t>EsMMVFh3</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>starfelt carl</t>
+          <t>milla pere</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>bsZTFhAa</t>
+          <t>YDxiIlER</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>rodriguez galiano javier</t>
+          <t>romero carlos</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>h8cBI9v2</t>
+          <t>n7ISbL3j</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>rioja luis</t>
+          <t>tejero alvaro</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>h8cBI9v2</t>
+          <t>n7ISbL3j</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>rioja luis</t>
+          <t>tejero alvaro</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>2yyy00aj</t>
+          <t>z9FaGS78</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>guerra javi</t>
+          <t>el hilali omar</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>Grc4eSof</t>
+          <t>fqdLdpc3</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>tejon martin</t>
+          <t>kubo takefusa</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>Grc4eSof</t>
+          <t>fqdLdpc3</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>tejon martin</t>
+          <t>kubo takefusa</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>SGjehmsG</t>
+          <t>Ey5XjmJt</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>lopez noguerol diego</t>
+          <t>mendez brais</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>65F8DTep</t>
+          <t>O8nKKpaP</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>foulquier dimitri</t>
+          <t>olasagasti jon</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>65F8DTep</t>
+          <t>O8nKKpaP</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>foulquier dimitri</t>
+          <t>olasagasti jon</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>Sv5sgVLE</t>
+          <t>WtVfJtAm</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>correia thierry</t>
+          <t>turrientes benat</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>UVDJACJ9</t>
+          <t>UsKF9Yzn</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>gomez daniel</t>
+          <t>sadiq umar</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>UVDJACJ9</t>
+          <t>UsKF9Yzn</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>gomez daniel</t>
+          <t>sadiq umar</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>EP4vWYSf</t>
+          <t>dQ1P695O</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>duro hugo</t>
+          <t>oyarzabal mikel</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>4bjEksiR</t>
+          <t>vNTtZiAr</t>
         </is>
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>mari alberto</t>
+          <t>aranburu jon</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>4bjEksiR</t>
+          <t>vNTtZiAr</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
         <is>
-          <t>mari alberto</t>
+          <t>aranburu jon</t>
         </is>
       </c>
       <c r="EN5" t="inlineStr">
         <is>
-          <t>IXRaCzVt</t>
+          <t>fRSnvKQG</t>
         </is>
       </c>
       <c r="EO5" t="inlineStr">
         <is>
-          <t>mir rafael</t>
+          <t>traore hamari</t>
         </is>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>GW5JRBD0</t>
+          <t>Ye976xiA</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>de la torre luca</t>
+          <t>marin pablo</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>8zW214va</t>
+          <t>Ye976xiA</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>ristic mihailo</t>
-        </is>
-      </c>
-      <c r="ET5" t="inlineStr"/>
-      <c r="EU5" t="inlineStr"/>
-      <c r="EV5" t="inlineStr"/>
-      <c r="EW5" t="inlineStr"/>
+          <t>marin pablo</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>2scm2TO3</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>becker sheraldo</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>A3vo4Lf6</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>barrenetxea muguruza ander</t>
+        </is>
+      </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>2iri9TaP</t>
+          <t>0zO9SfkA</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>canos sergi</t>
+          <t>odriozola alvaro</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>O6bdhMA2</t>
+          <t>r7qw7OKg</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>castillejo samu</t>
+          <t>zakharian arsen</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>2gqO56Xu</t>
+          <t>phTjGNq0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>diakhaby mouctar</t>
-        </is>
-      </c>
-      <c r="FD5" t="inlineStr">
-        <is>
-          <t>KbobTIgr</t>
-        </is>
-      </c>
-      <c r="FE5" t="inlineStr">
-        <is>
-          <t>domenech jaume</t>
-        </is>
-      </c>
+          <t>zubeldia igor</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr"/>
+      <c r="FE5" t="inlineStr"/>
       <c r="FF5" t="inlineStr">
         <is>
-          <t>xWguLPCU</t>
+          <t>n7ISbL3j</t>
         </is>
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>gaya jose</t>
+          <t>tejero alvaro</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>b7lKkJBn</t>
+          <t>SChm1pCo</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>duran pablo</t>
-        </is>
-      </c>
-      <c r="FJ5" t="inlineStr">
-        <is>
-          <t>b7lKkJBn</t>
-        </is>
-      </c>
-      <c r="FK5" t="inlineStr">
-        <is>
-          <t>duran pablo</t>
-        </is>
-      </c>
-      <c r="FL5" t="inlineStr">
-        <is>
-          <t>rVBGggAd</t>
-        </is>
-      </c>
-      <c r="FM5" t="inlineStr">
-        <is>
-          <t>aspas iago</t>
-        </is>
-      </c>
-      <c r="FN5" t="inlineStr">
-        <is>
-          <t>6HSinoFJ</t>
-        </is>
-      </c>
-      <c r="FO5" t="inlineStr">
-        <is>
-          <t>vidal marc</t>
-        </is>
-      </c>
-      <c r="FP5" t="inlineStr">
-        <is>
-          <t>bePNNa1r</t>
-        </is>
-      </c>
-      <c r="FQ5" t="inlineStr">
-        <is>
-          <t>perez francisco</t>
-        </is>
-      </c>
+          <t>exposito edu</t>
+        </is>
+      </c>
+      <c r="FJ5" t="inlineStr"/>
+      <c r="FK5" t="inlineStr"/>
+      <c r="FL5" t="inlineStr"/>
+      <c r="FM5" t="inlineStr"/>
+      <c r="FN5" t="inlineStr"/>
+      <c r="FO5" t="inlineStr"/>
+      <c r="FP5" t="inlineStr"/>
+      <c r="FQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fcYpyo85</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E34WEy2D</t>
+          <t>2VpTGXlE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fernandez andres</t>
+          <t>soria david</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bNOatO8R</t>
+          <t>K0bkMuVF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>garcia andres</t>
+          <t>iglesias juan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cn91dgeB</t>
+          <t>xnvqJMC1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>elgezabal unai</t>
+          <t>djene</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vk0AZDyh</t>
+          <t>fLceoUtl</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>cabello jorge</t>
+          <t>alderete omar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>x0EyRyUD</t>
+          <t>l0v5oji3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>navarro marcos</t>
+          <t>rico diego</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SIemT8iq</t>
+          <t>8fpOagmR</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>kochorashvili giorgi</t>
+          <t>sola alex</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>xhJNiaWc</t>
+          <t>lWTa55Ta</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>rey oriol</t>
+          <t>nabil aberdin</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>pWvRJqSt</t>
+          <t>jwhHdRF0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>brugue roger</t>
+          <t>milla luis</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Eguxo4bb</t>
+          <t>vP5uwPQf</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>alvarez carlos</t>
+          <t>alena carles</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6s42ZkRu</t>
+          <t>0WJHh4Qs</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>lozano sergio</t>
+          <t>perez carles</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>jXCYJBqg</t>
+          <t>8G2sXaI8</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>morales jose</t>
+          <t>uche chrisantus</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dfeW7Mbo</t>
+          <t>0v264VE8</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>gil david</t>
+          <t>cardenas dani</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>xbrr5N5M</t>
+          <t>CzBEqCjK</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>zaldua joseba</t>
+          <t>balliu ivan</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>ldvybSuH</t>
+          <t>K2JPoFRo</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>fali</t>
+          <t>mumin abdul</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2cLeSIk1</t>
+          <t>fNu1l3xc</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>chust victor</t>
+          <t>lejeune florian</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>GzloPZi6</t>
+          <t>vHFG4hw9</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>antonio cristian</t>
+          <t>espino alfonso</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>CUi1nPXC</t>
+          <t>fcuYevNb</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>isaac carcelen</t>
+          <t>valentin oscar</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>dKEu5Txk</t>
+          <t>zRB7v9IT</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>alcaraz ruben</t>
+          <t>ciss pathe</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>ferBlfmN</t>
+          <t>UiH85aKC</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>escalante gonzalo</t>
+          <t>de frutos jorge</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>YioE1eTi</t>
+          <t>42E71F4r</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>sobrino ruben</t>
+          <t>trejo oscar</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>xnYg4l8i</t>
+          <t>x8BHeb6c</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>ramos christopher</t>
+          <t>embarba adri</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>OGkTSXOg</t>
+          <t>M5IbUyg1</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>ocampo brian</t>
+          <t>nketa randy</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>biJcu016</t>
+          <t>viZPCO3c</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>algobia angel</t>
+          <t>alcantara alberto risco</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>INnNHikC</t>
+          <t>zHQB5zMa</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>bouldini mohamed</t>
+          <t>arambarri mauro</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Yqzk346P</t>
+          <t>8YG04fHd</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>clemente oscar</t>
+          <t>berrocal juan</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>hUTZz8kN</t>
+          <t>bDpj7xEB</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>cortina borja</t>
+          <t>duarte domingos</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>O6MiTbze</t>
+          <t>46yHKt1f</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>de la fuente adrian</t>
+          <t>letacek jiri</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>WURwLTen</t>
+          <t>lGNHRlTm</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>espi carlos</t>
+          <t>peter federico</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>ln6I6cmp</t>
+          <t>QPU3c6Hm</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>fernandez victor</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>dlLPyt7q</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>primo alejandro</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>lbxUqXq3</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>romero ivan</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>OA13bbjO</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>selles david</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>KK19HiR5</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>grande xavier</t>
-        </is>
-      </c>
+          <t>santiago yellu</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0I0RtqEN</t>
+          <t>8Wuyaqc4</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>alejo ivan</t>
+          <t>batalla augusto</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>84UQsk74</t>
+          <t>fFlZRkvF</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>almagro samu</t>
+          <t>camello sergio</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0GWHdB0l</t>
+          <t>hGPnN7fG</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>aznar ussen victor</t>
+          <t>chavarria pep</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>CQmSCTxB</t>
+          <t>jcX738kC</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>caro jose antonio</t>
+          <t>de las sias marco</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>4rn7WXta</t>
+          <t>MVcspA2M</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>de la rosa jose antonio</t>
+          <t>de tomas raul</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>MscufTZE</t>
+          <t>2i6AHS2l</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>diakite moussa</t>
+          <t>diaz pedro</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>d8NunIqn</t>
+          <t>21xu5Zng</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>balboa pelayo</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>80VKCLhl</t>
+          <t>OMUGUEla</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>roger</t>
+          <t>garcia alvaro</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>GI2LU0X1</t>
+          <t>raqVZ405</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>matos jose</t>
+          <t>gumbau gerard</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>IkbbTlTP</t>
+          <t>dln9VIHe</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>mwepu francisco</t>
+          <t>aridane</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>lAD5z2Ck</t>
+          <t>dYFtDut6</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>ontiveros javier</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
+          <t>lopez unai</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>x2AuZhpr</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>palazon isaac</t>
+        </is>
+      </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>INnNHikC</t>
+          <t>QPU3c6Hm</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>bouldini mohamed</t>
+          <t>santiago yellu</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>INnNHikC</t>
+          <t>QPU3c6Hm</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>bouldini mohamed</t>
+          <t>santiago yellu</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>jXCYJBqg</t>
+          <t>lWTa55Ta</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>morales jose</t>
+          <t>nabil aberdin</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>biJcu016</t>
+          <t>viZPCO3c</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>algobia angel</t>
+          <t>alcantara alberto risco</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>biJcu016</t>
+          <t>viZPCO3c</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>algobia angel</t>
+          <t>alcantara alberto risco</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>6s42ZkRu</t>
+          <t>8fpOagmR</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>lozano sergio</t>
+          <t>sola alex</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>O6MiTbze</t>
+          <t>lGNHRlTm</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>de la fuente adrian</t>
+          <t>peter federico</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>O6MiTbze</t>
+          <t>lGNHRlTm</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
-          <t>de la fuente adrian</t>
+          <t>peter federico</t>
         </is>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>x0EyRyUD</t>
+          <t>vP5uwPQf</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>navarro marcos</t>
+          <t>alena carles</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
         <is>
-          <t>lbxUqXq3</t>
+          <t>zHQB5zMa</t>
         </is>
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>romero ivan</t>
+          <t>arambarri mauro</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>lbxUqXq3</t>
+          <t>zHQB5zMa</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
         <is>
-          <t>romero ivan</t>
+          <t>arambarri mauro</t>
         </is>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>pWvRJqSt</t>
+          <t>0WJHh4Qs</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>brugue roger</t>
-        </is>
-      </c>
-      <c r="DL6" t="inlineStr">
-        <is>
-          <t>lAD5z2Ck</t>
-        </is>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>ontiveros javier</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>lAD5z2Ck</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>ontiveros javier</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>OGkTSXOg</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>ocampo brian</t>
-        </is>
-      </c>
+          <t>perez carles</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr"/>
+      <c r="DM6" t="inlineStr"/>
+      <c r="DN6" t="inlineStr"/>
+      <c r="DO6" t="inlineStr"/>
+      <c r="DP6" t="inlineStr"/>
+      <c r="DQ6" t="inlineStr"/>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>0I0RtqEN</t>
+          <t>x2AuZhpr</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
         <is>
-          <t>alejo ivan</t>
+          <t>palazon isaac</t>
         </is>
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>0I0RtqEN</t>
+          <t>x2AuZhpr</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
         <is>
-          <t>alejo ivan</t>
+          <t>palazon isaac</t>
         </is>
       </c>
       <c r="DV6" t="inlineStr">
         <is>
-          <t>CUi1nPXC</t>
+          <t>42E71F4r</t>
         </is>
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>isaac carcelen</t>
+          <t>trejo oscar</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>4rn7WXta</t>
+          <t>OMUGUEla</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>de la rosa jose antonio</t>
+          <t>garcia alvaro</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>4rn7WXta</t>
+          <t>OMUGUEla</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>de la rosa jose antonio</t>
+          <t>garcia alvaro</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>YioE1eTi</t>
+          <t>UiH85aKC</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>sobrino ruben</t>
-        </is>
-      </c>
-      <c r="ED6" t="inlineStr"/>
-      <c r="EE6" t="inlineStr"/>
-      <c r="EF6" t="inlineStr"/>
-      <c r="EG6" t="inlineStr"/>
-      <c r="EH6" t="inlineStr"/>
-      <c r="EI6" t="inlineStr"/>
-      <c r="EJ6" t="inlineStr"/>
-      <c r="EK6" t="inlineStr"/>
-      <c r="EL6" t="inlineStr"/>
-      <c r="EM6" t="inlineStr"/>
-      <c r="EN6" t="inlineStr"/>
-      <c r="EO6" t="inlineStr"/>
-      <c r="EP6" t="inlineStr"/>
-      <c r="EQ6" t="inlineStr"/>
-      <c r="ER6" t="inlineStr"/>
-      <c r="ES6" t="inlineStr"/>
-      <c r="ET6" t="inlineStr"/>
-      <c r="EU6" t="inlineStr"/>
-      <c r="EV6" t="inlineStr"/>
-      <c r="EW6" t="inlineStr"/>
-      <c r="EX6" t="inlineStr"/>
-      <c r="EY6" t="inlineStr"/>
+          <t>de frutos jorge</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>fFlZRkvF</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>camello sergio</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>fFlZRkvF</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>camello sergio</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>M5IbUyg1</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>nketa randy</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>dYFtDut6</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>lopez unai</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>dYFtDut6</t>
+        </is>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>lopez unai</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>zRB7v9IT</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>ciss pathe</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>2i6AHS2l</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>diaz pedro</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
+          <t>2i6AHS2l</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>diaz pedro</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>x8BHeb6c</t>
+        </is>
+      </c>
+      <c r="EU6" t="inlineStr">
+        <is>
+          <t>embarba adri</t>
+        </is>
+      </c>
+      <c r="EV6" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="EW6" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t>Eo8SAMoI</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t>ratiu andrei</t>
+        </is>
+      </c>
       <c r="EZ6" t="inlineStr"/>
       <c r="FA6" t="inlineStr"/>
       <c r="FB6" t="inlineStr"/>
@@ -5270,8 +5254,16 @@
       <c r="FE6" t="inlineStr"/>
       <c r="FF6" t="inlineStr"/>
       <c r="FG6" t="inlineStr"/>
-      <c r="FH6" t="inlineStr"/>
-      <c r="FI6" t="inlineStr"/>
+      <c r="FH6" t="inlineStr">
+        <is>
+          <t>8OTCRUh0</t>
+        </is>
+      </c>
+      <c r="FI6" t="inlineStr">
+        <is>
+          <t>mayoral borja</t>
+        </is>
+      </c>
       <c r="FJ6" t="inlineStr"/>
       <c r="FK6" t="inlineStr"/>
       <c r="FL6" t="inlineStr"/>
@@ -5284,727 +5276,759 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fqgCMogC</t>
+          <t>tEvOrxAE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C4QzBLde</t>
+          <t>0YMlqiSM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ruiz suarez jesus</t>
+          <t>raul</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6ymj1g0J</t>
+          <t>lAgIB16T</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>bunuel aitor</t>
+          <t>alvaro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pxnL1kvb</t>
+          <t>vwcobdxb</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>puric aleksa</t>
+          <t>garcia jon</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hrrTRxpk</t>
+          <t>Y9HNvyBJ</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>naldo</t>
+          <t>martinez ros</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>zy4hmf7N</t>
+          <t>nsEvRNJH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>martinez brais</t>
+          <t>costa jaume</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CWQsr3Ua</t>
+          <t>lAyK4sZ3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>perea luis</t>
+          <t>quiles alberto</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4zJYXfS5</t>
+          <t>zo61BrW3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>manzanara fran</t>
+          <t>marchan rai</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6i10QpDe</t>
+          <t>4CIfCKQ5</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>sene josep</t>
+          <t>rodriguez riki</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Ue7stu5g</t>
+          <t>Y7vZ4xCl</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>borrego christian</t>
+          <t>morcillo jon</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>MojshSPt</t>
+          <t>0zIF6Wg2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>gimenez alvaro</t>
+          <t>fidel</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Uoj9CpGa</t>
+          <t>OCmIC7xi</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>dorrio josue</t>
+          <t>garcia juanma</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>jPxdddKn</t>
+          <t>6uLxUVCT</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>zidane luca</t>
+          <t>dituro matias</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>bygZPyD7</t>
+          <t>U93anmS8</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>sanchez ricard</t>
+          <t>nunez alvaro</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>YiUPEL9t</t>
+          <t>bqApK6mO</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rubio miguel</t>
+          <t>mario gaspar</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2PZuGsll</t>
+          <t>jkeA7fag</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>insua pablo</t>
+          <t>barzic matia</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>n5JmutJP</t>
+          <t>fXlAtRep</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>neva carlos</t>
+          <t>salinas jose</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Qq6pTCV6</t>
+          <t>IylSu6Jk</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>tsitaishvili giorgi</t>
+          <t>febas aleix</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>lSKS5xcF</t>
+          <t>lhUwqUHS</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>hongla martin</t>
+          <t>plano oscar</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>lvN1Z92B</t>
+          <t>2ur060Vt</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>ruiz sergio</t>
+          <t>castro nicolas</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>E77oeEa6</t>
+          <t>fJhTE3Am</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>trigueros manuel</t>
+          <t>fernandez mercau nicolas</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>YiAqdTFb</t>
+          <t>pdMGox1K</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>boye lucas</t>
+          <t>boayar adam</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>YTgDvwwU</t>
+          <t>fRxu5Qk7</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>weissman shon</t>
+          <t>alonso yago</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>QwCBOtxg</t>
+          <t>OAHrCN0T</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>carballo david</t>
+          <t>aguilar lalo</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>t4Qr1TuP</t>
+          <t>tdCq3gMJ</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>delmas julian</t>
+          <t>agus medina</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>txKg0Oob</t>
+          <t>4SRz95Sf</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>sanchez emilio</t>
+          <t>alcedo juan</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0YjKZLrF</t>
+          <t>44AZIBAr</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>vegara aitor</t>
+          <t>gonzalez diego</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>vg348Cm0</t>
+          <t>U3NYWaPL</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>jauregi eneko</t>
+          <t>lazo jose carlos</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2eIBHd23</t>
+          <t>pO1wPsLU</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>lopez alex</t>
+          <t>melendez alejandro</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>lUXUBmdN</t>
+          <t>GtEDHjtF</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>delgado moises</t>
+          <t>moreno marcos</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>M52h5BNQ</t>
+          <t>ziGOv0PB</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>sanz alvaro</t>
+          <t>pacheco antonio</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>Eey3vaud</t>
+          <t>bPy9CrrI</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>vallejo manu</t>
+          <t>ramos mario</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>vuG4kXUC</t>
+          <t>4Aa1KcL9</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>rodriguez yoel</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
+          <t>rivero cristian</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>tt4Mm9ws</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>rueda javier</t>
+        </is>
+      </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>AsdIWlXn</t>
+          <t>tzAxVrkH</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>balde siren</t>
+          <t>alvarez agustin</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0EXj8XA8</t>
+          <t>jJAqqPNm</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>brau miguel</t>
+          <t>badia edgar</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>WEjccUQr</t>
+          <t>65NCnIoE</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>corbeanu theodor</t>
+          <t>castella didac</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>C4WwYAD1</t>
+          <t>SY7HnwqR</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>jozwiak kamil</t>
+          <t>diaby bambo</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>E3BsytEA</t>
+          <t>27MtyaII</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>martinez marc</t>
+          <t>el ghezouani mourad</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>xdh9EmXK</t>
+          <t>v5SjOstp</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>miquel ignasi</t>
+          <t>houary ali</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>6NWnm0oL</t>
+          <t>G4s5mw5N</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>oscar naasei oppong</t>
+          <t>josan</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>UPLFNnyN</t>
+          <t>YNiXFzek</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>saenz ezquerra pablo</t>
+          <t>mendoza rodrigo</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>IVs2nF0f</t>
+          <t>WnnjuJl7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>sanchez ruben</t>
+          <t>rafael leonardo nunez mata</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>AN4BmAif</t>
+          <t>vLfzfoSg</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>uzuni myrto</t>
+          <t>roldan fran</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>QZtXmJ94</t>
+          <t>ERmJI7HF</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>villar gonzalo</t>
+          <t>salvador cristian</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>dWVXsr1m</t>
+          <t>pCDDvlwE</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>williams loic</t>
+          <t>san roman miguel</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>vg348Cm0</t>
+          <t>tt4Mm9ws</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>jauregi eneko</t>
+          <t>rueda javier</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>vg348Cm0</t>
+          <t>tt4Mm9ws</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>jauregi eneko</t>
+          <t>rueda javier</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>MojshSPt</t>
+          <t>lAgIB16T</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>gimenez alvaro</t>
+          <t>alvaro</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>Eey3vaud</t>
+          <t>4SRz95Sf</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>vallejo manu</t>
+          <t>alcedo juan</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>Eey3vaud</t>
+          <t>4SRz95Sf</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>vallejo manu</t>
+          <t>alcedo juan</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Ue7stu5g</t>
+          <t>nsEvRNJH</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>borrego christian</t>
+          <t>costa jaume</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>2eIBHd23</t>
+          <t>U3NYWaPL</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>lopez alex</t>
+          <t>lazo jose carlos</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>2eIBHd23</t>
+          <t>U3NYWaPL</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
-          <t>lopez alex</t>
+          <t>lazo jose carlos</t>
         </is>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>CWQsr3Ua</t>
+          <t>0zIF6Wg2</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>perea luis</t>
+          <t>fidel</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
         <is>
-          <t>lUXUBmdN</t>
+          <t>tdCq3gMJ</t>
         </is>
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>delgado moises</t>
+          <t>agus medina</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>lUXUBmdN</t>
+          <t>tdCq3gMJ</t>
         </is>
       </c>
       <c r="DI7" t="inlineStr">
         <is>
-          <t>delgado moises</t>
+          <t>agus medina</t>
         </is>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>zy4hmf7N</t>
+          <t>Y7vZ4xCl</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>martinez brais</t>
+          <t>morcillo jon</t>
         </is>
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>QZtXmJ94</t>
+          <t>ziGOv0PB</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>villar gonzalo</t>
+          <t>pacheco antonio</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>QZtXmJ94</t>
+          <t>ziGOv0PB</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>villar gonzalo</t>
+          <t>pacheco antonio</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>lvN1Z92B</t>
+          <t>OCmIC7xi</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>ruiz sergio</t>
+          <t>garcia juanma</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>AN4BmAif</t>
+          <t>tzAxVrkH</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
         <is>
-          <t>uzuni myrto</t>
+          <t>alvarez agustin</t>
         </is>
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>AN4BmAif</t>
+          <t>tzAxVrkH</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
         <is>
-          <t>uzuni myrto</t>
+          <t>alvarez agustin</t>
         </is>
       </c>
       <c r="DV7" t="inlineStr">
         <is>
-          <t>YTgDvwwU</t>
+          <t>pdMGox1K</t>
         </is>
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>weissman shon</t>
+          <t>boayar adam</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>UPLFNnyN</t>
+          <t>SY7HnwqR</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>saenz ezquerra pablo</t>
+          <t>diaby bambo</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>UPLFNnyN</t>
+          <t>SY7HnwqR</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>saenz ezquerra pablo</t>
+          <t>diaby bambo</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>Qq6pTCV6</t>
+          <t>bqApK6mO</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>tsitaishvili giorgi</t>
+          <t>mario gaspar</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>xdh9EmXK</t>
+          <t>27MtyaII</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>miquel ignasi</t>
+          <t>el ghezouani mourad</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>xdh9EmXK</t>
+          <t>27MtyaII</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>miquel ignasi</t>
+          <t>el ghezouani mourad</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>YiAqdTFb</t>
+          <t>lhUwqUHS</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
         <is>
-          <t>boye lucas</t>
+          <t>plano oscar</t>
         </is>
       </c>
       <c r="EJ7" t="inlineStr">
         <is>
-          <t>IVs2nF0f</t>
+          <t>G4s5mw5N</t>
         </is>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>sanchez ruben</t>
+          <t>josan</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>IVs2nF0f</t>
+          <t>G4s5mw5N</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
         <is>
-          <t>sanchez ruben</t>
+          <t>josan</t>
         </is>
       </c>
       <c r="EN7" t="inlineStr">
         <is>
-          <t>E77oeEa6</t>
+          <t>IylSu6Jk</t>
         </is>
       </c>
       <c r="EO7" t="inlineStr">
         <is>
-          <t>trigueros manuel</t>
-        </is>
-      </c>
-      <c r="EP7" t="inlineStr"/>
-      <c r="EQ7" t="inlineStr"/>
-      <c r="ER7" t="inlineStr"/>
-      <c r="ES7" t="inlineStr"/>
-      <c r="ET7" t="inlineStr"/>
-      <c r="EU7" t="inlineStr"/>
+          <t>febas aleix</t>
+        </is>
+      </c>
+      <c r="EP7" t="inlineStr">
+        <is>
+          <t>YNiXFzek</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t>mendoza rodrigo</t>
+        </is>
+      </c>
+      <c r="ER7" t="inlineStr">
+        <is>
+          <t>YNiXFzek</t>
+        </is>
+      </c>
+      <c r="ES7" t="inlineStr">
+        <is>
+          <t>mendoza rodrigo</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t>jkeA7fag</t>
+        </is>
+      </c>
+      <c r="EU7" t="inlineStr">
+        <is>
+          <t>barzic matia</t>
+        </is>
+      </c>
       <c r="EV7" t="inlineStr"/>
       <c r="EW7" t="inlineStr"/>
       <c r="EX7" t="inlineStr"/>
@@ -6015,8 +6039,16 @@
       <c r="FC7" t="inlineStr"/>
       <c r="FD7" t="inlineStr"/>
       <c r="FE7" t="inlineStr"/>
-      <c r="FF7" t="inlineStr"/>
-      <c r="FG7" t="inlineStr"/>
+      <c r="FF7" t="inlineStr">
+        <is>
+          <t>p6Ky2D9n</t>
+        </is>
+      </c>
+      <c r="FG7" t="inlineStr">
+        <is>
+          <t>touaizi nabil</t>
+        </is>
+      </c>
       <c r="FH7" t="inlineStr"/>
       <c r="FI7" t="inlineStr"/>
       <c r="FJ7" t="inlineStr"/>
@@ -6031,719 +6063,735 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>QwI4i6hn</t>
+          <t>jBnLKPNO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8pgzl3LK</t>
+          <t>46MITnQj</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yanez ruben</t>
+          <t>herrero alfonso</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pze8wfDU</t>
+          <t>d0cy0VJH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rosas guille</t>
+          <t>puga carlos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>U5hhoskc</t>
+          <t>zoUoVMHM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>curbelo eric</t>
+          <t>pastor alex</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CxiorZwU</t>
+          <t>nqdEHSMq</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>sanchez perez diego</t>
+          <t>galilea einar</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IT0uBnYR</t>
+          <t>WYY1lfvc</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>jose angel cote</t>
+          <t>garcia victor</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2FGMRAob</t>
+          <t>hWytXuuP</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>mendez nacho</t>
+          <t>larrubia david</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>b3fSezor</t>
+          <t>x2yeSVsN</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>martin nacho</t>
+          <t>molina manuel</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>tIyuiCVm</t>
+          <t>Sbu7wJf2</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>olaetxea lander</t>
+          <t>juanpe</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>OAnvSOxm</t>
+          <t>dYhjJbao</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>dubasin jonathan</t>
+          <t>villodres kevin</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2wcI5I5g</t>
+          <t>bwOobz6e</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>otero juan</t>
+          <t>baturina roko</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>UXpIdbF5</t>
+          <t>zJKzpcZ2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>gaspar campos</t>
+          <t>lorenzo guerrero daniel</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0KsY9323</t>
+          <t>8Ui4Uj3f</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>martin dani</t>
+          <t>fernandez raul</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>SQi6oCZp</t>
+          <t>IsnTW9M8</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>garcia victor</t>
+          <t>gutierrez juan</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Aa9VBz0p</t>
+          <t>pGFgjhdA</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>dumic dario</t>
+          <t>postigo sergio</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>O2QaMQfb</t>
+          <t>O2ZB51wk</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>sebastian inigo</t>
+          <t>tomeo pablo</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>OE8ypMGf</t>
+          <t>rBfMulYr</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>mateu marc</t>
+          <t>rincon lumbreras hugo</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>WzjfmHbs</t>
+          <t>d4Ngmj4o</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>chapela ivan</t>
+          <t>lachuer mathis</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>nqRME05G</t>
+          <t>QkiaT3F6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>ortuno diaz sergio</t>
+          <t>tachi</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>nTh80kX9</t>
+          <t>faenCRar</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>timor david</t>
+          <t>gorrotxategi jon</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>SCL2q4g1</t>
+          <t>Iw3Th1z9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>jorquera joel</t>
+          <t>alonso sosa julio</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>dQNNg6WM</t>
+          <t>SSL080TM</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>quintana nacho</t>
+          <t>panichelli joaquin</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6TptgFVm</t>
+          <t>rFSzAZrl</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>bernal alex</t>
+          <t>reina alberto</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>SEPjubn6</t>
+          <t>YsYtFhZ9</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>bernal jesus</t>
+          <t>abaida haitam</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>nu2txHU7</t>
+          <t>tQQcMsFa</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>campuzano victor</t>
+          <t>cordero antonio</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>pC24qs4I</t>
+          <t>CfduQMtk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>garcia pablo</t>
+          <t>dioni</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>hOJjnS7J</t>
+          <t>KEhgZM7C</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>gelabert cesar</t>
+          <t>gabilondo jokin</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4zaBOIZu</t>
+          <t>bqRE7w3c</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>sanchez christian</t>
+          <t>lobete julen</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>ptBouLBj</t>
+          <t>nPtLZN7K</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>kembo yann</t>
+          <t>lopez carlos</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>WG2RVScK</t>
+          <t>x8QCalTA</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>lozano esteban</t>
+          <t>luismi</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>4O78Ls6k</t>
+          <t>vPYNTnQ5</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>martinez iker</t>
+          <t>merino izan</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>jRGPIVqQ</t>
+          <t>4z4O5z5A</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>oyon alex</t>
+          <t>murillo diego</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>lMzBTA7j</t>
+          <t>OlIJGJpI</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>queipo dani</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
+          <t>ochoa aaron</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>vZSESiem</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>sanchez daniel</t>
+        </is>
+      </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>ldjKikv4</t>
+          <t>ClaYwZZA</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>camarasa victor</t>
+          <t>calvo alejandro</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>IsNRKVtG</t>
+          <t>niNE1O1d</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>poloni derick</t>
+          <t>garcia alberto</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>fP50jBbo</t>
+          <t>n7WLyvsf</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>gamez francisco</t>
+          <t>gonzalez victor parada</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>zaB6bU4A</t>
+          <t>dli7hlod</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>dominguez alan godoy</t>
+          <t>homenchenko santiago</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>plLDgpFg</t>
+          <t>E1UCv80p</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>grigore ricardo</t>
+          <t>urko iruretagoiena</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>Mg4L621f</t>
+          <t>v5HKEYQm</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>mackay ian</t>
+          <t>lopez luis</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>fRUEYwjU</t>
+          <t>GnRv5VCn</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>monsalve nacho</t>
+          <t>ortiz asier</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>U3NEfc8n</t>
+          <t>WGvUbvMF</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>montes christian</t>
+          <t>casals</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>ph2LnYwp</t>
+          <t>n77thmF8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>ogbuehi sixtus</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>Agghrm2F</t>
-        </is>
-      </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>ortuno juanto</t>
-        </is>
-      </c>
-      <c r="CJ8" t="inlineStr">
-        <is>
-          <t>AD0qhhph</t>
-        </is>
-      </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>ropero unai</t>
-        </is>
-      </c>
+          <t>rosales diego</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
       <c r="CL8" t="inlineStr"/>
       <c r="CM8" t="inlineStr"/>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>SEPjubn6</t>
+          <t>bqRE7w3c</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>bernal jesus</t>
+          <t>lobete julen</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>SEPjubn6</t>
+          <t>bqRE7w3c</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>bernal jesus</t>
+          <t>lobete julen</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>U5hhoskc</t>
+          <t>dYhjJbao</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>curbelo eric</t>
+          <t>villodres kevin</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>lMzBTA7j</t>
+          <t>OlIJGJpI</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>queipo dani</t>
+          <t>ochoa aaron</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>lMzBTA7j</t>
+          <t>OlIJGJpI</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>queipo dani</t>
+          <t>ochoa aaron</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>b3fSezor</t>
+          <t>Sbu7wJf2</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>martin nacho</t>
+          <t>juanpe</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>nu2txHU7</t>
+          <t>CfduQMtk</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>campuzano victor</t>
+          <t>dioni</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
         <is>
-          <t>nu2txHU7</t>
+          <t>CfduQMtk</t>
         </is>
       </c>
       <c r="DC8" t="inlineStr">
         <is>
-          <t>campuzano victor</t>
+          <t>dioni</t>
         </is>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>UXpIdbF5</t>
+          <t>bwOobz6e</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>gaspar campos</t>
+          <t>baturina roko</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
         <is>
-          <t>hOJjnS7J</t>
+          <t>tQQcMsFa</t>
         </is>
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>gelabert cesar</t>
+          <t>cordero antonio</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>hOJjnS7J</t>
+          <t>tQQcMsFa</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
         <is>
-          <t>gelabert cesar</t>
+          <t>cordero antonio</t>
         </is>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>2wcI5I5g</t>
+          <t>hWytXuuP</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>otero juan</t>
+          <t>larrubia david</t>
         </is>
       </c>
       <c r="DL8" t="inlineStr">
         <is>
-          <t>Agghrm2F</t>
+          <t>YsYtFhZ9</t>
         </is>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>ortuno juanto</t>
+          <t>abaida haitam</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>Agghrm2F</t>
+          <t>YsYtFhZ9</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>ortuno juanto</t>
+          <t>abaida haitam</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>WzjfmHbs</t>
+          <t>bqRE7w3c</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
-          <t>chapela ivan</t>
+          <t>lobete julen</t>
         </is>
       </c>
       <c r="DR8" t="inlineStr">
         <is>
-          <t>U3NEfc8n</t>
+          <t>dli7hlod</t>
         </is>
       </c>
       <c r="DS8" t="inlineStr">
         <is>
-          <t>montes christian</t>
+          <t>homenchenko santiago</t>
         </is>
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>U3NEfc8n</t>
+          <t>dli7hlod</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
         <is>
-          <t>montes christian</t>
+          <t>homenchenko santiago</t>
         </is>
       </c>
       <c r="DV8" t="inlineStr">
         <is>
-          <t>SCL2q4g1</t>
+          <t>QkiaT3F6</t>
         </is>
       </c>
       <c r="DW8" t="inlineStr">
         <is>
-          <t>jorquera joel</t>
+          <t>tachi</t>
         </is>
       </c>
       <c r="DX8" t="inlineStr">
         <is>
-          <t>zaB6bU4A</t>
+          <t>E1UCv80p</t>
         </is>
       </c>
       <c r="DY8" t="inlineStr">
         <is>
-          <t>dominguez alan godoy</t>
+          <t>urko iruretagoiena</t>
         </is>
       </c>
       <c r="DZ8" t="inlineStr">
         <is>
-          <t>zaB6bU4A</t>
+          <t>E1UCv80p</t>
         </is>
       </c>
       <c r="EA8" t="inlineStr">
         <is>
-          <t>dominguez alan godoy</t>
+          <t>urko iruretagoiena</t>
         </is>
       </c>
       <c r="EB8" t="inlineStr">
         <is>
-          <t>6TptgFVm</t>
+          <t>SSL080TM</t>
         </is>
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>bernal alex</t>
+          <t>panichelli joaquin</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>ldjKikv4</t>
+          <t>WGvUbvMF</t>
         </is>
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>camarasa victor</t>
+          <t>casals</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>ldjKikv4</t>
+          <t>WGvUbvMF</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>camarasa victor</t>
+          <t>casals</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>dQNNg6WM</t>
+          <t>faenCRar</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
         <is>
-          <t>quintana nacho</t>
+          <t>gorrotxategi jon</t>
         </is>
       </c>
       <c r="EJ8" t="inlineStr">
         <is>
-          <t>fRUEYwjU</t>
+          <t>n7WLyvsf</t>
         </is>
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>monsalve nacho</t>
+          <t>gonzalez victor parada</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>fRUEYwjU</t>
+          <t>n7WLyvsf</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
         <is>
-          <t>monsalve nacho</t>
+          <t>gonzalez victor parada</t>
         </is>
       </c>
       <c r="EN8" t="inlineStr">
         <is>
-          <t>nqRME05G</t>
+          <t>pGFgjhdA</t>
         </is>
       </c>
       <c r="EO8" t="inlineStr">
         <is>
-          <t>ortuno diaz sergio</t>
-        </is>
-      </c>
-      <c r="EP8" t="inlineStr"/>
-      <c r="EQ8" t="inlineStr"/>
-      <c r="ER8" t="inlineStr"/>
-      <c r="ES8" t="inlineStr"/>
-      <c r="ET8" t="inlineStr"/>
-      <c r="EU8" t="inlineStr"/>
+          <t>postigo sergio</t>
+        </is>
+      </c>
+      <c r="EP8" t="inlineStr">
+        <is>
+          <t>ClaYwZZA</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t>calvo alejandro</t>
+        </is>
+      </c>
+      <c r="ER8" t="inlineStr">
+        <is>
+          <t>ClaYwZZA</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>calvo alejandro</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>d4Ngmj4o</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t>lachuer mathis</t>
+        </is>
+      </c>
       <c r="EV8" t="inlineStr"/>
       <c r="EW8" t="inlineStr"/>
       <c r="EX8" t="inlineStr"/>
@@ -6754,38 +6802,22 @@
       <c r="FC8" t="inlineStr"/>
       <c r="FD8" t="inlineStr"/>
       <c r="FE8" t="inlineStr"/>
-      <c r="FF8" t="inlineStr"/>
-      <c r="FG8" t="inlineStr"/>
-      <c r="FH8" t="inlineStr">
-        <is>
-          <t>4O78Ls6k</t>
-        </is>
-      </c>
-      <c r="FI8" t="inlineStr">
-        <is>
-          <t>martinez iker</t>
-        </is>
-      </c>
-      <c r="FJ8" t="inlineStr">
-        <is>
-          <t>4O78Ls6k</t>
-        </is>
-      </c>
-      <c r="FK8" t="inlineStr">
-        <is>
-          <t>martinez iker</t>
-        </is>
-      </c>
-      <c r="FL8" t="inlineStr">
-        <is>
-          <t>pze8wfDU</t>
-        </is>
-      </c>
-      <c r="FM8" t="inlineStr">
-        <is>
-          <t>rosas guille</t>
-        </is>
-      </c>
+      <c r="FF8" t="inlineStr">
+        <is>
+          <t>MqP5Tzz4</t>
+        </is>
+      </c>
+      <c r="FG8" t="inlineStr">
+        <is>
+          <t>sangalli luca</t>
+        </is>
+      </c>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+      <c r="FL8" t="inlineStr"/>
+      <c r="FM8" t="inlineStr"/>
       <c r="FN8" t="inlineStr"/>
       <c r="FO8" t="inlineStr"/>
       <c r="FP8" t="inlineStr"/>
@@ -6794,727 +6826,727 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jPRgZOxI</t>
+          <t>QHtUvT8t</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lCAHqdrp</t>
+          <t>63syan4K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jimenez dani</t>
+          <t>nadal tomeu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nyxEi6on</t>
+          <t>Of2PA2Td</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>abad jose toni</t>
+          <t>mellot jeremy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GCW1cIvp</t>
+          <t>AupfG8yP</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>blasco jeremy</t>
+          <t>juande</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>fsjkK41s</t>
+          <t>MHMBJsTD</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>pulido jorge</t>
+          <t>leon jose</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>hG15cPG8</t>
+          <t>MiNhvPQS</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>vilarrasa ignasi</t>
+          <t>medrano fernando</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>bca3igNk</t>
+          <t>zXy8vKe2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>sielva oscar</t>
+          <t>cruz luismi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>WKZZtJEE</t>
+          <t>tpszulN9</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>perez mateo javier</t>
+          <t>diarra youssouf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>riikyhEG</t>
+          <t>G87TNXSP</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>soko patrick</t>
+          <t>gonzalez sergio</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>GE65dlKG</t>
+          <t>ngNLVMtM</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>mier javi</t>
+          <t>rubio waldo</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>fmp1pdv1</t>
+          <t>MZYiJsf5</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>munoz joaquin</t>
+          <t>rodriguez angel</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>rF4Be8Yj</t>
+          <t>vmSOV0qD</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>enrich sergio</t>
+          <t>mesa maikel</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>rX4BCOC6</t>
+          <t>lfgji9jR</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>parreno german</t>
+          <t>maximiano luis</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>UVspkTsq</t>
+          <t>lEgtMYw4</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>petxa alex</t>
+          <t>pozo alejandro</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>4b3CXnY3</t>
+          <t>0KsyLPE4</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>vazquez perez pablo</t>
+          <t>chumi</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>I9kZL6aT</t>
+          <t>Eks5aVRG</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>martinez pablo</t>
+          <t>kaiky</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>QHP29Y9q</t>
+          <t>hrUwhqn3</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>navarro ximo</t>
+          <t>centelles alex</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>n1QEm2xS</t>
+          <t>pCJBsskE</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>mella david</t>
+          <t>gonzalez edgar</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>jeHmEmdJ</t>
+          <t>nN06Zcrh</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>villares diego</t>
+          <t>melero gonzalo</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>WpVDmC22</t>
+          <t>OMxL6tQB</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>jurado jose angel</t>
+          <t>puigmal arnau</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>4zhDcXCG</t>
+          <t>GIzJfhLr</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>hernandez yeremay</t>
+          <t>arribas sergio</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>pEIRfpB9</t>
+          <t>U1OOFFBl</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>soriano m</t>
+          <t>ribaudo nico</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>YsCMvAvd</t>
+          <t>fV4fAvB8</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>perez lucas</t>
+          <t>suarez luis</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>j7UjY8ZD</t>
+          <t>YDX3HtAo</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>anglada hugo</t>
+          <t>gonzalez ruben</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>hvwCqMdo</t>
+          <t>bXfFubxl</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>arguigue ayman</t>
+          <t>bodiger yann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0faIxHq6</t>
+          <t>WOsowK7D</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>armero sergi</t>
+          <t>cantero alejandro</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>plM3yHRN</t>
+          <t>th9dk6j8</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>fita alex</t>
+          <t>montanez carrasco salvador</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>OK9jn5Tm</t>
+          <t>zwpagAwR</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>gonzalez cabanes diego</t>
+          <t>corredera alex</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8QF1BiDA</t>
+          <t>zc8vwd36</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>hernandez javier</t>
+          <t>gallego enric</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>I3ZFJ978</t>
+          <t>KfbbZ1xQ</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>kortajarena iker</t>
+          <t>gaya josep</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>EatllJ9F</t>
+          <t>MeRdZHGT</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>pereda adrian</t>
+          <t>guerrero adrian</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>WxeiCXE4</t>
+          <t>4OJxMhNq</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>perez juan</t>
+          <t>manjam alassan</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>vkZyDCe0</t>
+          <t>UqQAKe7t</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>pulido ruben</t>
+          <t>david rodriguez ramos</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>vu4cWvkc</t>
+          <t>nHp3CHac</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>valentin gerard</t>
+          <t>senhadji yanis</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>21SuW5Vq</t>
+          <t>8YnlOgwC</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>ivan barbero</t>
+          <t>baba iddrisu</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>4AnCE6ed</t>
+          <t>0M5sG7Bk</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>barcia dani</t>
+          <t>fettal rachad</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>rBnegnOq</t>
+          <t>nJ9VW6i9</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>rodriguez luis</t>
+          <t>gomez valen</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>hM8jpBm7</t>
+          <t>lh0DDoRr</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>davo</t>
+          <t>guedes guilherme</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>UPakvWjd</t>
+          <t>fDlwwgkH</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>garcia pablo</t>
+          <t>iribarne bruno</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>OtuX2bMG</t>
+          <t>8xxQPuzJ</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>leite helton</t>
+          <t>langa bruno alberto</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>KlZcipw3</t>
+          <t>nHPmbQaR</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>lopez ruben</t>
+          <t>lopy dion</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>pYKOx7d0</t>
+          <t>Y9vWlK55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>mfulu omenuke</t>
+          <t>milovanovic marko</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>z3xcnF35</t>
+          <t>EJs3SlPl</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>obrador rafael</t>
+          <t>fernando</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>xfFOyHXH</t>
+          <t>j9EcJFsj</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>puerto eric</t>
+          <t>montes cesar</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0Ca5CLYL</t>
+          <t>df21B0le</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>rama hugo</t>
+          <t>pena marcos</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>U1vHUa98</t>
+          <t>jDh6SEKj</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>sanchez jaime</t>
+          <t>radovanovic aleksandar</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>I3ZFJ978</t>
+          <t>UqQAKe7t</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>kortajarena iker</t>
+          <t>david rodriguez ramos</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>I3ZFJ978</t>
+          <t>UqQAKe7t</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>kortajarena iker</t>
+          <t>david rodriguez ramos</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>GE65dlKG</t>
+          <t>MiNhvPQS</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>mier javi</t>
+          <t>medrano fernando</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>vu4cWvkc</t>
+          <t>bXfFubxl</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>valentin gerard</t>
+          <t>bodiger yann</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>vu4cWvkc</t>
+          <t>bXfFubxl</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>valentin gerard</t>
+          <t>bodiger yann</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>riikyhEG</t>
+          <t>G87TNXSP</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>soko patrick</t>
+          <t>gonzalez sergio</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>OWvS7e5J</t>
+          <t>YDX3HtAo</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>vallejo hugo</t>
+          <t>gonzalez ruben</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>OWvS7e5J</t>
+          <t>YDX3HtAo</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
         <is>
-          <t>vallejo hugo</t>
+          <t>gonzalez ruben</t>
         </is>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>fmp1pdv1</t>
+          <t>tpszulN9</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>munoz joaquin</t>
+          <t>diarra youssouf</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
         <is>
-          <t>vkZyDCe0</t>
+          <t>WOsowK7D</t>
         </is>
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>pulido ruben</t>
+          <t>cantero alejandro</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>vkZyDCe0</t>
+          <t>WOsowK7D</t>
         </is>
       </c>
       <c r="DI9" t="inlineStr">
         <is>
-          <t>pulido ruben</t>
+          <t>cantero alejandro</t>
         </is>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>nyxEi6on</t>
+          <t>vmSOV0qD</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>abad jose toni</t>
+          <t>mesa maikel</t>
         </is>
       </c>
       <c r="DL9" t="inlineStr">
         <is>
-          <t>21SuW5Vq</t>
+          <t>zwpagAwR</t>
         </is>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>ivan barbero</t>
+          <t>corredera alex</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>21SuW5Vq</t>
+          <t>zwpagAwR</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>ivan barbero</t>
+          <t>corredera alex</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>UVspkTsq</t>
+          <t>MZYiJsf5</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
         <is>
-          <t>petxa alex</t>
+          <t>rodriguez angel</t>
         </is>
       </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>pYKOx7d0</t>
+          <t>nHPmbQaR</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
         <is>
-          <t>mfulu omenuke</t>
+          <t>lopy dion</t>
         </is>
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>pYKOx7d0</t>
+          <t>nHPmbQaR</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
         <is>
-          <t>mfulu omenuke</t>
+          <t>lopy dion</t>
         </is>
       </c>
       <c r="DV9" t="inlineStr">
         <is>
-          <t>WpVDmC22</t>
+          <t>Eks5aVRG</t>
         </is>
       </c>
       <c r="DW9" t="inlineStr">
         <is>
-          <t>jurado jose angel</t>
+          <t>kaiky</t>
         </is>
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>hM8jpBm7</t>
+          <t>8xxQPuzJ</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>davo</t>
+          <t>langa bruno alberto</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>hM8jpBm7</t>
+          <t>8xxQPuzJ</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>davo</t>
+          <t>langa bruno alberto</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>n1QEm2xS</t>
+          <t>OMxL6tQB</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>mella david</t>
+          <t>puigmal arnau</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
-          <t>0Ca5CLYL</t>
+          <t>8YnlOgwC</t>
         </is>
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>rama hugo</t>
+          <t>baba iddrisu</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>0Ca5CLYL</t>
+          <t>8YnlOgwC</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>rama hugo</t>
+          <t>baba iddrisu</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>4zhDcXCG</t>
+          <t>nN06Zcrh</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
-          <t>hernandez yeremay</t>
+          <t>melero gonzalo</t>
         </is>
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>rBnegnOq</t>
+          <t>nJ9VW6i9</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>rodriguez luis</t>
+          <t>gomez valen</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>rBnegnOq</t>
+          <t>nJ9VW6i9</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>rodriguez luis</t>
+          <t>gomez valen</t>
         </is>
       </c>
       <c r="EN9" t="inlineStr">
         <is>
-          <t>pEIRfpB9</t>
+          <t>GIzJfhLr</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr">
         <is>
-          <t>soriano m</t>
+          <t>arribas sergio</t>
         </is>
       </c>
       <c r="EP9" t="inlineStr"/>
@@ -7533,821 +7565,26 @@
       <c r="FC9" t="inlineStr"/>
       <c r="FD9" t="inlineStr"/>
       <c r="FE9" t="inlineStr"/>
-      <c r="FF9" t="inlineStr"/>
-      <c r="FG9" t="inlineStr"/>
-      <c r="FH9" t="inlineStr">
-        <is>
-          <t>hvwCqMdo</t>
-        </is>
-      </c>
-      <c r="FI9" t="inlineStr">
-        <is>
-          <t>arguigue ayman</t>
-        </is>
-      </c>
-      <c r="FJ9" t="inlineStr">
-        <is>
-          <t>hvwCqMdo</t>
-        </is>
-      </c>
-      <c r="FK9" t="inlineStr">
-        <is>
-          <t>arguigue ayman</t>
-        </is>
-      </c>
-      <c r="FL9" t="inlineStr">
-        <is>
-          <t>rF4Be8Yj</t>
-        </is>
-      </c>
-      <c r="FM9" t="inlineStr">
-        <is>
-          <t>enrich sergio</t>
-        </is>
-      </c>
-      <c r="FN9" t="inlineStr">
-        <is>
-          <t>OWvS7e5J</t>
-        </is>
-      </c>
-      <c r="FO9" t="inlineStr">
-        <is>
-          <t>vallejo hugo</t>
-        </is>
-      </c>
+      <c r="FF9" t="inlineStr">
+        <is>
+          <t>t4ZOn0H3</t>
+        </is>
+      </c>
+      <c r="FG9" t="inlineStr">
+        <is>
+          <t>teto</t>
+        </is>
+      </c>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="inlineStr"/>
+      <c r="FN9" t="inlineStr"/>
+      <c r="FO9" t="inlineStr"/>
       <c r="FP9" t="inlineStr"/>
       <c r="FQ9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OxQ1X27U</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>IPkF6s5H</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ezkieta jokin</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>hCaJleT0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>michelin clement</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>fogIyhDp</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>hernando manu</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>vwcbjRMJ</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>montero francisco</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>YVGq2FQ6</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>garcia saul</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>jm5x4JNf</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>vencedor unai</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>OAI6QtxN</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>aldasoro aritz</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>jm3RjZt2</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>martin andres</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>jDKBJJ9H</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>pablo</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>xj86hQ3C</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>vicente inigo</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0AlVvNwC</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>arana gomez juan carlos</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>U97akWoJ</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>magunagoitia jonmi</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>tY9B9R8R</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>corpas jose</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>6FZTZse6</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>carrillo alvaro</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>I5wpPbNu</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>arbilla anaitz</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>jZrmTaWb</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>arrillaga hodei</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>WANBOspq</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>alvarez sergio</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>SYXL5EpQ</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>pereira matheus</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>r9rn0Wtd</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>merquelanz martin</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>MNbqVtWt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>pascual jorge</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>SMRPNG5i</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>puertas antonio</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>Y7dM1nsL</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>jon bautista orgilles</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>vwj8fVTt</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>camara suleiman</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>88fszyHn</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>carrascal marco</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>lAOXx9U7</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>castro urdin javier</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>nDpCW7DC</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>garcia mario</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>Ysb0B298</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>junior lago</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>xChow1PH</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>karrikaburu jon</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>tQ5ht3jI</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>moreno pol</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>v1Ti8Jup</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>parera miquel</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>Egjuac7e</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>sainz maza inigo</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>hCp3VZOF</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>salinas jorge</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>IuIj7V6O</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>sangalli marco</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>MNbQbqQ4</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>alday iker</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>xOUihsv0</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>carrasco oscar</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>Kjc7Gst2</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>chema</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>xfS51jmd</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>cubero sergio</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>hY8G1T3f</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>daniel fuzato</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>r1yFv4o6</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>guruzeta jon</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>4tgH7UUS</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>gutierrez cristian</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>6Rvb9XRN</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>madariaga ander</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>f1i71kYp</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>nolaskoain peru</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>OOPqZM2P</t>
-        </is>
-      </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>rahmani yanis</t>
-        </is>
-      </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>lUkrLco1</t>
-        </is>
-      </c>
-      <c r="CK10" t="inlineStr">
-        <is>
-          <t>slavy</t>
-        </is>
-      </c>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
-      <c r="CN10" t="inlineStr">
-        <is>
-          <t>Egjuac7e</t>
-        </is>
-      </c>
-      <c r="CO10" t="inlineStr">
-        <is>
-          <t>sainz maza inigo</t>
-        </is>
-      </c>
-      <c r="CP10" t="inlineStr">
-        <is>
-          <t>Egjuac7e</t>
-        </is>
-      </c>
-      <c r="CQ10" t="inlineStr">
-        <is>
-          <t>sainz maza inigo</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>jm5x4JNf</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>vencedor unai</t>
-        </is>
-      </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>IuIj7V6O</t>
-        </is>
-      </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>sangalli marco</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>IuIj7V6O</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>sangalli marco</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>hCaJleT0</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>michelin clement</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>xChow1PH</t>
-        </is>
-      </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>karrikaburu jon</t>
-        </is>
-      </c>
-      <c r="DB10" t="inlineStr">
-        <is>
-          <t>xChow1PH</t>
-        </is>
-      </c>
-      <c r="DC10" t="inlineStr">
-        <is>
-          <t>karrikaburu jon</t>
-        </is>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>jDKBJJ9H</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>pablo</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>vwj8fVTt</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>camara suleiman</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>vwj8fVTt</t>
-        </is>
-      </c>
-      <c r="DI10" t="inlineStr">
-        <is>
-          <t>camara suleiman</t>
-        </is>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>OAI6QtxN</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>aldasoro aritz</t>
-        </is>
-      </c>
-      <c r="DL10" t="inlineStr">
-        <is>
-          <t>6Rvb9XRN</t>
-        </is>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>madariaga ander</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>6Rvb9XRN</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>madariaga ander</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>r9rn0Wtd</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>merquelanz martin</t>
-        </is>
-      </c>
-      <c r="DR10" t="inlineStr">
-        <is>
-          <t>r1yFv4o6</t>
-        </is>
-      </c>
-      <c r="DS10" t="inlineStr">
-        <is>
-          <t>guruzeta jon</t>
-        </is>
-      </c>
-      <c r="DT10" t="inlineStr">
-        <is>
-          <t>r1yFv4o6</t>
-        </is>
-      </c>
-      <c r="DU10" t="inlineStr">
-        <is>
-          <t>guruzeta jon</t>
-        </is>
-      </c>
-      <c r="DV10" t="inlineStr">
-        <is>
-          <t>MNbqVtWt</t>
-        </is>
-      </c>
-      <c r="DW10" t="inlineStr">
-        <is>
-          <t>pascual jorge</t>
-        </is>
-      </c>
-      <c r="DX10" t="inlineStr">
-        <is>
-          <t>xfS51jmd</t>
-        </is>
-      </c>
-      <c r="DY10" t="inlineStr">
-        <is>
-          <t>cubero sergio</t>
-        </is>
-      </c>
-      <c r="DZ10" t="inlineStr">
-        <is>
-          <t>xfS51jmd</t>
-        </is>
-      </c>
-      <c r="EA10" t="inlineStr">
-        <is>
-          <t>cubero sergio</t>
-        </is>
-      </c>
-      <c r="EB10" t="inlineStr">
-        <is>
-          <t>tY9B9R8R</t>
-        </is>
-      </c>
-      <c r="EC10" t="inlineStr">
-        <is>
-          <t>corpas jose</t>
-        </is>
-      </c>
-      <c r="ED10" t="inlineStr">
-        <is>
-          <t>f1i71kYp</t>
-        </is>
-      </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>nolaskoain peru</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>f1i71kYp</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
-        <is>
-          <t>nolaskoain peru</t>
-        </is>
-      </c>
-      <c r="EH10" t="inlineStr">
-        <is>
-          <t>SYXL5EpQ</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr">
-        <is>
-          <t>pereira matheus</t>
-        </is>
-      </c>
-      <c r="EJ10" t="inlineStr">
-        <is>
-          <t>4tgH7UUS</t>
-        </is>
-      </c>
-      <c r="EK10" t="inlineStr">
-        <is>
-          <t>gutierrez cristian</t>
-        </is>
-      </c>
-      <c r="EL10" t="inlineStr">
-        <is>
-          <t>4tgH7UUS</t>
-        </is>
-      </c>
-      <c r="EM10" t="inlineStr">
-        <is>
-          <t>gutierrez cristian</t>
-        </is>
-      </c>
-      <c r="EN10" t="inlineStr">
-        <is>
-          <t>SMRPNG5i</t>
-        </is>
-      </c>
-      <c r="EO10" t="inlineStr">
-        <is>
-          <t>puertas antonio</t>
-        </is>
-      </c>
-      <c r="EP10" t="inlineStr"/>
-      <c r="EQ10" t="inlineStr"/>
-      <c r="ER10" t="inlineStr"/>
-      <c r="ES10" t="inlineStr"/>
-      <c r="ET10" t="inlineStr"/>
-      <c r="EU10" t="inlineStr"/>
-      <c r="EV10" t="inlineStr"/>
-      <c r="EW10" t="inlineStr"/>
-      <c r="EX10" t="inlineStr"/>
-      <c r="EY10" t="inlineStr"/>
-      <c r="EZ10" t="inlineStr"/>
-      <c r="FA10" t="inlineStr"/>
-      <c r="FB10" t="inlineStr"/>
-      <c r="FC10" t="inlineStr"/>
-      <c r="FD10" t="inlineStr"/>
-      <c r="FE10" t="inlineStr"/>
-      <c r="FF10" t="inlineStr"/>
-      <c r="FG10" t="inlineStr"/>
-      <c r="FH10" t="inlineStr">
-        <is>
-          <t>nDpCW7DC</t>
-        </is>
-      </c>
-      <c r="FI10" t="inlineStr">
-        <is>
-          <t>garcia mario</t>
-        </is>
-      </c>
-      <c r="FJ10" t="inlineStr">
-        <is>
-          <t>nDpCW7DC</t>
-        </is>
-      </c>
-      <c r="FK10" t="inlineStr">
-        <is>
-          <t>garcia mario</t>
-        </is>
-      </c>
-      <c r="FL10" t="inlineStr">
-        <is>
-          <t>vwcbjRMJ</t>
-        </is>
-      </c>
-      <c r="FM10" t="inlineStr">
-        <is>
-          <t>montero francisco</t>
-        </is>
-      </c>
-      <c r="FN10" t="inlineStr"/>
-      <c r="FO10" t="inlineStr"/>
-      <c r="FP10" t="inlineStr"/>
-      <c r="FQ10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ9"/>
+  <dimension ref="A1:FI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,4491 +761,4419 @@
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_home_12</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_12</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_away_1</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_1</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_2</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_2</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_3</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_3</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_4</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_4</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_5</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_5</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_6</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_6</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_7</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_7</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_8</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_8</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_9</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_9</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_10</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_10</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_11</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_11</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_12</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_12</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_home_12</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_home_12</t>
-        </is>
-      </c>
       <c r="FH1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_1</t>
+          <t>id_player_miss_home_3</t>
         </is>
       </c>
       <c r="FI1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
           <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>lMLBCMLN</t>
+          <t>pIgzAKRr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sivera antonio</t>
+          <t>roman leonardo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WAG63va3</t>
+          <t>KvHXl88g</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tenaglia nahuel</t>
+          <t>maffeo pablo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gp35on1c</t>
+          <t>pbb8dhGG</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>abqar abdelkebir</t>
+          <t>valjent martin</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>h4BWTxSF</t>
+          <t>p8RSvp74</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>sedlar aleksandar</t>
+          <t>raillo antonio</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>b3mITAJa</t>
+          <t>drRlRNNC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>sanchez manuel</t>
+          <t>mojica johan</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>bRBNu8DM</t>
+          <t>AXPRNqQn</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>vicente carlos</t>
+          <t>costa samuel</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>hMjEwTOg</t>
+          <t>nerrfVfR</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>guevara ander</t>
+          <t>morlanes manu</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MTG8l3Dq</t>
+          <t>On7NYLWr</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>blanco antonio</t>
+          <t>darder sergi</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>zZJGkBEQ</t>
+          <t>pSceH9EI</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>conechny tomas</t>
+          <t>sanchez antonio</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Kneifk5H</t>
+          <t>CjwNDgqi</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>stoichkov</t>
+          <t>muriqi vedat</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>GfoivbEm</t>
+          <t>vNpXFtuQ</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>kike</t>
+          <t>larin cyle</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>GErUsMSq</t>
+          <t>UJ9btoDi</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>silva rui</t>
+          <t>nyland orjan</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>vFNb1rQ5</t>
+          <t>dE2MbgQ4</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>sabaly youssouf</t>
+          <t>carmona jose angel</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>8K4WA9Gh</t>
+          <t>YgxuEfvL</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>bartra marc</t>
+          <t>bade loic</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2XJ8qBI1</t>
+          <t>SKLFEpf6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>llorente diego</t>
+          <t>gudelj nemanja</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8EqrjqCF</t>
+          <t>t4j4NUO8</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>rodriguez ricardo</t>
+          <t>pedrosa adria</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>jmbMzvQa</t>
+          <t>tUNr1qOE</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>carvalho william</t>
+          <t>sow djibril</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0SJZRycC</t>
+          <t>fefkCPrH</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>roca marc</t>
+          <t>lokonga sambi</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>CfghB0gf</t>
+          <t>hSbvVwW7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>fornals pablo</t>
+          <t>niguez saul</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>xG1QmowQ</t>
+          <t>08a9jhm9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>fekir nabil</t>
+          <t>lukebakio dodi</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0vLnUdTa</t>
+          <t>dIaES012</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>juanmi</t>
+          <t>iheanacho kelechi</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>jLOnYYdH</t>
+          <t>8zvngfOe</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>aitor rubal</t>
+          <t>ejuke chidera</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>K4275W3e</t>
+          <t>lrscbe6I</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>benavidez carlos</t>
+          <t>asano takuma</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>Op7pPJv2</t>
+          <t>ABXxQRR6</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>diarra moussa</t>
+          <t>arias copete jose manuel</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>WhV8JXPD</t>
+          <t>xUwdHPXa</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>guridi jon</t>
+          <t>domenech marc</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>dnvBgOsP</t>
+          <t>ID9k7lap</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>martin carlos</t>
+          <t>greif dominik</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>KtWwVS3K</t>
+          <t>hCPqc747</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>novoa ramos hugo</t>
+          <t>lato toni</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>AcqRuf0b</t>
+          <t>bkeWsRZc</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>owono jesus</t>
+          <t>luna daniel</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>baSksbWn</t>
+          <t>vJSVZFpR</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>pica adrian</t>
+          <t>mascarell omar</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0Oxc76wG</t>
+          <t>lx119mnI</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>rebbach abderrahmane</t>
+          <t>cuellar ivan</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>MLlf8c4E</t>
+          <t>zB1s0lKl</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>rodriguez adrian</t>
+          <t>prats abdon</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>r9HfBE6F</t>
+          <t>n7jmYVFc</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>romero luka</t>
+          <t>rodriguez daniel</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>C4Qtc3iO</t>
+          <t>feNCiQzT</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>villalibre asier</t>
+          <t>salas jan</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>CEm70uDg</t>
+          <t>fToJY0qQ</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>adrian</t>
+          <t>van der heyden siebe</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>4rf7A6PR</t>
+          <t>bmJjJR1B</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>altimira sergi</t>
+          <t>agoume lucien</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>UchGKR53</t>
+          <t>tfywn0Ad</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>chimy avila</t>
+          <t>fernandez alvaro</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>pxq49QlK</t>
+          <t>SzbPY3Ma</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>bellerin hector</t>
+          <t>flores alberto</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>rZziaoTk</t>
+          <t>zRYlzwwb</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>diao assane</t>
+          <t>idumbo muzambo stanis</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>YRiVcQ3T</t>
+          <t>OOFwBfsT</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>ez abde</t>
+          <t>marcao</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>CCyECQae</t>
+          <t>hWt5ZIrn</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>gonzalez manu</t>
+          <t>navas jesus</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>v5Xtt1xa</t>
+          <t>zHxpGqc8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>johnny cardoso</t>
+          <t>kouassi nianzou</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>jmkzeFcs</t>
+          <t>GOkrxtHi</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>losada iker</t>
+          <t>peque</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>dpUJtnsM</t>
+          <t>OK0Lcg44</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>natan</t>
+          <t>romero isaac</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>l6FMek3E</t>
+          <t>6uf4Y1d2</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>perraud romain</t>
+          <t>rooms kike</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>Ik7xMDsb</t>
+          <t>CtN0gVgf</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>rodri</t>
+          <t>sanchez juanlu</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>r9HfBE6F</t>
+          <t>n7jmYVFc</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>romero luka</t>
+          <t>rodriguez daniel</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>r9HfBE6F</t>
+          <t>n7jmYVFc</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>romero luka</t>
+          <t>rodriguez daniel</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>zZJGkBEQ</t>
+          <t>pSceH9EI</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>conechny tomas</t>
+          <t>sanchez antonio</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>dnvBgOsP</t>
+          <t>lrscbe6I</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>martin carlos</t>
+          <t>asano takuma</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>dnvBgOsP</t>
+          <t>lrscbe6I</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>martin carlos</t>
+          <t>asano takuma</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Kneifk5H</t>
+          <t>vNpXFtuQ</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>stoichkov</t>
+          <t>larin cyle</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>K4275W3e</t>
+          <t>vJSVZFpR</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>benavidez carlos</t>
+          <t>mascarell omar</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>K4275W3e</t>
+          <t>vJSVZFpR</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>benavidez carlos</t>
+          <t>mascarell omar</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>hMjEwTOg</t>
+          <t>nerrfVfR</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>guevara ander</t>
+          <t>morlanes manu</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>WhV8JXPD</t>
+          <t>xUwdHPXa</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>guridi jon</t>
+          <t>domenech marc</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>WhV8JXPD</t>
+          <t>xUwdHPXa</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>guridi jon</t>
+          <t>domenech marc</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>GfoivbEm</t>
+          <t>On7NYLWr</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>kike</t>
+          <t>darder sergi</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>Op7pPJv2</t>
+          <t>zB1s0lKl</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>diarra moussa</t>
+          <t>prats abdon</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>Op7pPJv2</t>
+          <t>zB1s0lKl</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>diarra moussa</t>
+          <t>prats abdon</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>bRBNu8DM</t>
+          <t>CjwNDgqi</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>vicente carlos</t>
+          <t>muriqi vedat</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>l6FMek3E</t>
+          <t>OK0Lcg44</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>perraud romain</t>
+          <t>romero isaac</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>l6FMek3E</t>
+          <t>OK0Lcg44</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>perraud romain</t>
+          <t>romero isaac</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>8EqrjqCF</t>
+          <t>dIaES012</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>rodriguez ricardo</t>
+          <t>iheanacho kelechi</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>YRiVcQ3T</t>
+          <t>CtN0gVgf</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>ez abde</t>
+          <t>sanchez juanlu</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>YRiVcQ3T</t>
+          <t>CtN0gVgf</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>ez abde</t>
+          <t>sanchez juanlu</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>0vLnUdTa</t>
+          <t>fefkCPrH</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>juanmi</t>
+          <t>lokonga sambi</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>UchGKR53</t>
+          <t>hWt5ZIrn</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>chimy avila</t>
+          <t>navas jesus</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>UchGKR53</t>
+          <t>hWt5ZIrn</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>chimy avila</t>
+          <t>navas jesus</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>jLOnYYdH</t>
+          <t>08a9jhm9</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>aitor rubal</t>
+          <t>lukebakio dodi</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>Ik7xMDsb</t>
+          <t>OOFwBfsT</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>rodri</t>
+          <t>marcao</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>Ik7xMDsb</t>
+          <t>OOFwBfsT</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>rodri</t>
+          <t>marcao</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>CfghB0gf</t>
+          <t>SKLFEpf6</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>fornals pablo</t>
+          <t>gudelj nemanja</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>dpUJtnsM</t>
+          <t>bmJjJR1B</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>natan</t>
+          <t>agoume lucien</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>dpUJtnsM</t>
+          <t>bmJjJR1B</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>natan</t>
+          <t>agoume lucien</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>8K4WA9Gh</t>
+          <t>8zvngfOe</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>bartra marc</t>
+          <t>ejuke chidera</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>vZ3QJXBc</t>
+          <t>Ew10Xoy6</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>bakambu cedric</t>
+          <t>llabres javier</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>f7TcxoGd</t>
+          <t>jRBXx0H4</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>garreta felix marti</t>
+          <t>morey mateu</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>ULLmpdEb</t>
+          <t>rN9tdN16</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>isco</t>
+          <t>montiel gonzalo</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>by4YfNNK</t>
+          <t>2s2ATpKI</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>mendy nobel</t>
+          <t>ocampos lucas</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>SEXE75E5</t>
+          <t>Aexbrioc</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>vieites francisco</t>
+          <t>suso</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr"/>
       <c r="FG2" t="inlineStr"/>
       <c r="FH2" t="inlineStr"/>
       <c r="FI2" t="inlineStr"/>
-      <c r="FJ2" t="inlineStr"/>
-      <c r="FK2" t="inlineStr"/>
-      <c r="FL2" t="inlineStr"/>
-      <c r="FM2" t="inlineStr"/>
-      <c r="FN2" t="inlineStr"/>
-      <c r="FO2" t="inlineStr"/>
-      <c r="FP2" t="inlineStr"/>
-      <c r="FQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tAaD36mt</t>
+          <t>GMOMNJbs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>soriano juan</t>
+          <t>conde diego</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6B7YK1Tu</t>
+          <t>ryjofHOu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rosier valentin</t>
+          <t>kiko</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UkvndELE</t>
+          <t>AkMslDtA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>arambarri aritz</t>
+          <t>albiol raul</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6Nmx29Pj</t>
+          <t>G8VcNrxU</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>gonzalez sergio</t>
+          <t>bailly eric</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6NFqRQVg</t>
+          <t>vVh7yy15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>hernandez javi</t>
+          <t>cardona sergi</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OAPggVhT</t>
+          <t>8fnHDvMe</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>brasanac darko</t>
+          <t>santos yeremi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SbettZSO</t>
+          <t>KK4TPIBj</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>neyou noupa yvan</t>
+          <t>comesana santi</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2cPwbh8J</t>
+          <t>z7YvfLZ8</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>raba daniel</t>
+          <t>parejo daniel</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>E3s5eF5I</t>
+          <t>bmeQTB92</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>cisse seydouba</t>
+          <t>baena alex</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>WWNny3e7</t>
+          <t>UwfDD083</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>rodriguez oscar</t>
+          <t>moreno gerard</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>6yaQrJGS</t>
+          <t>tYV4tvqr</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>de la fuente miguel</t>
+          <t>groeneveld arnaut</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>25zBQ1q4</t>
+          <t>IRro97ls</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>cillessen jasper</t>
+          <t>villar ivan</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>fBI7cV4b</t>
+          <t>8bvxeNAG</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>alex suarez</t>
+          <t>manquillo javier</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>AerDGNDO</t>
+          <t>ptNHGRiJ</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>mckenna scott</t>
+          <t>starfelt carl</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Cz3awDFR</t>
+          <t>ITqxsbsR</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>marmol mika</t>
+          <t>jailson</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>xlaNl83K</t>
+          <t>rHUdQZPd</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>munoz alex</t>
+          <t>carreira sergio</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>lQJaaIBC</t>
+          <t>MoAntFV8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>munoz javier</t>
+          <t>kourouma moriba</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>OKNQawg3</t>
+          <t>IR1ghK3I</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>kirian</t>
+          <t>rodriguez damian</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>SjTBQO7b</t>
+          <t>YkHSwt2b</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>park marvin</t>
+          <t>mingueza oscar</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>b5g6gWjn</t>
+          <t>IXim7pWh</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>moleiro alberto</t>
+          <t>gonzalez alfonso</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>fapXP9VS</t>
+          <t>n9uHpbM8</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>ramirez sandro</t>
+          <t>bamba jonathan</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>rNFSg6i4</t>
+          <t>0vQciH42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>mcburnie oliver</t>
+          <t>iglesias borja</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>4AaiuZpF</t>
+          <t>ATAVnRY7</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>altimira adria</t>
+          <t>akhomach ilias</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>zk34NV3A</t>
+          <t>KYQuxWEL</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>alvin</t>
+          <t>barry thierno</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>WWHLyhpR</t>
+          <t>EL0WleP6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>chicco julian</t>
+          <t>costa logan</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>E5Et3VgM</t>
+          <t>p6rsDQvN</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>cruz juan</t>
+          <t>gueye pape</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>pO8Jn4Xm</t>
+          <t>WShuFWRi</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>dmitrovic marko</t>
+          <t>junior reis</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0QAeQWxE</t>
+          <t>S6QWzDng</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>franquesa enric</t>
+          <t>kambwala willy</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>EeUtTZld</t>
+          <t>bwHQNPyE</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>garcia campos diego</t>
+          <t>navarro pablo</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>pIpdGy2U</t>
+          <t>j3Hk0qEj</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>lopez roberto</t>
+          <t>pepe nicolas</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>CKYnnUEo</t>
+          <t>jVHfHxGn</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>munir el haddadi</t>
+          <t>perez ayoze</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>AufokyHE</t>
+          <t>Kjmmf9C3</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>porozo jackson</t>
+          <t>sola arnau</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>EwStt8o4</t>
+          <t>rLsgetTF</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>saenz jorge</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>A16UgbkJ</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>bassinga aboubacar</t>
-        </is>
-      </c>
+          <t>terrats ramon</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>KE0WWa1e</t>
+          <t>AVpwhNL9</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>campana jose</t>
+          <t>aidoo joseph</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>AkH99Ojn</t>
+          <t>nyLFv8t3</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>cardona marc</t>
+          <t>alvarez hugo</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>UaHeoBot</t>
+          <t>rVBGggAd</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>fuster manuel</t>
+          <t>aspas iago</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>jTdCpLmR</t>
+          <t>zykz5SJb</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>gil ivan</t>
+          <t>beltran francisco</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>xrJQVv9C</t>
+          <t>f79qYNc4</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>herzog juanma</t>
+          <t>dominguez carlos</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>nw5d39V0</t>
+          <t>YgPGkQYi</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>horkas dinko</t>
+          <t>douvikas anastasios</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>px36Cwpj</t>
+          <t>b7lKkJBn</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>loiodice enzo</t>
+          <t>duran pablo</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>r92RZve6</t>
+          <t>Au7zDEEL</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>mata jaime</t>
+          <t>guaita vicente</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>pjIG0H3d</t>
+          <t>bsZTFhAa</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>ramirez benito</t>
+          <t>rodriguez galiano javier</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>hSNXqigO</t>
+          <t>tGJYwtjh</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>sinkgraven daley</t>
+          <t>sotelo hugo</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>tYi46reg</t>
+          <t>KluZeL4G</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>viti</t>
+          <t>swedberg williot</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>6qPig05P</t>
+          <t>jVHfHxGn</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>tapia renato</t>
+          <t>perez ayoze</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>6qPig05P</t>
+          <t>jVHfHxGn</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>tapia renato</t>
+          <t>perez ayoze</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>OAPggVhT</t>
+          <t>UwfDD083</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>brasanac darko</t>
+          <t>moreno gerard</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>E5Et3VgM</t>
+          <t>EL0WleP6</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>cruz juan</t>
+          <t>costa logan</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>E5Et3VgM</t>
+          <t>EL0WleP6</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>cruz juan</t>
+          <t>costa logan</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>2cPwbh8J</t>
+          <t>G8VcNrxU</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>raba daniel</t>
+          <t>bailly eric</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>EeUtTZld</t>
+          <t>j3Hk0qEj</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>garcia campos diego</t>
+          <t>pepe nicolas</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>EeUtTZld</t>
+          <t>j3Hk0qEj</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>garcia campos diego</t>
+          <t>pepe nicolas</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>6yaQrJGS</t>
+          <t>8fnHDvMe</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>de la fuente miguel</t>
+          <t>santos yeremi</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>0QAeQWxE</t>
+          <t>KYQuxWEL</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>franquesa enric</t>
+          <t>barry thierno</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>0QAeQWxE</t>
+          <t>KYQuxWEL</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>franquesa enric</t>
+          <t>barry thierno</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>E3s5eF5I</t>
+          <t>tYV4tvqr</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>cisse seydouba</t>
+          <t>groeneveld arnaut</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>4AaiuZpF</t>
+          <t>p6rsDQvN</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>altimira adria</t>
+          <t>gueye pape</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>4AaiuZpF</t>
+          <t>p6rsDQvN</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>altimira adria</t>
+          <t>gueye pape</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>WWNny3e7</t>
+          <t>bmeQTB92</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>rodriguez oscar</t>
+          <t>baena alex</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>tYi46reg</t>
+          <t>zykz5SJb</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>viti</t>
+          <t>beltran francisco</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>tYi46reg</t>
+          <t>zykz5SJb</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>viti</t>
+          <t>beltran francisco</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>fBI7cV4b</t>
+          <t>MoAntFV8</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>alex suarez</t>
+          <t>kourouma moriba</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>px36Cwpj</t>
+          <t>nyLFv8t3</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>loiodice enzo</t>
+          <t>alvarez hugo</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>px36Cwpj</t>
+          <t>nyLFv8t3</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>loiodice enzo</t>
+          <t>alvarez hugo</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>b5g6gWjn</t>
+          <t>rHUdQZPd</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>moleiro alberto</t>
+          <t>carreira sergio</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>pjIG0H3d</t>
+          <t>KluZeL4G</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>ramirez benito</t>
+          <t>swedberg williot</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>pjIG0H3d</t>
+          <t>KluZeL4G</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>ramirez benito</t>
+          <t>swedberg williot</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>SjTBQO7b</t>
+          <t>8bvxeNAG</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>park marvin</t>
+          <t>manquillo javier</t>
         </is>
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>r92RZve6</t>
+          <t>rVBGggAd</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>mata jaime</t>
+          <t>aspas iago</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>r92RZve6</t>
+          <t>rVBGggAd</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>mata jaime</t>
+          <t>aspas iago</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>xlaNl83K</t>
+          <t>IXim7pWh</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>munoz alex</t>
+          <t>gonzalez alfonso</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>UaHeoBot</t>
+          <t>YgPGkQYi</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>fuster manuel</t>
+          <t>douvikas anastasios</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>UaHeoBot</t>
+          <t>YgPGkQYi</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>fuster manuel</t>
+          <t>douvikas anastasios</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>OKNQawg3</t>
+          <t>0vQciH42</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
         <is>
-          <t>kirian</t>
+          <t>iglesias borja</t>
         </is>
       </c>
       <c r="EV3" t="inlineStr">
         <is>
-          <t>fgqxKdwL</t>
+          <t>KxSmFSum</t>
         </is>
       </c>
       <c r="EW3" t="inlineStr">
         <is>
-          <t>gonzalez fabio</t>
+          <t>alfonso pedraza</t>
         </is>
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>6qyeYCYO</t>
+          <t>vcqiFPHQ</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>januzaj adnan</t>
+          <t>foyth juan</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>St8XPCaD</t>
+          <t>GW5JRBD0</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>pejino</t>
-        </is>
-      </c>
-      <c r="FB3" t="inlineStr"/>
-      <c r="FC3" t="inlineStr"/>
+          <t>de la torre luca</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>8zW214va</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>ristic mihailo</t>
+        </is>
+      </c>
       <c r="FD3" t="inlineStr"/>
       <c r="FE3" t="inlineStr"/>
       <c r="FF3" t="inlineStr">
         <is>
-          <t>6qPig05P</t>
+          <t>6HSinoFJ</t>
         </is>
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>tapia renato</t>
-        </is>
-      </c>
-      <c r="FH3" t="inlineStr"/>
-      <c r="FI3" t="inlineStr"/>
-      <c r="FJ3" t="inlineStr"/>
-      <c r="FK3" t="inlineStr"/>
-      <c r="FL3" t="inlineStr"/>
-      <c r="FM3" t="inlineStr"/>
-      <c r="FN3" t="inlineStr"/>
-      <c r="FO3" t="inlineStr"/>
-      <c r="FP3" t="inlineStr"/>
-      <c r="FQ3" t="inlineStr"/>
+          <t>vidal marc</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="FI3" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MVExOq3n</t>
+          <t>SYy8ZHN9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>courtois thibaut</t>
+          <t>oblak jan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rZh5FTHE</t>
+          <t>CMGUADgt</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>carvajal daniel</t>
+          <t>azpilicueta cesar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>zX2Rm9YG</t>
+          <t>IgRLzKhM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>militao eder</t>
+          <t>gimenez jose</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rZHXvTho</t>
+          <t>8GVQFgH4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>rudiger antonio</t>
+          <t>le normand robin</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>tURBbW9S</t>
+          <t>z3D5zvbD</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fran garcia</t>
+          <t>llorente marcos</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>nscfER6B</t>
+          <t>AZ6TTjDC</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>valverde federico</t>
+          <t>de paul rodrigo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>QkiZum3e</t>
+          <t>AaZiGJ9E</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>tchouameni aurelien</t>
+          <t>barrios pablo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>zPUyR5Up</t>
+          <t>2iQMPvBg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>rodrygo</t>
+          <t>riquelme rodrigo</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>CUU9qDpb</t>
+          <t>OxCa1jdT</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>guler arda</t>
+          <t>griezmann antoine</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CbwQ4Mws</t>
+          <t>vTPgNn01</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>vinicius junior</t>
+          <t>lino samuel</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Wn6E2SED</t>
+          <t>bBHauDIC</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>mbappe kylian</t>
+          <t>alvarez julian</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>jyH8E81E</t>
+          <t>jB3F3wGi</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>hein karl</t>
+          <t>gazzaniga paulo</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4zgv0hGk</t>
+          <t>UTk2FzpS</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>perez luis</t>
+          <t>martinez arnau</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>EZg4jPUF</t>
+          <t>250rn438</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>comert eray</t>
+          <t>lopez david</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>G6IFcpHK</t>
+          <t>U5mPqlh6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>boyomos flavien enzo</t>
+          <t>blind daley</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2g3Pa3qH</t>
+          <t>z9xliwUd</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>rosa lucas</t>
+          <t>gutierrez miguel</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>SCxfo9Zu</t>
+          <t>tzwJ3As6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>kike</t>
+          <t>herrera yangel</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>dfLinARB</t>
+          <t>WCC5IrWg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>juric stanko</t>
+          <t>romeu oriol</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>vkmiDN8F</t>
+          <t>vLPRaVJo</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>sanchez ivan</t>
+          <t>martin ivan</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>EN3EbULf</t>
+          <t>8l99epoQ</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>meseguer victor</t>
+          <t>tsygankov viktor</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>nBtLrBRF</t>
+          <t>EauanyEm</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>machis darwin</t>
+          <t>ruiz abel</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>dEgxh8oM</t>
+          <t>xSXBYlvl</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>marcos andre</t>
+          <t>gil bryan</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>zPYmze7F</t>
+          <t>McWkid34</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>ceballos dani</t>
+          <t>correa angel</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>nm2Qvnyk</t>
+          <t>t8GDN709</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>diaz brahim</t>
+          <t>galan javier</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>bXHrpEJ4</t>
+          <t>dtbJO8B3</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>endrick</t>
+          <t>gallagher conor</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>Is0aEgM6</t>
+          <t>0rBkNdYp</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>perez francisco javier gonzalez</t>
+          <t>gomis aleman antonio</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>pEjBDsSH</t>
+          <t>29aQRcre</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>lucas</t>
+          <t>iturbe alejandro</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0S7ye9jr</t>
+          <t>v9hLv1xJ</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>lunin andriy</t>
+          <t>koke</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>bZWyoJnA</t>
+          <t>QTc0qeb2</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>modric luka</t>
+          <t>kostis ilias</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>dIvLWqXc</t>
+          <t>zekFd0M8</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>naveros jacobo</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
+          <t>mandava reinildo</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>M3TzoLot</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>molina nahuel</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>IJTJu41i</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>simeone giuliano</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>QwqgNkTP</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>sorloth alexander</t>
+        </is>
+      </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>f7bNFe72</t>
+          <t>2JsUqijl</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>amallah selim</t>
+          <t>witsel axel</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>bcJKuoR6</t>
+          <t>zy0jwcjQ</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>chuki</t>
+          <t>almena iker</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0n8qUmN8</t>
+          <t>OjpPzOu0</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>de la hoz cesar</t>
+          <t>frances alejandro</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>j5SMgGHu</t>
+          <t>n1iE7ch5</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>ferreira andre</t>
+          <t>juan carlos</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>UHqRA6g4</t>
+          <t>GbY2OPWp</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>iglesias koke</t>
+          <t>juanpe</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>IXreUcCq</t>
+          <t>nZ8SVvvE</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>martin mario</t>
+          <t>krejci ladislav</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>zw8vYjwk</t>
+          <t>rZes9CKA</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>moro raul</t>
+          <t>lopez pau</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>42y06OiE</t>
+          <t>2ZExqRk3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>ndiaye amath</t>
+          <t>miovski bojan</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>AJg8NPiE</t>
+          <t>2e75edda</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>ruiz raul chasco</t>
+          <t>misehouy gabriel osei</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>6NytetE5</t>
+          <t>n5xqpcKc</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>sanchez javier</t>
+          <t>portu</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>YqtgOOMN</t>
+          <t>CxVKphX0</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>sylla mamadou</t>
+          <t>solis jhon</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>8S0B28YJ</t>
+          <t>U5yv9YBB</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>torres david</t>
+          <t>stuani christian</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>bZWyoJnA</t>
+          <t>dtbJO8B3</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>modric luka</t>
+          <t>gallagher conor</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>bZWyoJnA</t>
+          <t>dtbJO8B3</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>modric luka</t>
+          <t>gallagher conor</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>zPUyR5Up</t>
+          <t>2iQMPvBg</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>rodrygo</t>
+          <t>riquelme rodrigo</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>nm2Qvnyk</t>
+          <t>v9hLv1xJ</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>diaz brahim</t>
+          <t>koke</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>nm2Qvnyk</t>
+          <t>v9hLv1xJ</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>diaz brahim</t>
+          <t>koke</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>CUU9qDpb</t>
+          <t>AZ6TTjDC</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>guler arda</t>
+          <t>de paul rodrigo</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>zPYmze7F</t>
+          <t>zekFd0M8</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>ceballos dani</t>
+          <t>mandava reinildo</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>zPYmze7F</t>
+          <t>zekFd0M8</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>ceballos dani</t>
+          <t>mandava reinildo</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>CbwQ4Mws</t>
+          <t>vTPgNn01</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>vinicius junior</t>
+          <t>lino samuel</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
         <is>
-          <t>bXHrpEJ4</t>
+          <t>QwqgNkTP</t>
         </is>
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>endrick</t>
+          <t>sorloth alexander</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>bXHrpEJ4</t>
+          <t>QwqgNkTP</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>endrick</t>
+          <t>sorloth alexander</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>Wn6E2SED</t>
+          <t>bBHauDIC</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>mbappe kylian</t>
-        </is>
-      </c>
-      <c r="DL4" t="inlineStr"/>
-      <c r="DM4" t="inlineStr"/>
-      <c r="DN4" t="inlineStr"/>
-      <c r="DO4" t="inlineStr"/>
-      <c r="DP4" t="inlineStr"/>
-      <c r="DQ4" t="inlineStr"/>
+          <t>alvarez julian</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>McWkid34</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>correa angel</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>McWkid34</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>correa angel</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>OxCa1jdT</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>griezmann antoine</t>
+        </is>
+      </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>zw8vYjwk</t>
+          <t>n5xqpcKc</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>moro raul</t>
+          <t>portu</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>zw8vYjwk</t>
+          <t>n5xqpcKc</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
         <is>
-          <t>moro raul</t>
+          <t>portu</t>
         </is>
       </c>
       <c r="DV4" t="inlineStr">
         <is>
-          <t>nBtLrBRF</t>
+          <t>vLPRaVJo</t>
         </is>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>machis darwin</t>
+          <t>martin ivan</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>f7bNFe72</t>
+          <t>2ZExqRk3</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>amallah selim</t>
+          <t>miovski bojan</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
         <is>
-          <t>f7bNFe72</t>
+          <t>2ZExqRk3</t>
         </is>
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>amallah selim</t>
+          <t>miovski bojan</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
         <is>
-          <t>EN3EbULf</t>
+          <t>EauanyEm</t>
         </is>
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>meseguer victor</t>
+          <t>ruiz abel</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>YqtgOOMN</t>
+          <t>CxVKphX0</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>sylla mamadou</t>
+          <t>solis jhon</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>YqtgOOMN</t>
+          <t>CxVKphX0</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>sylla mamadou</t>
+          <t>solis jhon</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>dEgxh8oM</t>
+          <t>WCC5IrWg</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>marcos andre</t>
+          <t>romeu oriol</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>IXreUcCq</t>
+          <t>zy0jwcjQ</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>martin mario</t>
+          <t>almena iker</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>IXreUcCq</t>
+          <t>zy0jwcjQ</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
         <is>
-          <t>martin mario</t>
+          <t>almena iker</t>
         </is>
       </c>
       <c r="EN4" t="inlineStr">
         <is>
-          <t>dfLinARB</t>
+          <t>8l99epoQ</t>
         </is>
       </c>
       <c r="EO4" t="inlineStr">
         <is>
-          <t>juric stanko</t>
-        </is>
-      </c>
-      <c r="EP4" t="inlineStr">
-        <is>
-          <t>42y06OiE</t>
-        </is>
-      </c>
-      <c r="EQ4" t="inlineStr">
-        <is>
-          <t>ndiaye amath</t>
-        </is>
-      </c>
-      <c r="ER4" t="inlineStr">
-        <is>
-          <t>42y06OiE</t>
-        </is>
-      </c>
-      <c r="ES4" t="inlineStr">
-        <is>
-          <t>ndiaye amath</t>
-        </is>
-      </c>
-      <c r="ET4" t="inlineStr">
-        <is>
-          <t>SCxfo9Zu</t>
-        </is>
-      </c>
-      <c r="EU4" t="inlineStr">
-        <is>
-          <t>kike</t>
-        </is>
-      </c>
+          <t>tsygankov viktor</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
       <c r="EV4" t="inlineStr">
         <is>
-          <t>bygTWQzR</t>
+          <t>jX8PENMO</t>
         </is>
       </c>
       <c r="EW4" t="inlineStr">
         <is>
-          <t>anuar</t>
-        </is>
-      </c>
-      <c r="EX4" t="inlineStr"/>
-      <c r="EY4" t="inlineStr"/>
-      <c r="EZ4" t="inlineStr"/>
-      <c r="FA4" t="inlineStr"/>
-      <c r="FB4" t="inlineStr"/>
-      <c r="FC4" t="inlineStr"/>
-      <c r="FD4" t="inlineStr"/>
-      <c r="FE4" t="inlineStr"/>
-      <c r="FF4" t="inlineStr"/>
-      <c r="FG4" t="inlineStr"/>
-      <c r="FH4" t="inlineStr">
-        <is>
-          <t>hKx3nCTp</t>
-        </is>
-      </c>
-      <c r="FI4" t="inlineStr">
-        <is>
-          <t>alaba david</t>
-        </is>
-      </c>
-      <c r="FJ4" t="inlineStr">
-        <is>
-          <t>QNvlPm7s</t>
-        </is>
-      </c>
-      <c r="FK4" t="inlineStr">
-        <is>
-          <t>bellingham jude</t>
-        </is>
-      </c>
-      <c r="FL4" t="inlineStr">
-        <is>
-          <t>6ekYsPfO</t>
-        </is>
-      </c>
-      <c r="FM4" t="inlineStr">
-        <is>
-          <t>camavinga eduardo</t>
-        </is>
-      </c>
-      <c r="FN4" t="inlineStr">
-        <is>
-          <t>KnytnSKl</t>
-        </is>
-      </c>
-      <c r="FO4" t="inlineStr">
-        <is>
-          <t>mendy ferland</t>
-        </is>
-      </c>
-      <c r="FP4" t="inlineStr">
-        <is>
-          <t>WSRdoQ7I</t>
-        </is>
-      </c>
-      <c r="FQ4" t="inlineStr">
-        <is>
-          <t>vallejo jesus</t>
-        </is>
-      </c>
+          <t>lemar thomas</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t>OQY4TKul</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>marcos paulo</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>nev0KWuA</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>fernandez valery</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
+          <t>bs2gvblF</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t>van de beek donny</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr"/>
+      <c r="FI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>nXUxw7wg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vuAlEqes</t>
+          <t>WGae8d9E</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>garcia joan</t>
+          <t>marin carlos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>z9FaGS78</t>
+          <t>S4KW2ean</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>el hilali omar</t>
+          <t>albarran carlos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8xTCtgln</t>
+          <t>O6hVP1TB</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>kumbulla marash</t>
+          <t>ruiz adrian</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IsOwrMdM</t>
+          <t>jwvNqlFq</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cabrera leandro</t>
+          <t>antonio martinez jose</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>YDxiIlER</t>
+          <t>8t3vtwdc</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>romero carlos</t>
+          <t>calderon jose</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>KSNZwPAG</t>
+          <t>f5JqWchj</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>carreras jofe</t>
+          <t>zidane theo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>QPoHzbRQ</t>
+          <t>veLxs2Gg</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>gragera jose</t>
+          <t>sala alex</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>UuiJcUMl</t>
+          <t>Qav8SAwf</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>kral alex</t>
+          <t>rodriganez jacobo</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>86UW3kYK</t>
+          <t>j9FVq54i</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>cardona irvin</t>
+          <t>carracedo cristian</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>hph7e3vc</t>
+          <t>trR2Luu5</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>veliz alejo</t>
+          <t>casas antonio</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Cl8Ia7Q9</t>
+          <t>O6KQ2Fml</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>puado javi</t>
+          <t>adilson</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>UmDjbtRC</t>
+          <t>rPMUGw3h</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>remiro alejandro</t>
+          <t>cantero ander</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>fRSnvKQG</t>
+          <t>AyAxdOaP</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>traore hamari</t>
+          <t>arroyo anderson</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>6qVwC9AH</t>
+          <t>S2nS0dZr</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>elustondo aritz</t>
+          <t>lopez david</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Qk9dJWGB</t>
+          <t>hQpQJSqn</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>pacheco jon</t>
+          <t>cordoba aitor</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>MaufHIJ2</t>
+          <t>46wCqoNi</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>lopez javi</t>
+          <t>miguel florian</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2scm2TO3</t>
+          <t>IijdLfIb</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>becker sheraldo</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>fNI6Gsdr</t>
+          <t>4fkoGF10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>zubimendi martin</t>
+          <t>navarro raul</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>WtVfJtAm</t>
+          <t>KI3xYemP</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>turrientes benat</t>
+          <t>appin kevin</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>fmGvlHVM</t>
+          <t>UPMWp37R</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>gomez sergio</t>
+          <t>ojeda daniel</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Ey5XjmJt</t>
+          <t>v1g9lCm3</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>mendez brais</t>
+          <t>curro sanchez</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>dQ1P695O</t>
+          <t>EPzCN58J</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>oyarzabal mikel</t>
+          <t>nino fer</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>fyEdYgal</t>
+          <t>hzNRiFk1</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>aguado alvaro</t>
+          <t>barboza matias</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>jcshWJpG</t>
+          <t>xAhhX5Vm</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>bauza rafel</t>
+          <t>munoz carlos</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sj35PsHd</t>
+          <t>CKovzT1H</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>calero fernando</t>
+          <t>molina antonio</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>jRx96X5h</t>
+          <t>YsOcklca</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>fortuno angel</t>
+          <t>obolskiy nikolay</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>v1bRsEDN</t>
+          <t>bZb6aNtj</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>gomez sergi</t>
+          <t>ortiz josema</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>6o8Nnmm1</t>
+          <t>Agk5MJwd</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>lozano pol</t>
+          <t>rodriguez genaro</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>EsMMVFh3</t>
+          <t>IV8hD3Am</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>milla pere</t>
+          <t>sintes xavi</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>n9R1WQ3p</t>
+          <t>CfBHradb</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>olivan brian</t>
+          <t>soonsup bell jude</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>27U3P9mT</t>
+          <t>KAc8u2f4</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>pacheco fernando</t>
+          <t>vila ramon</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>ILCGOm9n</t>
+          <t>fu9bjNgL</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>roca antoniu</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>x0TzcxX6</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>sanchez salvi</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>vNTtZiAr</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>aranburu jon</t>
-        </is>
-      </c>
+          <t>aizagar ander yoldi</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>QLpDwPEJ</t>
+          <t>0poEwxl4</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>arana egoitz</t>
+          <t>atienza miguel</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>OvykMeki</t>
+          <t>hQU1V6u9</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>gonzalez urko</t>
+          <t>badiashile loic</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>fqdLdpc3</t>
+          <t>S8CD3sIU</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>kubo takefusa</t>
+          <t>cordoba inigo</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0IZE0zuH</t>
+          <t>lIO1oG6S</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>magunazelaia jon</t>
+          <t>del cerro saul</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>Ye976xiA</t>
+          <t>6kWRKUsC</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>marin pablo</t>
+          <t>espiau edu</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>Wr5ZTIf7</t>
+          <t>rTFUvlCc</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>marrero larranaga unai</t>
+          <t>exposito jimenez marcelo</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>dd9n67gb</t>
+          <t>ljSkZFwn</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>martin jon</t>
+          <t>gonzalez david</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>C8QkouJU</t>
+          <t>lvl2kso0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>munoz aihen</t>
+          <t>lopez javier</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>O8nKKpaP</t>
+          <t>U5V6iENe</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>olasagasti jon</t>
+          <t>martin ander</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>UsKF9Yzn</t>
+          <t>tSrz5SW1</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>sadiq umar</t>
+          <t>morante ivan</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>p6f9CgsE</t>
+          <t>8zZErFJT</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>sucic luka</t>
+          <t>pascual hugo</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>n9R1WQ3p</t>
+          <t>fu9bjNgL</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>olivan brian</t>
+          <t>aizagar ander yoldi</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>n9R1WQ3p</t>
+          <t>fu9bjNgL</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>olivan brian</t>
+          <t>aizagar ander yoldi</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>86UW3kYK</t>
+          <t>O6KQ2Fml</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>cardona irvin</t>
+          <t>adilson</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>fyEdYgal</t>
+          <t>YsOcklca</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>aguado alvaro</t>
+          <t>obolskiy nikolay</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>fyEdYgal</t>
+          <t>YsOcklca</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>aguado alvaro</t>
+          <t>obolskiy nikolay</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>QPoHzbRQ</t>
+          <t>trR2Luu5</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>gragera jose</t>
+          <t>casas antonio</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>ILCGOm9n</t>
+          <t>Agk5MJwd</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>roca antoniu</t>
+          <t>rodriguez genaro</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>ILCGOm9n</t>
+          <t>Agk5MJwd</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>roca antoniu</t>
+          <t>rodriguez genaro</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>KSNZwPAG</t>
+          <t>f5JqWchj</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>carreras jofe</t>
+          <t>zidane theo</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>EsMMVFh3</t>
+          <t>IV8hD3Am</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>milla pere</t>
+          <t>sintes xavi</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>EsMMVFh3</t>
+          <t>IV8hD3Am</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>milla pere</t>
+          <t>sintes xavi</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>YDxiIlER</t>
+          <t>j9FVq54i</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>romero carlos</t>
+          <t>carracedo cristian</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>n7ISbL3j</t>
+          <t>xAhhX5Vm</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>tejero alvaro</t>
+          <t>munoz carlos</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>n7ISbL3j</t>
+          <t>xAhhX5Vm</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>tejero alvaro</t>
+          <t>munoz carlos</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>z9FaGS78</t>
+          <t>Qav8SAwf</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>el hilali omar</t>
+          <t>rodriganez jacobo</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>fqdLdpc3</t>
+          <t>tSrz5SW1</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>kubo takefusa</t>
+          <t>morante ivan</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>fqdLdpc3</t>
+          <t>tSrz5SW1</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>kubo takefusa</t>
+          <t>morante ivan</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>Ey5XjmJt</t>
+          <t>4fkoGF10</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>mendez brais</t>
+          <t>navarro raul</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>O8nKKpaP</t>
+          <t>6kWRKUsC</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>olasagasti jon</t>
+          <t>espiau edu</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>O8nKKpaP</t>
+          <t>6kWRKUsC</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>olasagasti jon</t>
+          <t>espiau edu</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>WtVfJtAm</t>
+          <t>EPzCN58J</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>turrientes benat</t>
+          <t>nino fer</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>UsKF9Yzn</t>
+          <t>S8CD3sIU</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>sadiq umar</t>
+          <t>cordoba inigo</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>UsKF9Yzn</t>
+          <t>S8CD3sIU</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>sadiq umar</t>
+          <t>cordoba inigo</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>dQ1P695O</t>
+          <t>UPMWp37R</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>oyarzabal mikel</t>
+          <t>ojeda daniel</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>vNTtZiAr</t>
+          <t>ljSkZFwn</t>
         </is>
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>aranburu jon</t>
+          <t>gonzalez david</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>vNTtZiAr</t>
+          <t>ljSkZFwn</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
         <is>
-          <t>aranburu jon</t>
+          <t>gonzalez david</t>
         </is>
       </c>
       <c r="EN5" t="inlineStr">
         <is>
-          <t>fRSnvKQG</t>
+          <t>KI3xYemP</t>
         </is>
       </c>
       <c r="EO5" t="inlineStr">
         <is>
-          <t>traore hamari</t>
+          <t>appin kevin</t>
         </is>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>Ye976xiA</t>
+          <t>0poEwxl4</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>marin pablo</t>
+          <t>atienza miguel</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>Ye976xiA</t>
+          <t>0poEwxl4</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>marin pablo</t>
+          <t>atienza miguel</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>2scm2TO3</t>
+          <t>IijdLfIb</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
         <is>
-          <t>becker sheraldo</t>
-        </is>
-      </c>
-      <c r="EV5" t="inlineStr">
-        <is>
-          <t>A3vo4Lf6</t>
-        </is>
-      </c>
-      <c r="EW5" t="inlineStr">
-        <is>
-          <t>barrenetxea muguruza ander</t>
-        </is>
-      </c>
-      <c r="EX5" t="inlineStr">
-        <is>
-          <t>0zO9SfkA</t>
-        </is>
-      </c>
-      <c r="EY5" t="inlineStr">
-        <is>
-          <t>odriozola alvaro</t>
-        </is>
-      </c>
-      <c r="EZ5" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="FA5" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
-      <c r="FB5" t="inlineStr">
-        <is>
-          <t>phTjGNq0</t>
-        </is>
-      </c>
-      <c r="FC5" t="inlineStr">
-        <is>
-          <t>zubeldia igor</t>
-        </is>
-      </c>
+          <t>alex</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+      <c r="EX5" t="inlineStr"/>
+      <c r="EY5" t="inlineStr"/>
+      <c r="EZ5" t="inlineStr"/>
+      <c r="FA5" t="inlineStr"/>
+      <c r="FB5" t="inlineStr"/>
+      <c r="FC5" t="inlineStr"/>
       <c r="FD5" t="inlineStr"/>
       <c r="FE5" t="inlineStr"/>
       <c r="FF5" t="inlineStr">
         <is>
-          <t>n7ISbL3j</t>
+          <t>xOIewwcB</t>
         </is>
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>tejero alvaro</t>
-        </is>
-      </c>
-      <c r="FH5" t="inlineStr">
-        <is>
-          <t>SChm1pCo</t>
-        </is>
-      </c>
-      <c r="FI5" t="inlineStr">
-        <is>
-          <t>exposito edu</t>
-        </is>
-      </c>
-      <c r="FJ5" t="inlineStr"/>
-      <c r="FK5" t="inlineStr"/>
-      <c r="FL5" t="inlineStr"/>
-      <c r="FM5" t="inlineStr"/>
-      <c r="FN5" t="inlineStr"/>
-      <c r="FO5" t="inlineStr"/>
-      <c r="FP5" t="inlineStr"/>
-      <c r="FQ5" t="inlineStr"/>
+          <t>rastrilla hugo</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr"/>
+      <c r="FI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>Q31eQTgm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2VpTGXlE</t>
+          <t>G4b5p859</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>soria david</t>
+          <t>campos pablo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>K0bkMuVF</t>
+          <t>pSeqAJ0c</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>iglesias juan</t>
+          <t>aguirregabiria martin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>xnvqJMC1</t>
+          <t>KrX5waGB</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>djene</t>
+          <t>sipcic nikola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>fLceoUtl</t>
+          <t>juxRzfwF</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>alderete omar</t>
+          <t>kiko olivas</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>l0v5oji3</t>
+          <t>IilHTmj9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>rico diego</t>
+          <t>rios reina jose</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8fpOagmR</t>
+          <t>8xkqsBHk</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>sola alex</t>
+          <t>musto marcelo daniel</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>lWTa55Ta</t>
+          <t>WMnz8BzK</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>nabil aberdin</t>
+          <t>andy</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>jwhHdRF0</t>
+          <t>nFO9fFkl</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>milla luis</t>
+          <t>izquierdo jairo</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>vP5uwPQf</t>
+          <t>nThR7Un8</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>alena carles</t>
+          <t>guerrero sergio</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0WJHh4Qs</t>
+          <t>KnJdARG3</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>perez carles</t>
+          <t>teguia cedric</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>8G2sXaI8</t>
+          <t>46haE6np</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>uche chrisantus</t>
+          <t>valles gaston</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0v264VE8</t>
+          <t>2RWVJ0mS</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>cardenas dani</t>
+          <t>poussin gaetan</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>CzBEqCjK</t>
+          <t>EctXf3CQ</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>balliu ivan</t>
+          <t>calero ivan</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>K2JPoFRo</t>
+          <t>ADwlmnw6</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>mumin abdul</t>
+          <t>marmol lluis</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>fNu1l3xc</t>
+          <t>2yO22dZF</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>lejeune florian</t>
+          <t>vital bernardo</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>vHFG4hw9</t>
+          <t>MsLEXo2J</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>espino alfonso</t>
+          <t>tasende dani</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>fcuYevNb</t>
+          <t>ULQo1Vhr</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>valentin oscar</t>
+          <t>bermejo sergio</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>zRB7v9IT</t>
+          <t>4jcnOm31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>ciss pathe</t>
+          <t>bare keidi</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>UiH85aKC</t>
+          <t>KQYMzB7t</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>de frutos jorge</t>
+          <t>aguado marc</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>42E71F4r</t>
+          <t>EPkF4hUA</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>trejo oscar</t>
+          <t>liso adrian</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>x8BHeb6c</t>
+          <t>xAKBBXpc</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>embarba adri</t>
+          <t>soberon mario</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>M5IbUyg1</t>
+          <t>6mb7wPdI</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>nketa randy</t>
+          <t>bazdar samed</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>viZPCO3c</t>
+          <t>rqnIpvc8</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>alcantara alberto risco</t>
+          <t>alcala pedro</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>zHQB5zMa</t>
+          <t>8b3l0HB5</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>arambarri mauro</t>
+          <t>andugar angel</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>8YG04fHd</t>
+          <t>baZ7aMTa</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>berrocal juan</t>
+          <t>escriche daniel</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>bDpj7xEB</t>
+          <t>6gGt1XDd</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>duarte domingos</t>
+          <t>fuidias toni</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>46yHKt1f</t>
+          <t>vRNUBqy4</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>letacek jiri</t>
+          <t>moreno jorge</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>lGNHRlTm</t>
+          <t>MJcnwOI5</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>peter federico</t>
+          <t>munoz luis</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>QPU3c6Hm</t>
+          <t>6DIWoQi4</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>santiago yellu</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>8Wuyaqc4</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>batalla augusto</t>
-        </is>
-      </c>
+          <t>ortuno alfredo</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>xnPUpahj</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>reyes jhafets</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>nJwfryI5</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>ayton roman lucas</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>fFDutvUN</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>sanchez carmelo</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>KK2GPNcn</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>vukcevic andrija</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>fFlZRkvF</t>
+          <t>vFkqiEfF</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>camello sergio</t>
+          <t>acin guillermo</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>hGPnN7fG</t>
+          <t>GjsJwEtR</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>chavarria pep</t>
+          <t>alvarez cristian</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>jcX738kC</t>
+          <t>Mol2TYUm</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>de las sias marco</t>
+          <t>azon ivan</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>MVcspA2M</t>
+          <t>6uXqLpX9</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>de tomas raul</t>
+          <t>garcia francho</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2i6AHS2l</t>
+          <t>E3pkEtFM</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>diaz pedro</t>
+          <t>gori</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>21xu5Zng</t>
+          <t>YBErmO6h</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>balboa pelayo</t>
+          <t>lecoeuche quentin</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>OMUGUEla</t>
+          <t>lGBLl2mm</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>garcia alvaro</t>
+          <t>luna marcos</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>raqVZ405</t>
+          <t>6gQosNq6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>gumbau gerard</t>
+          <t>moya toni</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>dln9VIHe</t>
+          <t>2RBw3D8c</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>aridane</t>
+          <t>sabater juan carlos</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>dYFtDut6</t>
+          <t>rPH2xAjh</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>lopez unai</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>x2AuZhpr</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>palazon isaac</t>
-        </is>
-      </c>
+          <t>sans pau</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>QPU3c6Hm</t>
+          <t>MJcnwOI5</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>santiago yellu</t>
+          <t>munoz luis</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>QPU3c6Hm</t>
+          <t>MJcnwOI5</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>santiago yellu</t>
+          <t>munoz luis</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>lWTa55Ta</t>
+          <t>KnJdARG3</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>nabil aberdin</t>
+          <t>teguia cedric</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>viZPCO3c</t>
+          <t>KK2GPNcn</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>alcantara alberto risco</t>
+          <t>vukcevic andrija</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>viZPCO3c</t>
+          <t>KK2GPNcn</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>alcantara alberto risco</t>
+          <t>vukcevic andrija</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>8fpOagmR</t>
+          <t>nFO9fFkl</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>sola alex</t>
+          <t>izquierdo jairo</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>lGNHRlTm</t>
+          <t>baZ7aMTa</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>peter federico</t>
+          <t>escriche daniel</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>lGNHRlTm</t>
+          <t>baZ7aMTa</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
-          <t>peter federico</t>
+          <t>escriche daniel</t>
         </is>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>vP5uwPQf</t>
+          <t>nThR7Un8</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>alena carles</t>
+          <t>guerrero sergio</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
         <is>
-          <t>zHQB5zMa</t>
+          <t>6DIWoQi4</t>
         </is>
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>arambarri mauro</t>
+          <t>ortuno alfredo</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>zHQB5zMa</t>
+          <t>6DIWoQi4</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
         <is>
-          <t>arambarri mauro</t>
+          <t>ortuno alfredo</t>
         </is>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>0WJHh4Qs</t>
+          <t>46haE6np</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>perez carles</t>
-        </is>
-      </c>
-      <c r="DL6" t="inlineStr"/>
-      <c r="DM6" t="inlineStr"/>
-      <c r="DN6" t="inlineStr"/>
-      <c r="DO6" t="inlineStr"/>
-      <c r="DP6" t="inlineStr"/>
-      <c r="DQ6" t="inlineStr"/>
+          <t>valles gaston</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>nJwfryI5</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>ayton roman lucas</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>nJwfryI5</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>ayton roman lucas</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>IilHTmj9</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>rios reina jose</t>
+        </is>
+      </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>x2AuZhpr</t>
+          <t>Mol2TYUm</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
         <is>
-          <t>palazon isaac</t>
+          <t>azon ivan</t>
         </is>
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>x2AuZhpr</t>
+          <t>Mol2TYUm</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
         <is>
-          <t>palazon isaac</t>
+          <t>azon ivan</t>
         </is>
       </c>
       <c r="DV6" t="inlineStr">
         <is>
-          <t>42E71F4r</t>
+          <t>ULQo1Vhr</t>
         </is>
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>trejo oscar</t>
+          <t>bermejo sergio</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>OMUGUEla</t>
+          <t>rPH2xAjh</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>garcia alvaro</t>
+          <t>sans pau</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>OMUGUEla</t>
+          <t>rPH2xAjh</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>garcia alvaro</t>
+          <t>sans pau</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>UiH85aKC</t>
+          <t>xAKBBXpc</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>de frutos jorge</t>
+          <t>soberon mario</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>fFlZRkvF</t>
+          <t>6uXqLpX9</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>camello sergio</t>
+          <t>garcia francho</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>fFlZRkvF</t>
+          <t>6uXqLpX9</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>camello sergio</t>
+          <t>garcia francho</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>M5IbUyg1</t>
+          <t>4jcnOm31</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
         <is>
-          <t>nketa randy</t>
+          <t>bare keidi</t>
         </is>
       </c>
       <c r="EJ6" t="inlineStr">
         <is>
-          <t>dYFtDut6</t>
+          <t>6gQosNq6</t>
         </is>
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>lopez unai</t>
+          <t>moya toni</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>dYFtDut6</t>
+          <t>6gQosNq6</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
         <is>
-          <t>lopez unai</t>
+          <t>moya toni</t>
         </is>
       </c>
       <c r="EN6" t="inlineStr">
         <is>
-          <t>zRB7v9IT</t>
+          <t>KQYMzB7t</t>
         </is>
       </c>
       <c r="EO6" t="inlineStr">
         <is>
-          <t>ciss pathe</t>
+          <t>aguado marc</t>
         </is>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>2i6AHS2l</t>
+          <t>lGBLl2mm</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>diaz pedro</t>
+          <t>luna marcos</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>2i6AHS2l</t>
+          <t>lGBLl2mm</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>diaz pedro</t>
+          <t>luna marcos</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>x8BHeb6c</t>
+          <t>6mb7wPdI</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
         <is>
-          <t>embarba adri</t>
-        </is>
-      </c>
-      <c r="EV6" t="inlineStr">
-        <is>
-          <t>SdatvAiU</t>
-        </is>
-      </c>
-      <c r="EW6" t="inlineStr">
-        <is>
-          <t>mendez diego</t>
-        </is>
-      </c>
-      <c r="EX6" t="inlineStr">
-        <is>
-          <t>Eo8SAMoI</t>
-        </is>
-      </c>
-      <c r="EY6" t="inlineStr">
-        <is>
-          <t>ratiu andrei</t>
-        </is>
-      </c>
+          <t>bazdar samed</t>
+        </is>
+      </c>
+      <c r="EV6" t="inlineStr"/>
+      <c r="EW6" t="inlineStr"/>
+      <c r="EX6" t="inlineStr"/>
+      <c r="EY6" t="inlineStr"/>
       <c r="EZ6" t="inlineStr"/>
       <c r="FA6" t="inlineStr"/>
       <c r="FB6" t="inlineStr"/>
@@ -5254,779 +5182,707 @@
       <c r="FE6" t="inlineStr"/>
       <c r="FF6" t="inlineStr"/>
       <c r="FG6" t="inlineStr"/>
-      <c r="FH6" t="inlineStr">
-        <is>
-          <t>8OTCRUh0</t>
-        </is>
-      </c>
-      <c r="FI6" t="inlineStr">
-        <is>
-          <t>mayoral borja</t>
-        </is>
-      </c>
-      <c r="FJ6" t="inlineStr"/>
-      <c r="FK6" t="inlineStr"/>
-      <c r="FL6" t="inlineStr"/>
-      <c r="FM6" t="inlineStr"/>
-      <c r="FN6" t="inlineStr"/>
-      <c r="FO6" t="inlineStr"/>
-      <c r="FP6" t="inlineStr"/>
-      <c r="FQ6" t="inlineStr"/>
+      <c r="FH6" t="inlineStr"/>
+      <c r="FI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tEvOrxAE</t>
+          <t>MVf4O7Oa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0YMlqiSM</t>
+          <t>Moj39S61</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>raul</t>
+          <t>alejandro gonzalo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lAgIB16T</t>
+          <t>lO6sobTG</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>alvaro</t>
+          <t>chirino daijiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>vwcobdxb</t>
+          <t>rZwPCDVc</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>garcia jon</t>
+          <t>jimenez alberto</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Y9HNvyBJ</t>
+          <t>hIm8dpPN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>martinez ros</t>
+          <t>vertrouwd jozhua</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>nsEvRNJH</t>
+          <t>nwdj0Ls1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>costa jaume</t>
+          <t>mamah kenneth obinna</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>lAyK4sZ3</t>
+          <t>fmjvOOXT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>quiles alberto</t>
+          <t>flakus bosilj david</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>zo61BrW3</t>
+          <t>Oz4LFsdm</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>marchan rai</t>
+          <t>gil oscar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4CIfCKQ5</t>
+          <t>63JPjZot</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>rodriguez riki</t>
+          <t>seuntjens mats</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Y7vZ4xCl</t>
+          <t>hdzS6xVf</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>morcillo jon</t>
+          <t>sanchez raul</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0zIF6Wg2</t>
+          <t>joO0HA3L</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>fidel</t>
+          <t>aurelio douglas</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>OCmIC7xi</t>
+          <t>MXMTbTjl</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>garcia juanma</t>
+          <t>de miguel jesus</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>6uLxUVCT</t>
+          <t>lA1Qa7LH</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>dituro matias</t>
+          <t>escandell aaron</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>U93anmS8</t>
+          <t>Cjw1V4uo</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>nunez alvaro</t>
+          <t>ahijado lucas</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>bqApK6mO</t>
+          <t>CxnAZJbo</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>mario gaspar</t>
+          <t>luengo oier</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>jkeA7fag</t>
+          <t>fgJYtAmE</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>barzic matia</t>
+          <t>calvo dani</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>fXlAtRep</t>
+          <t>69aNbb67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>salinas jose</t>
+          <t>alhassane rahim</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>IylSu6Jk</t>
+          <t>vg9tJMbL</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>febas aleix</t>
+          <t>sibo kwasi</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>lhUwqUHS</t>
+          <t>CMhGvpU0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>plano oscar</t>
+          <t>del moral alberto</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2ur060Vt</t>
+          <t>GODeIoHH</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>castro nicolas</t>
+          <t>hassan haissem</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>fJhTE3Am</t>
+          <t>YeImVH7d</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>fernandez mercau nicolas</t>
+          <t>dotor carlos</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>pdMGox1K</t>
+          <t>l88RYMiD</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>boayar adam</t>
+          <t>moyano francisco</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>fRxu5Qk7</t>
+          <t>ljVRztTj</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>alonso yago</t>
+          <t>alemao</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>OAHrCN0T</t>
+          <t>WKrXys11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>aguilar lalo</t>
+          <t>albert jose</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>tdCq3gMJ</t>
+          <t>b13gbSqm</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>agus medina</t>
+          <t>calatrava alex</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4SRz95Sf</t>
+          <t>URckqU07</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>alcedo juan</t>
+          <t>calavera josep</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>44AZIBAr</t>
+          <t>KQL5Shet</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>gonzalez diego</t>
+          <t>cipenga brian</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>U3NYWaPL</t>
+          <t>OG6pnQq7</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>lazo jose carlos</t>
+          <t>punzano iker</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>pO1wPsLU</t>
+          <t>fDbFeqY3</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>melendez alejandro</t>
+          <t>schwake brian</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>GtEDHjtF</t>
+          <t>Eg6LHAo8</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>moreno marcos</t>
+          <t>suero israel</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>ziGOv0PB</t>
+          <t>23VZWq4k</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>pacheco antonio</t>
+          <t>suner pere marco</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>bPy9CrrI</t>
+          <t>CUPz0tB5</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>ramos mario</t>
+          <t>van den belt thomas</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>4Aa1KcL9</t>
+          <t>WpAyP013</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>rivero cristian</t>
+          <t>villahermosa daniel</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>tt4Mm9ws</t>
+          <t>fw0yGQLQ</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>rueda javier</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>tzAxVrkH</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>alvarez agustin</t>
-        </is>
-      </c>
+          <t>willems jetro</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>jJAqqPNm</t>
+          <t>ngBNZ9LM</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>badia edgar</t>
+          <t>braat quentin</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>65NCnIoE</t>
+          <t>jsRoAy4E</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>castella didac</t>
+          <t>suarez cardero alejandro</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>SY7HnwqR</t>
+          <t>rVt0F12N</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>diaby bambo</t>
+          <t>cazorla santi</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>27MtyaII</t>
+          <t>bD41lxAF</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>el ghezouani mourad</t>
+          <t>costas david</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>v5SjOstp</t>
+          <t>KhzzCbCU</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>houary ali</t>
+          <t>de la fuente pau</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>G4s5mw5N</t>
+          <t>QwD9sQn9</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>josan</t>
+          <t>lemos alvaro</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>YNiXFzek</t>
+          <t>O608W9Wj</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>mendoza rodrigo</t>
+          <t>mascarenhas francisco</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>WnnjuJl7</t>
+          <t>GxH7SxPr</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>rafael leonardo nunez mata</t>
+          <t>paraschiv daniel george</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>vLfzfoSg</t>
+          <t>fBb6eDAH</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>roldan fran</t>
+          <t>pomares carlos</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>ERmJI7HF</t>
+          <t>nPkoWJvS</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>salvador cristian</t>
+          <t>sanchez borja</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>pCDDvlwE</t>
+          <t>f3yV6bvH</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>san roman miguel</t>
+          <t>vazquez jaime</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>tt4Mm9ws</t>
+          <t>b13gbSqm</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>rueda javier</t>
+          <t>calatrava alex</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>tt4Mm9ws</t>
+          <t>b13gbSqm</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>rueda javier</t>
+          <t>calatrava alex</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>lAgIB16T</t>
+          <t>MXMTbTjl</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>alvaro</t>
+          <t>de miguel jesus</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>4SRz95Sf</t>
+          <t>CUPz0tB5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>alcedo juan</t>
+          <t>van den belt thomas</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>4SRz95Sf</t>
+          <t>CUPz0tB5</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>alcedo juan</t>
+          <t>van den belt thomas</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>nsEvRNJH</t>
+          <t>Oz4LFsdm</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>costa jaume</t>
+          <t>gil oscar</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>U3NYWaPL</t>
+          <t>Eg6LHAo8</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>lazo jose carlos</t>
+          <t>suero israel</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>U3NYWaPL</t>
+          <t>Eg6LHAo8</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
-          <t>lazo jose carlos</t>
+          <t>suero israel</t>
         </is>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>0zIF6Wg2</t>
+          <t>63JPjZot</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>fidel</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr">
-        <is>
-          <t>tdCq3gMJ</t>
-        </is>
-      </c>
-      <c r="DG7" t="inlineStr">
-        <is>
-          <t>agus medina</t>
-        </is>
-      </c>
-      <c r="DH7" t="inlineStr">
-        <is>
-          <t>tdCq3gMJ</t>
-        </is>
-      </c>
-      <c r="DI7" t="inlineStr">
-        <is>
-          <t>agus medina</t>
-        </is>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>Y7vZ4xCl</t>
-        </is>
-      </c>
-      <c r="DK7" t="inlineStr">
-        <is>
-          <t>morcillo jon</t>
-        </is>
-      </c>
-      <c r="DL7" t="inlineStr">
-        <is>
-          <t>ziGOv0PB</t>
-        </is>
-      </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>pacheco antonio</t>
-        </is>
-      </c>
-      <c r="DN7" t="inlineStr">
-        <is>
-          <t>ziGOv0PB</t>
-        </is>
-      </c>
-      <c r="DO7" t="inlineStr">
-        <is>
-          <t>pacheco antonio</t>
-        </is>
-      </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>OCmIC7xi</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>garcia juanma</t>
-        </is>
-      </c>
+          <t>seuntjens mats</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="inlineStr"/>
+      <c r="DM7" t="inlineStr"/>
+      <c r="DN7" t="inlineStr"/>
+      <c r="DO7" t="inlineStr"/>
+      <c r="DP7" t="inlineStr"/>
+      <c r="DQ7" t="inlineStr"/>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>tzAxVrkH</t>
+          <t>rVt0F12N</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
         <is>
-          <t>alvarez agustin</t>
+          <t>cazorla santi</t>
         </is>
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>tzAxVrkH</t>
+          <t>rVt0F12N</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
         <is>
-          <t>alvarez agustin</t>
+          <t>cazorla santi</t>
         </is>
       </c>
       <c r="DV7" t="inlineStr">
         <is>
-          <t>pdMGox1K</t>
+          <t>YeImVH7d</t>
         </is>
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>boayar adam</t>
+          <t>dotor carlos</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>SY7HnwqR</t>
+          <t>O608W9Wj</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>diaby bambo</t>
+          <t>mascarenhas francisco</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>SY7HnwqR</t>
+          <t>O608W9Wj</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>diaby bambo</t>
+          <t>mascarenhas francisco</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>bqApK6mO</t>
+          <t>GODeIoHH</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>mario gaspar</t>
+          <t>hassan haissem</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>27MtyaII</t>
+          <t>KhzzCbCU</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>el ghezouani mourad</t>
+          <t>de la fuente pau</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>27MtyaII</t>
+          <t>KhzzCbCU</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>el ghezouani mourad</t>
+          <t>de la fuente pau</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>lhUwqUHS</t>
+          <t>l88RYMiD</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
         <is>
-          <t>plano oscar</t>
+          <t>moyano francisco</t>
         </is>
       </c>
       <c r="EJ7" t="inlineStr">
         <is>
-          <t>G4s5mw5N</t>
+          <t>GxH7SxPr</t>
         </is>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>josan</t>
+          <t>paraschiv daniel george</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>G4s5mw5N</t>
+          <t>GxH7SxPr</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
         <is>
-          <t>josan</t>
+          <t>paraschiv daniel george</t>
         </is>
       </c>
       <c r="EN7" t="inlineStr">
         <is>
-          <t>IylSu6Jk</t>
+          <t>ljVRztTj</t>
         </is>
       </c>
       <c r="EO7" t="inlineStr">
         <is>
-          <t>febas aleix</t>
+          <t>alemao</t>
         </is>
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>YNiXFzek</t>
+          <t>bD41lxAF</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>mendoza rodrigo</t>
+          <t>costas david</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>YNiXFzek</t>
+          <t>bD41lxAF</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>mendoza rodrigo</t>
+          <t>costas david</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>jkeA7fag</t>
+          <t>vg9tJMbL</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
         <is>
-          <t>barzic matia</t>
+          <t>sibo kwasi</t>
         </is>
       </c>
       <c r="EV7" t="inlineStr"/>
@@ -6039,1552 +5895,10 @@
       <c r="FC7" t="inlineStr"/>
       <c r="FD7" t="inlineStr"/>
       <c r="FE7" t="inlineStr"/>
-      <c r="FF7" t="inlineStr">
-        <is>
-          <t>p6Ky2D9n</t>
-        </is>
-      </c>
-      <c r="FG7" t="inlineStr">
-        <is>
-          <t>touaizi nabil</t>
-        </is>
-      </c>
+      <c r="FF7" t="inlineStr"/>
+      <c r="FG7" t="inlineStr"/>
       <c r="FH7" t="inlineStr"/>
       <c r="FI7" t="inlineStr"/>
-      <c r="FJ7" t="inlineStr"/>
-      <c r="FK7" t="inlineStr"/>
-      <c r="FL7" t="inlineStr"/>
-      <c r="FM7" t="inlineStr"/>
-      <c r="FN7" t="inlineStr"/>
-      <c r="FO7" t="inlineStr"/>
-      <c r="FP7" t="inlineStr"/>
-      <c r="FQ7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jBnLKPNO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>46MITnQj</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>herrero alfonso</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>d0cy0VJH</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>puga carlos</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>zoUoVMHM</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>pastor alex</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>nqdEHSMq</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>galilea einar</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>WYY1lfvc</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>garcia victor</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hWytXuuP</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>larrubia david</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>x2yeSVsN</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>molina manuel</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Sbu7wJf2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>juanpe</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>dYhjJbao</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>villodres kevin</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>bwOobz6e</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>baturina roko</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>zJKzpcZ2</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>lorenzo guerrero daniel</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>8Ui4Uj3f</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>fernandez raul</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>IsnTW9M8</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>gutierrez juan</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>pGFgjhdA</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>postigo sergio</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>O2ZB51wk</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>tomeo pablo</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>rBfMulYr</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>rincon lumbreras hugo</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>d4Ngmj4o</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>lachuer mathis</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>QkiaT3F6</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>tachi</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>faenCRar</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>gorrotxategi jon</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>Iw3Th1z9</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>alonso sosa julio</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>SSL080TM</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>panichelli joaquin</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>rFSzAZrl</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>reina alberto</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>YsYtFhZ9</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>abaida haitam</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>tQQcMsFa</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>cordero antonio</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>CfduQMtk</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>dioni</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>KEhgZM7C</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>gabilondo jokin</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>bqRE7w3c</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>lobete julen</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>nPtLZN7K</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>lopez carlos</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>x8QCalTA</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>luismi</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>vPYNTnQ5</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>merino izan</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>4z4O5z5A</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>murillo diego</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>OlIJGJpI</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>ochoa aaron</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>vZSESiem</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>sanchez daniel</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>ClaYwZZA</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>calvo alejandro</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>niNE1O1d</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>garcia alberto</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>n7WLyvsf</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>gonzalez victor parada</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>dli7hlod</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>homenchenko santiago</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>E1UCv80p</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>urko iruretagoiena</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>v5HKEYQm</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>lopez luis</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>GnRv5VCn</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>ortiz asier</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>WGvUbvMF</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>casals</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>n77thmF8</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>rosales diego</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr"/>
-      <c r="CI8" t="inlineStr"/>
-      <c r="CJ8" t="inlineStr"/>
-      <c r="CK8" t="inlineStr"/>
-      <c r="CL8" t="inlineStr"/>
-      <c r="CM8" t="inlineStr"/>
-      <c r="CN8" t="inlineStr">
-        <is>
-          <t>bqRE7w3c</t>
-        </is>
-      </c>
-      <c r="CO8" t="inlineStr">
-        <is>
-          <t>lobete julen</t>
-        </is>
-      </c>
-      <c r="CP8" t="inlineStr">
-        <is>
-          <t>bqRE7w3c</t>
-        </is>
-      </c>
-      <c r="CQ8" t="inlineStr">
-        <is>
-          <t>lobete julen</t>
-        </is>
-      </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>dYhjJbao</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>villodres kevin</t>
-        </is>
-      </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>OlIJGJpI</t>
-        </is>
-      </c>
-      <c r="CU8" t="inlineStr">
-        <is>
-          <t>ochoa aaron</t>
-        </is>
-      </c>
-      <c r="CV8" t="inlineStr">
-        <is>
-          <t>OlIJGJpI</t>
-        </is>
-      </c>
-      <c r="CW8" t="inlineStr">
-        <is>
-          <t>ochoa aaron</t>
-        </is>
-      </c>
-      <c r="CX8" t="inlineStr">
-        <is>
-          <t>Sbu7wJf2</t>
-        </is>
-      </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>juanpe</t>
-        </is>
-      </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>CfduQMtk</t>
-        </is>
-      </c>
-      <c r="DA8" t="inlineStr">
-        <is>
-          <t>dioni</t>
-        </is>
-      </c>
-      <c r="DB8" t="inlineStr">
-        <is>
-          <t>CfduQMtk</t>
-        </is>
-      </c>
-      <c r="DC8" t="inlineStr">
-        <is>
-          <t>dioni</t>
-        </is>
-      </c>
-      <c r="DD8" t="inlineStr">
-        <is>
-          <t>bwOobz6e</t>
-        </is>
-      </c>
-      <c r="DE8" t="inlineStr">
-        <is>
-          <t>baturina roko</t>
-        </is>
-      </c>
-      <c r="DF8" t="inlineStr">
-        <is>
-          <t>tQQcMsFa</t>
-        </is>
-      </c>
-      <c r="DG8" t="inlineStr">
-        <is>
-          <t>cordero antonio</t>
-        </is>
-      </c>
-      <c r="DH8" t="inlineStr">
-        <is>
-          <t>tQQcMsFa</t>
-        </is>
-      </c>
-      <c r="DI8" t="inlineStr">
-        <is>
-          <t>cordero antonio</t>
-        </is>
-      </c>
-      <c r="DJ8" t="inlineStr">
-        <is>
-          <t>hWytXuuP</t>
-        </is>
-      </c>
-      <c r="DK8" t="inlineStr">
-        <is>
-          <t>larrubia david</t>
-        </is>
-      </c>
-      <c r="DL8" t="inlineStr">
-        <is>
-          <t>YsYtFhZ9</t>
-        </is>
-      </c>
-      <c r="DM8" t="inlineStr">
-        <is>
-          <t>abaida haitam</t>
-        </is>
-      </c>
-      <c r="DN8" t="inlineStr">
-        <is>
-          <t>YsYtFhZ9</t>
-        </is>
-      </c>
-      <c r="DO8" t="inlineStr">
-        <is>
-          <t>abaida haitam</t>
-        </is>
-      </c>
-      <c r="DP8" t="inlineStr">
-        <is>
-          <t>bqRE7w3c</t>
-        </is>
-      </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>lobete julen</t>
-        </is>
-      </c>
-      <c r="DR8" t="inlineStr">
-        <is>
-          <t>dli7hlod</t>
-        </is>
-      </c>
-      <c r="DS8" t="inlineStr">
-        <is>
-          <t>homenchenko santiago</t>
-        </is>
-      </c>
-      <c r="DT8" t="inlineStr">
-        <is>
-          <t>dli7hlod</t>
-        </is>
-      </c>
-      <c r="DU8" t="inlineStr">
-        <is>
-          <t>homenchenko santiago</t>
-        </is>
-      </c>
-      <c r="DV8" t="inlineStr">
-        <is>
-          <t>QkiaT3F6</t>
-        </is>
-      </c>
-      <c r="DW8" t="inlineStr">
-        <is>
-          <t>tachi</t>
-        </is>
-      </c>
-      <c r="DX8" t="inlineStr">
-        <is>
-          <t>E1UCv80p</t>
-        </is>
-      </c>
-      <c r="DY8" t="inlineStr">
-        <is>
-          <t>urko iruretagoiena</t>
-        </is>
-      </c>
-      <c r="DZ8" t="inlineStr">
-        <is>
-          <t>E1UCv80p</t>
-        </is>
-      </c>
-      <c r="EA8" t="inlineStr">
-        <is>
-          <t>urko iruretagoiena</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
-        <is>
-          <t>SSL080TM</t>
-        </is>
-      </c>
-      <c r="EC8" t="inlineStr">
-        <is>
-          <t>panichelli joaquin</t>
-        </is>
-      </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>WGvUbvMF</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>casals</t>
-        </is>
-      </c>
-      <c r="EF8" t="inlineStr">
-        <is>
-          <t>WGvUbvMF</t>
-        </is>
-      </c>
-      <c r="EG8" t="inlineStr">
-        <is>
-          <t>casals</t>
-        </is>
-      </c>
-      <c r="EH8" t="inlineStr">
-        <is>
-          <t>faenCRar</t>
-        </is>
-      </c>
-      <c r="EI8" t="inlineStr">
-        <is>
-          <t>gorrotxategi jon</t>
-        </is>
-      </c>
-      <c r="EJ8" t="inlineStr">
-        <is>
-          <t>n7WLyvsf</t>
-        </is>
-      </c>
-      <c r="EK8" t="inlineStr">
-        <is>
-          <t>gonzalez victor parada</t>
-        </is>
-      </c>
-      <c r="EL8" t="inlineStr">
-        <is>
-          <t>n7WLyvsf</t>
-        </is>
-      </c>
-      <c r="EM8" t="inlineStr">
-        <is>
-          <t>gonzalez victor parada</t>
-        </is>
-      </c>
-      <c r="EN8" t="inlineStr">
-        <is>
-          <t>pGFgjhdA</t>
-        </is>
-      </c>
-      <c r="EO8" t="inlineStr">
-        <is>
-          <t>postigo sergio</t>
-        </is>
-      </c>
-      <c r="EP8" t="inlineStr">
-        <is>
-          <t>ClaYwZZA</t>
-        </is>
-      </c>
-      <c r="EQ8" t="inlineStr">
-        <is>
-          <t>calvo alejandro</t>
-        </is>
-      </c>
-      <c r="ER8" t="inlineStr">
-        <is>
-          <t>ClaYwZZA</t>
-        </is>
-      </c>
-      <c r="ES8" t="inlineStr">
-        <is>
-          <t>calvo alejandro</t>
-        </is>
-      </c>
-      <c r="ET8" t="inlineStr">
-        <is>
-          <t>d4Ngmj4o</t>
-        </is>
-      </c>
-      <c r="EU8" t="inlineStr">
-        <is>
-          <t>lachuer mathis</t>
-        </is>
-      </c>
-      <c r="EV8" t="inlineStr"/>
-      <c r="EW8" t="inlineStr"/>
-      <c r="EX8" t="inlineStr"/>
-      <c r="EY8" t="inlineStr"/>
-      <c r="EZ8" t="inlineStr"/>
-      <c r="FA8" t="inlineStr"/>
-      <c r="FB8" t="inlineStr"/>
-      <c r="FC8" t="inlineStr"/>
-      <c r="FD8" t="inlineStr"/>
-      <c r="FE8" t="inlineStr"/>
-      <c r="FF8" t="inlineStr">
-        <is>
-          <t>MqP5Tzz4</t>
-        </is>
-      </c>
-      <c r="FG8" t="inlineStr">
-        <is>
-          <t>sangalli luca</t>
-        </is>
-      </c>
-      <c r="FH8" t="inlineStr"/>
-      <c r="FI8" t="inlineStr"/>
-      <c r="FJ8" t="inlineStr"/>
-      <c r="FK8" t="inlineStr"/>
-      <c r="FL8" t="inlineStr"/>
-      <c r="FM8" t="inlineStr"/>
-      <c r="FN8" t="inlineStr"/>
-      <c r="FO8" t="inlineStr"/>
-      <c r="FP8" t="inlineStr"/>
-      <c r="FQ8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>QHtUvT8t</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>63syan4K</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>nadal tomeu</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Of2PA2Td</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>mellot jeremy</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AupfG8yP</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>juande</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>MHMBJsTD</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>leon jose</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>MiNhvPQS</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>medrano fernando</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>zXy8vKe2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>cruz luismi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>tpszulN9</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>diarra youssouf</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>G87TNXSP</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>gonzalez sergio</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>ngNLVMtM</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>rubio waldo</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>MZYiJsf5</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>rodriguez angel</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>vmSOV0qD</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>mesa maikel</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>lfgji9jR</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>maximiano luis</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>lEgtMYw4</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>pozo alejandro</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0KsyLPE4</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>chumi</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>Eks5aVRG</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>kaiky</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>hrUwhqn3</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>centelles alex</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>pCJBsskE</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>gonzalez edgar</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>nN06Zcrh</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>melero gonzalo</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>OMxL6tQB</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>puigmal arnau</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>GIzJfhLr</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>arribas sergio</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>U1OOFFBl</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>ribaudo nico</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>fV4fAvB8</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>suarez luis</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>YDX3HtAo</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>gonzalez ruben</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>bXfFubxl</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>bodiger yann</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>WOsowK7D</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>cantero alejandro</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>th9dk6j8</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>montanez carrasco salvador</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>zwpagAwR</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>corredera alex</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>zc8vwd36</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>gallego enric</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>KfbbZ1xQ</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>gaya josep</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>MeRdZHGT</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>guerrero adrian</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>4OJxMhNq</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>manjam alassan</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>UqQAKe7t</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>david rodriguez ramos</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>nHp3CHac</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>senhadji yanis</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>8YnlOgwC</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>baba iddrisu</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0M5sG7Bk</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>fettal rachad</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>nJ9VW6i9</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>gomez valen</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>lh0DDoRr</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>guedes guilherme</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>fDlwwgkH</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>iribarne bruno</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>8xxQPuzJ</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>langa bruno alberto</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>nHPmbQaR</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>lopy dion</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>Y9vWlK55</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>milovanovic marko</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>EJs3SlPl</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>fernando</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>j9EcJFsj</t>
-        </is>
-      </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>montes cesar</t>
-        </is>
-      </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>df21B0le</t>
-        </is>
-      </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>pena marcos</t>
-        </is>
-      </c>
-      <c r="CL9" t="inlineStr">
-        <is>
-          <t>jDh6SEKj</t>
-        </is>
-      </c>
-      <c r="CM9" t="inlineStr">
-        <is>
-          <t>radovanovic aleksandar</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr">
-        <is>
-          <t>UqQAKe7t</t>
-        </is>
-      </c>
-      <c r="CO9" t="inlineStr">
-        <is>
-          <t>david rodriguez ramos</t>
-        </is>
-      </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>UqQAKe7t</t>
-        </is>
-      </c>
-      <c r="CQ9" t="inlineStr">
-        <is>
-          <t>david rodriguez ramos</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>MiNhvPQS</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>medrano fernando</t>
-        </is>
-      </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>bXfFubxl</t>
-        </is>
-      </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>bodiger yann</t>
-        </is>
-      </c>
-      <c r="CV9" t="inlineStr">
-        <is>
-          <t>bXfFubxl</t>
-        </is>
-      </c>
-      <c r="CW9" t="inlineStr">
-        <is>
-          <t>bodiger yann</t>
-        </is>
-      </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>G87TNXSP</t>
-        </is>
-      </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>gonzalez sergio</t>
-        </is>
-      </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>YDX3HtAo</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>gonzalez ruben</t>
-        </is>
-      </c>
-      <c r="DB9" t="inlineStr">
-        <is>
-          <t>YDX3HtAo</t>
-        </is>
-      </c>
-      <c r="DC9" t="inlineStr">
-        <is>
-          <t>gonzalez ruben</t>
-        </is>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>tpszulN9</t>
-        </is>
-      </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>diarra youssouf</t>
-        </is>
-      </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>WOsowK7D</t>
-        </is>
-      </c>
-      <c r="DG9" t="inlineStr">
-        <is>
-          <t>cantero alejandro</t>
-        </is>
-      </c>
-      <c r="DH9" t="inlineStr">
-        <is>
-          <t>WOsowK7D</t>
-        </is>
-      </c>
-      <c r="DI9" t="inlineStr">
-        <is>
-          <t>cantero alejandro</t>
-        </is>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>vmSOV0qD</t>
-        </is>
-      </c>
-      <c r="DK9" t="inlineStr">
-        <is>
-          <t>mesa maikel</t>
-        </is>
-      </c>
-      <c r="DL9" t="inlineStr">
-        <is>
-          <t>zwpagAwR</t>
-        </is>
-      </c>
-      <c r="DM9" t="inlineStr">
-        <is>
-          <t>corredera alex</t>
-        </is>
-      </c>
-      <c r="DN9" t="inlineStr">
-        <is>
-          <t>zwpagAwR</t>
-        </is>
-      </c>
-      <c r="DO9" t="inlineStr">
-        <is>
-          <t>corredera alex</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>MZYiJsf5</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>rodriguez angel</t>
-        </is>
-      </c>
-      <c r="DR9" t="inlineStr">
-        <is>
-          <t>nHPmbQaR</t>
-        </is>
-      </c>
-      <c r="DS9" t="inlineStr">
-        <is>
-          <t>lopy dion</t>
-        </is>
-      </c>
-      <c r="DT9" t="inlineStr">
-        <is>
-          <t>nHPmbQaR</t>
-        </is>
-      </c>
-      <c r="DU9" t="inlineStr">
-        <is>
-          <t>lopy dion</t>
-        </is>
-      </c>
-      <c r="DV9" t="inlineStr">
-        <is>
-          <t>Eks5aVRG</t>
-        </is>
-      </c>
-      <c r="DW9" t="inlineStr">
-        <is>
-          <t>kaiky</t>
-        </is>
-      </c>
-      <c r="DX9" t="inlineStr">
-        <is>
-          <t>8xxQPuzJ</t>
-        </is>
-      </c>
-      <c r="DY9" t="inlineStr">
-        <is>
-          <t>langa bruno alberto</t>
-        </is>
-      </c>
-      <c r="DZ9" t="inlineStr">
-        <is>
-          <t>8xxQPuzJ</t>
-        </is>
-      </c>
-      <c r="EA9" t="inlineStr">
-        <is>
-          <t>langa bruno alberto</t>
-        </is>
-      </c>
-      <c r="EB9" t="inlineStr">
-        <is>
-          <t>OMxL6tQB</t>
-        </is>
-      </c>
-      <c r="EC9" t="inlineStr">
-        <is>
-          <t>puigmal arnau</t>
-        </is>
-      </c>
-      <c r="ED9" t="inlineStr">
-        <is>
-          <t>8YnlOgwC</t>
-        </is>
-      </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>baba iddrisu</t>
-        </is>
-      </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>8YnlOgwC</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
-        <is>
-          <t>baba iddrisu</t>
-        </is>
-      </c>
-      <c r="EH9" t="inlineStr">
-        <is>
-          <t>nN06Zcrh</t>
-        </is>
-      </c>
-      <c r="EI9" t="inlineStr">
-        <is>
-          <t>melero gonzalo</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>nJ9VW6i9</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr">
-        <is>
-          <t>gomez valen</t>
-        </is>
-      </c>
-      <c r="EL9" t="inlineStr">
-        <is>
-          <t>nJ9VW6i9</t>
-        </is>
-      </c>
-      <c r="EM9" t="inlineStr">
-        <is>
-          <t>gomez valen</t>
-        </is>
-      </c>
-      <c r="EN9" t="inlineStr">
-        <is>
-          <t>GIzJfhLr</t>
-        </is>
-      </c>
-      <c r="EO9" t="inlineStr">
-        <is>
-          <t>arribas sergio</t>
-        </is>
-      </c>
-      <c r="EP9" t="inlineStr"/>
-      <c r="EQ9" t="inlineStr"/>
-      <c r="ER9" t="inlineStr"/>
-      <c r="ES9" t="inlineStr"/>
-      <c r="ET9" t="inlineStr"/>
-      <c r="EU9" t="inlineStr"/>
-      <c r="EV9" t="inlineStr"/>
-      <c r="EW9" t="inlineStr"/>
-      <c r="EX9" t="inlineStr"/>
-      <c r="EY9" t="inlineStr"/>
-      <c r="EZ9" t="inlineStr"/>
-      <c r="FA9" t="inlineStr"/>
-      <c r="FB9" t="inlineStr"/>
-      <c r="FC9" t="inlineStr"/>
-      <c r="FD9" t="inlineStr"/>
-      <c r="FE9" t="inlineStr"/>
-      <c r="FF9" t="inlineStr">
-        <is>
-          <t>t4ZOn0H3</t>
-        </is>
-      </c>
-      <c r="FG9" t="inlineStr">
-        <is>
-          <t>teto</t>
-        </is>
-      </c>
-      <c r="FH9" t="inlineStr"/>
-      <c r="FI9" t="inlineStr"/>
-      <c r="FJ9" t="inlineStr"/>
-      <c r="FK9" t="inlineStr"/>
-      <c r="FL9" t="inlineStr"/>
-      <c r="FM9" t="inlineStr"/>
-      <c r="FN9" t="inlineStr"/>
-      <c r="FO9" t="inlineStr"/>
-      <c r="FP9" t="inlineStr"/>
-      <c r="FQ9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FI7"/>
+  <dimension ref="A1:FS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,2021 +861,2091 @@
       </c>
       <c r="CJ1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_away_10</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_10</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_11</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_11</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_12</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_12</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pIgzAKRr</t>
+          <t>25zBQ1q4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>roman leonardo</t>
+          <t>cillessen jasper</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KvHXl88g</t>
+          <t>SjTBQO7b</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>maffeo pablo</t>
+          <t>park marvin</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pbb8dhGG</t>
+          <t>fBI7cV4b</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>valjent martin</t>
+          <t>alex suarez</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>p8RSvp74</t>
+          <t>AerDGNDO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>raillo antonio</t>
+          <t>mckenna scott</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>drRlRNNC</t>
+          <t>Cz3awDFR</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>mojica johan</t>
+          <t>marmol mika</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>AXPRNqQn</t>
+          <t>KE0WWa1e</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>costa samuel</t>
+          <t>campana jose</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>nerrfVfR</t>
+          <t>OKNQawg3</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>morlanes manu</t>
+          <t>kirian</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>On7NYLWr</t>
+          <t>lQJaaIBC</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>darder sergi</t>
+          <t>munoz javier</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>pSceH9EI</t>
+          <t>b5g6gWjn</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>sanchez antonio</t>
+          <t>moleiro alberto</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CjwNDgqi</t>
+          <t>rNFSg6i4</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>muriqi vedat</t>
+          <t>mcburnie oliver</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>vNpXFtuQ</t>
+          <t>fapXP9VS</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>larin cyle</t>
+          <t>ramirez sandro</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>UJ9btoDi</t>
+          <t>MVExOq3n</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>nyland orjan</t>
+          <t>courtois thibaut</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dE2MbgQ4</t>
+          <t>pEjBDsSH</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>carmona jose angel</t>
+          <t>lucas</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>YgxuEfvL</t>
+          <t>zX2Rm9YG</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>bade loic</t>
+          <t>militao eder</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>SKLFEpf6</t>
+          <t>rZHXvTho</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>gudelj nemanja</t>
+          <t>rudiger antonio</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>t4j4NUO8</t>
+          <t>KnytnSKl</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>pedrosa adria</t>
+          <t>mendy ferland</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>tUNr1qOE</t>
+          <t>nscfER6B</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>sow djibril</t>
+          <t>valverde federico</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>fefkCPrH</t>
+          <t>QkiZum3e</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>lokonga sambi</t>
+          <t>tchouameni aurelien</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>hSbvVwW7</t>
+          <t>bZWyoJnA</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>niguez saul</t>
+          <t>modric luka</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>08a9jhm9</t>
+          <t>nm2Qvnyk</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>lukebakio dodi</t>
+          <t>diaz brahim</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>dIaES012</t>
+          <t>Wn6E2SED</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>iheanacho kelechi</t>
+          <t>mbappe kylian</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>8zvngfOe</t>
+          <t>CbwQ4Mws</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>ejuke chidera</t>
+          <t>vinicius junior</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>lrscbe6I</t>
+          <t>A16UgbkJ</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>asano takuma</t>
+          <t>bassinga aboubacar</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>ABXxQRR6</t>
+          <t>AkH99Ojn</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>arias copete jose manuel</t>
+          <t>cardona marc</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>xUwdHPXa</t>
+          <t>UaHeoBot</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>domenech marc</t>
+          <t>fuster manuel</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>ID9k7lap</t>
+          <t>jTdCpLmR</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>greif dominik</t>
+          <t>gil ivan</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>hCPqc747</t>
+          <t>fgqxKdwL</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>lato toni</t>
+          <t>gonzalez fabio</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>bkeWsRZc</t>
+          <t>xrJQVv9C</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>luna daniel</t>
+          <t>herzog juanma</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>vJSVZFpR</t>
+          <t>YVDjJMt4</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>mascarell omar</t>
+          <t>killane alvaro</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>lx119mnI</t>
+          <t>px36Cwpj</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>cuellar ivan</t>
+          <t>loiodice enzo</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>zB1s0lKl</t>
+          <t>r92RZve6</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>prats abdon</t>
+          <t>mata jaime</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>n7jmYVFc</t>
+          <t>xlaNl83K</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>rodriguez daniel</t>
+          <t>munoz alex</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>feNCiQzT</t>
+          <t>pjIG0H3d</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>salas jan</t>
+          <t>ramirez benito</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>fToJY0qQ</t>
+          <t>tYi46reg</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>van der heyden siebe</t>
+          <t>viti</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>bmJjJR1B</t>
+          <t>rZh5FTHE</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>agoume lucien</t>
+          <t>carvajal daniel</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>tfywn0Ad</t>
+          <t>zPYmze7F</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>fernandez alvaro</t>
+          <t>ceballos dani</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>SzbPY3Ma</t>
+          <t>bXHrpEJ4</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>flores alberto</t>
+          <t>endrick</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>zRYlzwwb</t>
+          <t>Is0aEgM6</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>idumbo muzambo stanis</t>
+          <t>perez francisco javier gonzalez</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>OOFwBfsT</t>
+          <t>tURBbW9S</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>marcao</t>
+          <t>fran garcia</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>hWt5ZIrn</t>
+          <t>CUU9qDpb</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>navas jesus</t>
+          <t>guler arda</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>zHxpGqc8</t>
+          <t>0S7ye9jr</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>kouassi nianzou</t>
+          <t>lunin andriy</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>GOkrxtHi</t>
+          <t>dIvLWqXc</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>peque</t>
+          <t>naveros jacobo</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>OK0Lcg44</t>
+          <t>zPUyR5Up</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>romero isaac</t>
+          <t>rodrygo</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>6uf4Y1d2</t>
+          <t>pjIG0H3d</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>rooms kike</t>
+          <t>ramirez benito</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>CtN0gVgf</t>
+          <t>pjIG0H3d</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>sanchez juanlu</t>
+          <t>ramirez benito</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>n7jmYVFc</t>
+          <t>b5g6gWjn</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>rodriguez daniel</t>
+          <t>moleiro alberto</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>n7jmYVFc</t>
+          <t>tYi46reg</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>rodriguez daniel</t>
+          <t>viti</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>pSceH9EI</t>
+          <t>tYi46reg</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>sanchez antonio</t>
+          <t>viti</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>lrscbe6I</t>
+          <t>fapXP9VS</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>asano takuma</t>
+          <t>ramirez sandro</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>lrscbe6I</t>
+          <t>r92RZve6</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>asano takuma</t>
+          <t>mata jaime</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>vNpXFtuQ</t>
+          <t>r92RZve6</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>larin cyle</t>
+          <t>mata jaime</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>vJSVZFpR</t>
+          <t>rNFSg6i4</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>mascarell omar</t>
+          <t>mcburnie oliver</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>vJSVZFpR</t>
+          <t>px36Cwpj</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>mascarell omar</t>
+          <t>loiodice enzo</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>nerrfVfR</t>
+          <t>px36Cwpj</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>morlanes manu</t>
+          <t>loiodice enzo</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>xUwdHPXa</t>
+          <t>KE0WWa1e</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>domenech marc</t>
+          <t>campana jose</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>xUwdHPXa</t>
+          <t>UaHeoBot</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>domenech marc</t>
+          <t>fuster manuel</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>On7NYLWr</t>
+          <t>UaHeoBot</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>darder sergi</t>
+          <t>fuster manuel</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>zB1s0lKl</t>
+          <t>OKNQawg3</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>prats abdon</t>
+          <t>kirian</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>zB1s0lKl</t>
+          <t>zPUyR5Up</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>prats abdon</t>
+          <t>rodrygo</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>CjwNDgqi</t>
+          <t>zPUyR5Up</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>muriqi vedat</t>
+          <t>rodrygo</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>OK0Lcg44</t>
+          <t>nm2Qvnyk</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>romero isaac</t>
+          <t>diaz brahim</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>OK0Lcg44</t>
+          <t>tURBbW9S</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>romero isaac</t>
+          <t>fran garcia</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>dIaES012</t>
+          <t>tURBbW9S</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>iheanacho kelechi</t>
+          <t>fran garcia</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>CtN0gVgf</t>
+          <t>KnytnSKl</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>sanchez juanlu</t>
+          <t>mendy ferland</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>CtN0gVgf</t>
+          <t>CUU9qDpb</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>sanchez juanlu</t>
+          <t>guler arda</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>fefkCPrH</t>
+          <t>CUU9qDpb</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>lokonga sambi</t>
+          <t>guler arda</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>hWt5ZIrn</t>
+          <t>bZWyoJnA</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>navas jesus</t>
+          <t>modric luka</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>hWt5ZIrn</t>
+          <t>rZh5FTHE</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>navas jesus</t>
+          <t>carvajal daniel</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>08a9jhm9</t>
+          <t>rZh5FTHE</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>lukebakio dodi</t>
+          <t>carvajal daniel</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>OOFwBfsT</t>
+          <t>pEjBDsSH</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>marcao</t>
+          <t>lucas</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>OOFwBfsT</t>
+          <t>bXHrpEJ4</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>marcao</t>
+          <t>endrick</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>SKLFEpf6</t>
+          <t>bXHrpEJ4</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>gudelj nemanja</t>
+          <t>endrick</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>bmJjJR1B</t>
+          <t>CbwQ4Mws</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>agoume lucien</t>
+          <t>vinicius junior</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>bmJjJR1B</t>
+          <t>6qyeYCYO</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>agoume lucien</t>
+          <t>januzaj adnan</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>8zvngfOe</t>
+          <t>St8XPCaD</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>ejuke chidera</t>
+          <t>pejino</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>Ew10Xoy6</t>
+          <t>hKx3nCTp</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>llabres javier</t>
+          <t>alaba david</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>jRBXx0H4</t>
+          <t>QNvlPm7s</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>morey mateu</t>
+          <t>bellingham jude</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>rN9tdN16</t>
+          <t>6ekYsPfO</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>montiel gonzalo</t>
+          <t>camavinga eduardo</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>2s2ATpKI</t>
+          <t>WSRdoQ7I</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>ocampos lucas</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>Aexbrioc</t>
-        </is>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>suso</t>
-        </is>
-      </c>
+          <t>vallejo jesus</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
       <c r="FF2" t="inlineStr"/>
       <c r="FG2" t="inlineStr"/>
       <c r="FH2" t="inlineStr"/>
       <c r="FI2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
+      <c r="FL2" t="inlineStr"/>
+      <c r="FM2" t="inlineStr"/>
+      <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="inlineStr"/>
+      <c r="FP2" t="inlineStr"/>
+      <c r="FQ2" t="inlineStr"/>
+      <c r="FR2" t="inlineStr"/>
+      <c r="FS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GMOMNJbs</t>
+          <t>jB3F3wGi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>conde diego</t>
+          <t>gazzaniga paulo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ryjofHOu</t>
+          <t>OjpPzOu0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kiko</t>
+          <t>frances alejandro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AkMslDtA</t>
+          <t>250rn438</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>albiol raul</t>
+          <t>lopez david</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>G8VcNrxU</t>
+          <t>U5mPqlh6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>bailly eric</t>
+          <t>blind daley</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>vVh7yy15</t>
+          <t>z9xliwUd</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>cardona sergi</t>
+          <t>gutierrez miguel</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8fnHDvMe</t>
+          <t>8l99epoQ</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>santos yeremi</t>
+          <t>tsygankov viktor</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>KK4TPIBj</t>
+          <t>tzwJ3As6</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>comesana santi</t>
+          <t>herrera yangel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>z7YvfLZ8</t>
+          <t>vLPRaVJo</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>parejo daniel</t>
+          <t>martin ivan</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>bmeQTB92</t>
+          <t>xSXBYlvl</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>baena alex</t>
+          <t>gil bryan</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>UwfDD083</t>
+          <t>EauanyEm</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>moreno gerard</t>
+          <t>ruiz abel</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>tYV4tvqr</t>
+          <t>2ZExqRk3</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>groeneveld arnaut</t>
+          <t>miovski bojan</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>IRro97ls</t>
+          <t>YDyOrTQO</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>villar ivan</t>
+          <t>herrera sergio</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8bvxeNAG</t>
+          <t>tCpvIBRC</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>manquillo javier</t>
+          <t>vidal nacho</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ptNHGRiJ</t>
+          <t>vqO0hBvp</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>starfelt carl</t>
+          <t>catena alejandro</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>ITqxsbsR</t>
+          <t>b7V04HCM</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>jailson</t>
+          <t>herrando jorge</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>rHUdQZPd</t>
+          <t>fmw1xiyC</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>carreira sergio</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>MoAntFV8</t>
+          <t>8b86g1el</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>kourouma moriba</t>
+          <t>gomez moi</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>IR1ghK3I</t>
+          <t>6y9ES72S</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>rodriguez damian</t>
+          <t>torro lucas</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>YkHSwt2b</t>
+          <t>SlzBPHAH</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>mingueza oscar</t>
+          <t>oroz aimar</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>IXim7pWh</t>
+          <t>KCtH4oIT</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>gonzalez alfonso</t>
+          <t>moncayola jon</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>n9uHpbM8</t>
+          <t>IeVXGQOi</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>bamba jonathan</t>
+          <t>budimir ante</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0vQciH42</t>
+          <t>hQyTbdVL</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>iglesias borja</t>
+          <t>zaragoza bryan</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>ATAVnRY7</t>
+          <t>lnGG8RDp</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>akhomach ilias</t>
+          <t>asprilla yaser</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>KYQuxWEL</t>
+          <t>n1iE7ch5</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>barry thierno</t>
+          <t>juan carlos</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>EL0WleP6</t>
+          <t>GbY2OPWp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>costa logan</t>
+          <t>juanpe</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>p6rsDQvN</t>
+          <t>nZ8SVvvE</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>gueye pape</t>
+          <t>krejci ladislav</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>WShuFWRi</t>
+          <t>rZes9CKA</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>junior reis</t>
+          <t>lopez pau</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>S6QWzDng</t>
+          <t>UTk2FzpS</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>kambwala willy</t>
+          <t>martinez arnau</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>bwHQNPyE</t>
+          <t>2e75edda</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>navarro pablo</t>
+          <t>misehouy gabriel osei</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>j3Hk0qEj</t>
+          <t>n5xqpcKc</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>pepe nicolas</t>
+          <t>portu</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>jVHfHxGn</t>
+          <t>WCC5IrWg</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>perez ayoze</t>
+          <t>romeu oriol</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>Kjmmf9C3</t>
+          <t>CxVKphX0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>sola arnau</t>
+          <t>solis jhon</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>rLsgetTF</t>
+          <t>U5yv9YBB</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>terrats ramon</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
+          <t>stuani christian</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>bs2gvblF</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>van de beek donny</t>
+        </is>
+      </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>AVpwhNL9</t>
+          <t>rPdVeI18</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>aidoo joseph</t>
+          <t>areso jesus</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>nyLFv8t3</t>
+          <t>8psoD6vm</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>alvarez hugo</t>
+          <t>arnaiz jose</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>rVBGggAd</t>
+          <t>ObepFC6G</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>aspas iago</t>
+          <t>benito iker</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>zykz5SJb</t>
+          <t>4rC8UP44</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>beltran francisco</t>
+          <t>bertones abel</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>f79qYNc4</t>
+          <t>htdKMO9m</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>dominguez carlos</t>
+          <t>fernandez aitor</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>YgPGkQYi</t>
+          <t>2HT2pDXL</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>douvikas anastasios</t>
+          <t>de haro raul</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>b7lKkJBn</t>
+          <t>Gpc9AB61</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>duran pablo</t>
+          <t>garcia ruben</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>Au7zDEEL</t>
+          <t>KShEvv1N</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>guaita vicente</t>
+          <t>garcia unai</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>bsZTFhAa</t>
+          <t>xOWXxrsi</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>rodriguez galiano javier</t>
+          <t>ibanez pablo</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>tGJYwtjh</t>
+          <t>WCC5IrWg</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>sotelo hugo</t>
+          <t>romeu oriol</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>KluZeL4G</t>
+          <t>WCC5IrWg</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>swedberg williot</t>
+          <t>romeu oriol</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>jVHfHxGn</t>
+          <t>tzwJ3As6</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>perez ayoze</t>
+          <t>herrera yangel</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>jVHfHxGn</t>
+          <t>U5yv9YBB</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>perez ayoze</t>
+          <t>stuani christian</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>UwfDD083</t>
+          <t>U5yv9YBB</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>moreno gerard</t>
+          <t>stuani christian</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>EL0WleP6</t>
+          <t>2ZExqRk3</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>costa logan</t>
+          <t>miovski bojan</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>EL0WleP6</t>
+          <t>lnGG8RDp</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>costa logan</t>
+          <t>asprilla yaser</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>G8VcNrxU</t>
+          <t>lnGG8RDp</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>bailly eric</t>
+          <t>asprilla yaser</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>j3Hk0qEj</t>
+          <t>EauanyEm</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>pepe nicolas</t>
+          <t>ruiz abel</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>j3Hk0qEj</t>
+          <t>bs2gvblF</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>pepe nicolas</t>
+          <t>van de beek donny</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>8fnHDvMe</t>
+          <t>bs2gvblF</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>santos yeremi</t>
+          <t>van de beek donny</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>KYQuxWEL</t>
+          <t>xSXBYlvl</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>barry thierno</t>
+          <t>gil bryan</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>KYQuxWEL</t>
+          <t>n5xqpcKc</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>barry thierno</t>
+          <t>portu</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>tYV4tvqr</t>
+          <t>n5xqpcKc</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>groeneveld arnaut</t>
+          <t>portu</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>p6rsDQvN</t>
+          <t>8l99epoQ</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>gueye pape</t>
+          <t>tsygankov viktor</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>p6rsDQvN</t>
+          <t>2HT2pDXL</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>gueye pape</t>
+          <t>de haro raul</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>bmeQTB92</t>
+          <t>2HT2pDXL</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>baena alex</t>
+          <t>de haro raul</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>zykz5SJb</t>
+          <t>IeVXGQOi</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>beltran francisco</t>
+          <t>budimir ante</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>zykz5SJb</t>
+          <t>Gpc9AB61</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>beltran francisco</t>
+          <t>garcia ruben</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>MoAntFV8</t>
+          <t>Gpc9AB61</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>kourouma moriba</t>
+          <t>garcia ruben</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>nyLFv8t3</t>
+          <t>KCtH4oIT</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>alvarez hugo</t>
+          <t>moncayola jon</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>nyLFv8t3</t>
+          <t>xOWXxrsi</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>alvarez hugo</t>
+          <t>ibanez pablo</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>rHUdQZPd</t>
+          <t>xOWXxrsi</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>carreira sergio</t>
+          <t>ibanez pablo</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>KluZeL4G</t>
+          <t>SlzBPHAH</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>swedberg williot</t>
+          <t>oroz aimar</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>KluZeL4G</t>
+          <t>ObepFC6G</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>swedberg williot</t>
+          <t>benito iker</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>8bvxeNAG</t>
+          <t>ObepFC6G</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>manquillo javier</t>
+          <t>benito iker</t>
         </is>
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>rVBGggAd</t>
+          <t>hQyTbdVL</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>aspas iago</t>
+          <t>zaragoza bryan</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>rVBGggAd</t>
+          <t>nBYFHtta</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>aspas iago</t>
+          <t>martinez calvo javier</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>IXim7pWh</t>
+          <t>nBYFHtta</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>gonzalez alfonso</t>
+          <t>martinez calvo javier</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>YgPGkQYi</t>
+          <t>6y9ES72S</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>douvikas anastasios</t>
+          <t>torro lucas</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>YgPGkQYi</t>
+          <t>vDI9I1M4</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>douvikas anastasios</t>
+          <t>artero ricard</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>0vQciH42</t>
+          <t>nev0KWuA</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
         <is>
-          <t>iglesias borja</t>
+          <t>fernandez valery</t>
         </is>
       </c>
       <c r="EV3" t="inlineStr">
         <is>
-          <t>KxSmFSum</t>
+          <t>KxtC5I27</t>
         </is>
       </c>
       <c r="EW3" t="inlineStr">
         <is>
-          <t>alfonso pedraza</t>
+          <t>barja enrique</t>
         </is>
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>vcqiFPHQ</t>
+          <t>ncU1c1uo</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>foyth juan</t>
+          <t>munoz iker</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>GW5JRBD0</t>
+          <t>hvSbhBpg</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>de la torre luca</t>
-        </is>
-      </c>
-      <c r="FB3" t="inlineStr">
-        <is>
-          <t>8zW214va</t>
-        </is>
-      </c>
-      <c r="FC3" t="inlineStr">
-        <is>
-          <t>ristic mihailo</t>
-        </is>
-      </c>
-      <c r="FD3" t="inlineStr"/>
-      <c r="FE3" t="inlineStr"/>
+          <t>pena ruben</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr"/>
+      <c r="FC3" t="inlineStr"/>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>nBYFHtta</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>martinez calvo javier</t>
+        </is>
+      </c>
       <c r="FF3" t="inlineStr">
         <is>
-          <t>6HSinoFJ</t>
+          <t>x8pmKbnD</t>
         </is>
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>vidal marc</t>
+          <t>stamatakis dimitrios</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>xWwucZ71</t>
+          <t>tGPWeqJs</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>suarez denis</t>
-        </is>
-      </c>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="FJ3" t="inlineStr"/>
+      <c r="FK3" t="inlineStr"/>
+      <c r="FL3" t="inlineStr"/>
+      <c r="FM3" t="inlineStr"/>
+      <c r="FN3" t="inlineStr"/>
+      <c r="FO3" t="inlineStr"/>
+      <c r="FP3" t="inlineStr"/>
+      <c r="FQ3" t="inlineStr"/>
+      <c r="FR3" t="inlineStr"/>
+      <c r="FS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2890,3001 +2960,3247 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>M3TzoLot</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>molina nahuel</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8GVQFgH4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>le normand robin</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2JsUqijl</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>witsel axel</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>CMGUADgt</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>azpilicueta cesar</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vTPgNn01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lino samuel</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>AZ6TTjDC</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>de paul rodrigo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>v9hLv1xJ</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>koke</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2iQMPvBg</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>riquelme rodrigo</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>QwqgNkTP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>sorloth alexander</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>bBHauDIC</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>alvarez julian</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>vuAlEqes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>garcia joan</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>z9FaGS78</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>el hilali omar</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Sj35PsHd</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>calero fernando</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>8xTCtgln</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>kumbulla marash</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>YDxiIlER</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>romero carlos</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>n7ISbL3j</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>tejero alvaro</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>UuiJcUMl</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>kral alex</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>QPoHzbRQ</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>gragera jose</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>fyEdYgal</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aguado alvaro</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Cl8Ia7Q9</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>puado javi</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>hph7e3vc</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>veliz alejo</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>AaZiGJ9E</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>barrios pablo</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>McWkid34</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>correa angel</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>t8GDN709</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>galan javier</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>dtbJO8B3</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>gallagher conor</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>IgRLzKhM</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>gimenez jose</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>8GVQFgH4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>le normand robin</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0rBkNdYp</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>gomis aleman antonio</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>OxCa1jdT</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>griezmann antoine</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>rH0mL7ws</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>lenglet clement</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>z3D5zvbD</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>llorente marcos</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>zekFd0M8</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>mandava reinildo</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>zB5O8dXn</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>musso juan</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>IJTJu41i</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>simeone giuliano</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>jcshWJpG</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>bauza rafel</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0renDAJu</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>jose catala</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>hYxF0Ust</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>cheddira walid</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>jRx96X5h</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>fortuno angel</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>v1bRsEDN</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>gomez sergi</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>KSNZwPAG</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>carreras jofe</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>6o8Nnmm1</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>lozano pol</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>EsMMVFh3</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>milla pere</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>n9R1WQ3p</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>olivan brian</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>OxCa1jdT</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>griezmann antoine</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>OxCa1jdT</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>griezmann antoine</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>bBHauDIC</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>alvarez julian</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>AaZiGJ9E</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>barrios pablo</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>AaZiGJ9E</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>barrios pablo</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>vTPgNn01</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>lino samuel</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>z3D5zvbD</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>llorente marcos</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>z3D5zvbD</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>llorente marcos</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>M3TzoLot</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>molina nahuel</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>McWkid34</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>correa angel</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>McWkid34</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>correa angel</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
         <is>
           <t>AZ6TTjDC</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="DG4" t="inlineStr">
         <is>
           <t>de paul rodrigo</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>AaZiGJ9E</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>barrios pablo</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2iQMPvBg</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>riquelme rodrigo</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>OxCa1jdT</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>griezmann antoine</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>vTPgNn01</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>lino samuel</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>bBHauDIC</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>alvarez julian</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>jB3F3wGi</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>gazzaniga paulo</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>UTk2FzpS</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>martinez arnau</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>250rn438</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>lopez david</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>U5mPqlh6</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>blind daley</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>z9xliwUd</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>gutierrez miguel</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>tzwJ3As6</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>herrera yangel</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>WCC5IrWg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>romeu oriol</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>vLPRaVJo</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>martin ivan</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>8l99epoQ</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>tsygankov viktor</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>EauanyEm</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>ruiz abel</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>xSXBYlvl</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>gil bryan</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>McWkid34</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>correa angel</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>t8GDN709</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>galan javier</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>dtbJO8B3</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>gallagher conor</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0rBkNdYp</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>gomis aleman antonio</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>29aQRcre</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>iturbe alejandro</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>v9hLv1xJ</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>koke</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>QTc0qeb2</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>kostis ilias</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
+      <c r="DH4" t="inlineStr">
         <is>
           <t>zekFd0M8</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="DI4" t="inlineStr">
         <is>
           <t>mandava reinildo</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>M3TzoLot</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>molina nahuel</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>IJTJu41i</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>simeone giuliano</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>zekFd0M8</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>mandava reinildo</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
         <is>
           <t>QwqgNkTP</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="DM4" t="inlineStr">
         <is>
           <t>sorloth alexander</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>2JsUqijl</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>witsel axel</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>zy0jwcjQ</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>almena iker</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>OjpPzOu0</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>frances alejandro</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>n1iE7ch5</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>juan carlos</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>GbY2OPWp</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>juanpe</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>nZ8SVvvE</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>krejci ladislav</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>rZes9CKA</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>lopez pau</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>2ZExqRk3</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>miovski bojan</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>2e75edda</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>misehouy gabriel osei</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>n5xqpcKc</t>
-        </is>
-      </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>portu</t>
-        </is>
-      </c>
-      <c r="CJ4" t="inlineStr">
-        <is>
-          <t>CxVKphX0</t>
-        </is>
-      </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>solis jhon</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>U5yv9YBB</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>stuani christian</t>
-        </is>
-      </c>
-      <c r="CN4" t="inlineStr">
-        <is>
-          <t>dtbJO8B3</t>
-        </is>
-      </c>
-      <c r="CO4" t="inlineStr">
-        <is>
-          <t>gallagher conor</t>
-        </is>
-      </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>dtbJO8B3</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>gallagher conor</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>2iQMPvBg</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>riquelme rodrigo</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>v9hLv1xJ</t>
-        </is>
-      </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>koke</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>v9hLv1xJ</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>koke</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>AZ6TTjDC</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>de paul rodrigo</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>zekFd0M8</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>mandava reinildo</t>
-        </is>
-      </c>
-      <c r="DB4" t="inlineStr">
-        <is>
-          <t>zekFd0M8</t>
-        </is>
-      </c>
-      <c r="DC4" t="inlineStr">
-        <is>
-          <t>mandava reinildo</t>
-        </is>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>vTPgNn01</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>lino samuel</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>QwqgNkTP</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>sorloth alexander</t>
-        </is>
-      </c>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>QwqgNkTP</t>
-        </is>
-      </c>
-      <c r="DI4" t="inlineStr">
-        <is>
-          <t>sorloth alexander</t>
-        </is>
-      </c>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>bBHauDIC</t>
-        </is>
-      </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>alvarez julian</t>
-        </is>
-      </c>
-      <c r="DL4" t="inlineStr">
-        <is>
-          <t>McWkid34</t>
-        </is>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>correa angel</t>
-        </is>
-      </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>McWkid34</t>
+          <t>n9R1WQ3p</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>correa angel</t>
+          <t>olivan brian</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>OxCa1jdT</t>
+          <t>n9R1WQ3p</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>griezmann antoine</t>
+          <t>olivan brian</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>n5xqpcKc</t>
+          <t>YDxiIlER</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>portu</t>
+          <t>romero carlos</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>n5xqpcKc</t>
+          <t>hYxF0Ust</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
         <is>
-          <t>portu</t>
+          <t>cheddira walid</t>
         </is>
       </c>
       <c r="DV4" t="inlineStr">
         <is>
-          <t>vLPRaVJo</t>
+          <t>hYxF0Ust</t>
         </is>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>martin ivan</t>
+          <t>cheddira walid</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>2ZExqRk3</t>
+          <t>hph7e3vc</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>miovski bojan</t>
+          <t>veliz alejo</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
         <is>
-          <t>2ZExqRk3</t>
+          <t>v1bRsEDN</t>
         </is>
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>miovski bojan</t>
+          <t>gomez sergi</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
         <is>
-          <t>EauanyEm</t>
+          <t>v1bRsEDN</t>
         </is>
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>ruiz abel</t>
+          <t>gomez sergi</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>CxVKphX0</t>
+          <t>8xTCtgln</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>solis jhon</t>
+          <t>kumbulla marash</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>CxVKphX0</t>
+          <t>6o8Nnmm1</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>solis jhon</t>
+          <t>lozano pol</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>WCC5IrWg</t>
+          <t>6o8Nnmm1</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>romeu oriol</t>
+          <t>lozano pol</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>zy0jwcjQ</t>
+          <t>QPoHzbRQ</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>almena iker</t>
+          <t>gragera jose</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>zy0jwcjQ</t>
+          <t>KSNZwPAG</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
         <is>
-          <t>almena iker</t>
+          <t>carreras jofe</t>
         </is>
       </c>
       <c r="EN4" t="inlineStr">
         <is>
-          <t>8l99epoQ</t>
+          <t>KSNZwPAG</t>
         </is>
       </c>
       <c r="EO4" t="inlineStr">
         <is>
-          <t>tsygankov viktor</t>
-        </is>
-      </c>
-      <c r="EP4" t="inlineStr"/>
-      <c r="EQ4" t="inlineStr"/>
-      <c r="ER4" t="inlineStr"/>
-      <c r="ES4" t="inlineStr"/>
+          <t>carreras jofe</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>fyEdYgal</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>aguado alvaro</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>jX8PENMO</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>lemar thomas</t>
+        </is>
+      </c>
       <c r="ET4" t="inlineStr"/>
       <c r="EU4" t="inlineStr"/>
       <c r="EV4" t="inlineStr">
         <is>
-          <t>jX8PENMO</t>
+          <t>IsOwrMdM</t>
         </is>
       </c>
       <c r="EW4" t="inlineStr">
         <is>
-          <t>lemar thomas</t>
+          <t>cabrera leandro</t>
         </is>
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>OQY4TKul</t>
+          <t>SChm1pCo</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>marcos paulo</t>
-        </is>
-      </c>
-      <c r="EZ4" t="inlineStr">
-        <is>
-          <t>vDI9I1M4</t>
-        </is>
-      </c>
-      <c r="FA4" t="inlineStr">
-        <is>
-          <t>artero ricard</t>
-        </is>
-      </c>
-      <c r="FB4" t="inlineStr">
-        <is>
-          <t>nev0KWuA</t>
-        </is>
-      </c>
-      <c r="FC4" t="inlineStr">
-        <is>
-          <t>fernandez valery</t>
-        </is>
-      </c>
+          <t>exposito edu</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr"/>
+      <c r="FA4" t="inlineStr"/>
+      <c r="FB4" t="inlineStr"/>
+      <c r="FC4" t="inlineStr"/>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>tGPWeqJs</t>
+          <t>27U3P9mT</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>jastin antonino</t>
+          <t>pacheco fernando</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
         <is>
-          <t>bs2gvblF</t>
+          <t>ILCGOm9n</t>
         </is>
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>van de beek donny</t>
+          <t>roca antoniu</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr"/>
       <c r="FI4" t="inlineStr"/>
+      <c r="FJ4" t="inlineStr">
+        <is>
+          <t>x0TzcxX6</t>
+        </is>
+      </c>
+      <c r="FK4" t="inlineStr">
+        <is>
+          <t>sanchez salvi</t>
+        </is>
+      </c>
+      <c r="FL4" t="inlineStr"/>
+      <c r="FM4" t="inlineStr"/>
+      <c r="FN4" t="inlineStr"/>
+      <c r="FO4" t="inlineStr"/>
+      <c r="FP4" t="inlineStr"/>
+      <c r="FQ4" t="inlineStr"/>
+      <c r="FR4" t="inlineStr"/>
+      <c r="FS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nXUxw7wg</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WGae8d9E</t>
+          <t>UmDjbtRC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marin carlos</t>
+          <t>remiro alejandro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S4KW2ean</t>
+          <t>fRSnvKQG</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>albarran carlos</t>
+          <t>traore hamari</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O6hVP1TB</t>
+          <t>phTjGNq0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ruiz adrian</t>
+          <t>zubeldia igor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>jwvNqlFq</t>
+          <t>Qk9dJWGB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>antonio martinez jose</t>
+          <t>pacheco jon</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8t3vtwdc</t>
+          <t>MaufHIJ2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>calderon jose</t>
+          <t>lopez javi</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>f5JqWchj</t>
+          <t>fqdLdpc3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>zidane theo</t>
+          <t>kubo takefusa</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>veLxs2Gg</t>
+          <t>fNI6Gsdr</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>sala alex</t>
+          <t>zubimendi martin</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Qav8SAwf</t>
+          <t>Ey5XjmJt</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>rodriganez jacobo</t>
+          <t>mendez brais</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>j9FVq54i</t>
+          <t>fmGvlHVM</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>carracedo cristian</t>
+          <t>gomez sergio</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>trR2Luu5</t>
+          <t>2scm2TO3</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>casas antonio</t>
+          <t>becker sheraldo</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>O6KQ2Fml</t>
+          <t>dQ1P695O</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>adilson</t>
+          <t>oyarzabal mikel</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>rPMUGw3h</t>
+          <t>lMLBCMLN</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>cantero ander</t>
+          <t>sivera antonio</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>AyAxdOaP</t>
+          <t>KtWwVS3K</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>arroyo anderson</t>
+          <t>novoa ramos hugo</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>S2nS0dZr</t>
+          <t>Gp35on1c</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>lopez david</t>
+          <t>abqar abdelkebir</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>hQpQJSqn</t>
+          <t>baSksbWn</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>cordoba aitor</t>
+          <t>pica adrian</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>46wCqoNi</t>
+          <t>Op7pPJv2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>miguel florian</t>
+          <t>diarra moussa</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>IijdLfIb</t>
+          <t>hMjEwTOg</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>guevara ander</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4fkoGF10</t>
+          <t>K4275W3e</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>navarro raul</t>
+          <t>benavidez carlos</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>KI3xYemP</t>
+          <t>bRBNu8DM</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>appin kevin</t>
+          <t>vicente carlos</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>UPMWp37R</t>
+          <t>WhV8JXPD</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ojeda daniel</t>
+          <t>guridi jon</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>v1g9lCm3</t>
+          <t>0Oxc76wG</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>curro sanchez</t>
+          <t>rebbach abderrahmane</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>EPzCN58J</t>
+          <t>C4Qtc3iO</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>nino fer</t>
+          <t>villalibre asier</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>hzNRiFk1</t>
+          <t>vNTtZiAr</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>barboza matias</t>
+          <t>aranburu jon</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>xAhhX5Vm</t>
+          <t>U3QeeyTk</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>munoz carlos</t>
+          <t>fraga aitor</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>CKovzT1H</t>
+          <t>OvykMeki</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>molina antonio</t>
+          <t>gonzalez urko</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>YsOcklca</t>
+          <t>0IZE0zuH</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>obolskiy nikolay</t>
+          <t>magunazelaia jon</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>bZb6aNtj</t>
+          <t>Ye976xiA</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>ortiz josema</t>
+          <t>marin pablo</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>Agk5MJwd</t>
+          <t>Wr5ZTIf7</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>rodriguez genaro</t>
+          <t>marrero larranaga unai</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>IV8hD3Am</t>
+          <t>dd9n67gb</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>sintes xavi</t>
+          <t>martin jon</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>CfBHradb</t>
+          <t>C8QkouJU</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>soonsup bell jude</t>
+          <t>munoz aihen</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>KAc8u2f4</t>
+          <t>O8nKKpaP</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>vila ramon</t>
+          <t>olasagasti jon</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>fu9bjNgL</t>
+          <t>UsKF9Yzn</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>aizagar ander yoldi</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
+          <t>sadiq umar</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>p6f9CgsE</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>sucic luka</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>WtVfJtAm</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>turrientes benat</t>
+        </is>
+      </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0poEwxl4</t>
+          <t>MTG8l3Dq</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>atienza miguel</t>
+          <t>blanco antonio</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>hQU1V6u9</t>
+          <t>zZJGkBEQ</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>badiashile loic</t>
+          <t>conechny tomas</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>S8CD3sIU</t>
+          <t>GfoivbEm</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>cordoba inigo</t>
+          <t>kike</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>lIO1oG6S</t>
+          <t>dnvBgOsP</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>del cerro saul</t>
+          <t>martin carlos</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6kWRKUsC</t>
+          <t>rw0nledT</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>espiau edu</t>
+          <t>martinez toni</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>rTFUvlCc</t>
+          <t>tQ4ufwYl</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>exposito jimenez marcelo</t>
+          <t>mourino santiago</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>ljSkZFwn</t>
+          <t>AcqRuf0b</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>gonzalez david</t>
+          <t>owono jesus</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>lvl2kso0</t>
+          <t>MLlf8c4E</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>lopez javier</t>
+          <t>rodriguez adrian</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>U5V6iENe</t>
+          <t>r9HfBE6F</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>martin ander</t>
+          <t>romero luka</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>tSrz5SW1</t>
+          <t>dd9n67gb</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>morante ivan</t>
+          <t>martin jon</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>8zZErFJT</t>
+          <t>dd9n67gb</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>pascual hugo</t>
+          <t>martin jon</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>fu9bjNgL</t>
+          <t>Qk9dJWGB</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>aizagar ander yoldi</t>
+          <t>pacheco jon</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>fu9bjNgL</t>
+          <t>UsKF9Yzn</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>aizagar ander yoldi</t>
+          <t>sadiq umar</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>O6KQ2Fml</t>
+          <t>UsKF9Yzn</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>adilson</t>
+          <t>sadiq umar</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>YsOcklca</t>
+          <t>2scm2TO3</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>obolskiy nikolay</t>
+          <t>becker sheraldo</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>YsOcklca</t>
+          <t>WtVfJtAm</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>obolskiy nikolay</t>
+          <t>turrientes benat</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>trR2Luu5</t>
+          <t>WtVfJtAm</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>casas antonio</t>
+          <t>turrientes benat</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>Agk5MJwd</t>
+          <t>phTjGNq0</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>rodriguez genaro</t>
+          <t>zubeldia igor</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>Agk5MJwd</t>
+          <t>Ye976xiA</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>rodriguez genaro</t>
+          <t>marin pablo</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>f5JqWchj</t>
+          <t>Ye976xiA</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>zidane theo</t>
+          <t>marin pablo</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>IV8hD3Am</t>
+          <t>Ey5XjmJt</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>sintes xavi</t>
+          <t>mendez brais</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>IV8hD3Am</t>
+          <t>O8nKKpaP</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>sintes xavi</t>
+          <t>olasagasti jon</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>j9FVq54i</t>
+          <t>O8nKKpaP</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>carracedo cristian</t>
+          <t>olasagasti jon</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>xAhhX5Vm</t>
+          <t>fmGvlHVM</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>munoz carlos</t>
+          <t>gomez sergio</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>xAhhX5Vm</t>
+          <t>Kneifk5H</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>munoz carlos</t>
+          <t>stoichkov</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>Qav8SAwf</t>
+          <t>Kneifk5H</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>rodriganez jacobo</t>
+          <t>stoichkov</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>tSrz5SW1</t>
+          <t>K4275W3e</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>morante ivan</t>
+          <t>benavidez carlos</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>tSrz5SW1</t>
+          <t>b3mITAJa</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>morante ivan</t>
+          <t>sanchez manuel</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>4fkoGF10</t>
+          <t>b3mITAJa</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>navarro raul</t>
+          <t>sanchez manuel</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>6kWRKUsC</t>
+          <t>Op7pPJv2</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>espiau edu</t>
+          <t>diarra moussa</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>6kWRKUsC</t>
+          <t>GfoivbEm</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>espiau edu</t>
+          <t>kike</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>EPzCN58J</t>
+          <t>GfoivbEm</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>nino fer</t>
+          <t>kike</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>S8CD3sIU</t>
+          <t>C4Qtc3iO</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>cordoba inigo</t>
+          <t>villalibre asier</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>S8CD3sIU</t>
+          <t>rw0nledT</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>cordoba inigo</t>
+          <t>martinez toni</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>UPMWp37R</t>
+          <t>rw0nledT</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>ojeda daniel</t>
+          <t>martinez toni</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>ljSkZFwn</t>
+          <t>0Oxc76wG</t>
         </is>
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>gonzalez david</t>
+          <t>rebbach abderrahmane</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>ljSkZFwn</t>
+          <t>MTG8l3Dq</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
         <is>
-          <t>gonzalez david</t>
+          <t>blanco antonio</t>
         </is>
       </c>
       <c r="EN5" t="inlineStr">
         <is>
-          <t>KI3xYemP</t>
+          <t>MTG8l3Dq</t>
         </is>
       </c>
       <c r="EO5" t="inlineStr">
         <is>
-          <t>appin kevin</t>
+          <t>blanco antonio</t>
         </is>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>0poEwxl4</t>
+          <t>bRBNu8DM</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>atienza miguel</t>
+          <t>vicente carlos</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>0poEwxl4</t>
+          <t>A3vo4Lf6</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>atienza miguel</t>
+          <t>barrenetxea muguruza ander</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>IijdLfIb</t>
+          <t>6qVwC9AH</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
         <is>
-          <t>alex</t>
-        </is>
-      </c>
-      <c r="EV5" t="inlineStr"/>
-      <c r="EW5" t="inlineStr"/>
+          <t>elustondo aritz</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>h4BWTxSF</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>sedlar aleksandar</t>
+        </is>
+      </c>
       <c r="EX5" t="inlineStr"/>
       <c r="EY5" t="inlineStr"/>
       <c r="EZ5" t="inlineStr"/>
       <c r="FA5" t="inlineStr"/>
       <c r="FB5" t="inlineStr"/>
       <c r="FC5" t="inlineStr"/>
-      <c r="FD5" t="inlineStr"/>
-      <c r="FE5" t="inlineStr"/>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>b3mITAJa</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>sanchez manuel</t>
+        </is>
+      </c>
       <c r="FF5" t="inlineStr">
         <is>
-          <t>xOIewwcB</t>
+          <t>Kneifk5H</t>
         </is>
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>rastrilla hugo</t>
-        </is>
-      </c>
-      <c r="FH5" t="inlineStr"/>
-      <c r="FI5" t="inlineStr"/>
+          <t>stoichkov</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr">
+        <is>
+          <t>0zO9SfkA</t>
+        </is>
+      </c>
+      <c r="FI5" t="inlineStr">
+        <is>
+          <t>odriozola alvaro</t>
+        </is>
+      </c>
+      <c r="FJ5" t="inlineStr">
+        <is>
+          <t>WAG63va3</t>
+        </is>
+      </c>
+      <c r="FK5" t="inlineStr">
+        <is>
+          <t>tenaglia nahuel</t>
+        </is>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
+          <t>r7qw7OKg</t>
+        </is>
+      </c>
+      <c r="FM5" t="inlineStr">
+        <is>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="FN5" t="inlineStr"/>
+      <c r="FO5" t="inlineStr"/>
+      <c r="FP5" t="inlineStr"/>
+      <c r="FQ5" t="inlineStr"/>
+      <c r="FR5" t="inlineStr"/>
+      <c r="FS5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Q31eQTgm</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G4b5p859</t>
+          <t>2iBBeOy8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>campos pablo</t>
+          <t>agirrezabala julen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>pSeqAJ0c</t>
+          <t>ljCE2GoH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>aguirregabiria martin</t>
+          <t>de marcos oscar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KrX5waGB</t>
+          <t>x2fvXYO7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>sipcic nikola</t>
+          <t>vivian daniel</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>juxRzfwF</t>
+          <t>nev6Da3D</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>kiko olivas</t>
+          <t>alvarez yeray</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IilHTmj9</t>
+          <t>fR7uJqwO</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>rios reina jose</t>
+          <t>boiro adama</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8xkqsBHk</t>
+          <t>hOdEyz15</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>musto marcelo daniel</t>
+          <t>jauregizar mikel</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>WMnz8BzK</t>
+          <t>t2Srcdis</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>andy</t>
+          <t>prados benat</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>nFO9fFkl</t>
+          <t>W4HzaGVn</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>izquierdo jairo</t>
+          <t>williams inaki</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>nThR7Un8</t>
+          <t>hpZLKZVC</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>guerrero sergio</t>
+          <t>sancet ohian</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>KnJdARG3</t>
+          <t>hxVl8TRJ</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>teguia cedric</t>
+          <t>djalo alvaro</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>46haE6np</t>
+          <t>bTKd7PI5</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>valles gaston</t>
+          <t>guruzeta gorka</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2RWVJ0mS</t>
+          <t>lxnsUkIc</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>poussin gaetan</t>
+          <t>mamardashvili giorgi</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>EctXf3CQ</t>
+          <t>65F8DTep</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>calero ivan</t>
+          <t>foulquier dimitri</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>ADwlmnw6</t>
+          <t>CIrZ775M</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>marmol lluis</t>
+          <t>tarrega cesar</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2yO22dZF</t>
+          <t>4O15XViB</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>vital bernardo</t>
+          <t>mosquera cristhian</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>MsLEXo2J</t>
+          <t>M5U2cN2q</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>tasende dani</t>
+          <t>vazquez jesus</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>ULQo1Vhr</t>
+          <t>SGjehmsG</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>bermejo sergio</t>
+          <t>lopez noguerol diego</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4jcnOm31</t>
+          <t>nosv3azp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>bare keidi</t>
+          <t>pepelu</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>KQYMzB7t</t>
+          <t>Wpw94bj6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>aguado marc</t>
+          <t>guillamon hugo</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>EPkF4hUA</t>
+          <t>h8cBI9v2</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>liso adrian</t>
+          <t>rioja luis</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>xAKBBXpc</t>
+          <t>EP4vWYSf</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>soberon mario</t>
+          <t>duro hugo</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6mb7wPdI</t>
+          <t>IXRaCzVt</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>bazdar samed</t>
+          <t>mir rafael</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>rqnIpvc8</t>
+          <t>UuKvqHl9</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>alcala pedro</t>
+          <t>ares djalo malcom adu</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>8b3l0HB5</t>
+          <t>nuQn903r</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>andugar angel</t>
+          <t>berenguer alejandro</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>baZ7aMTa</t>
+          <t>I71fjzT2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>escriche daniel</t>
+          <t>eguiluz unai</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>6gGt1XDd</t>
+          <t>b9174gL1</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>fuidias toni</t>
+          <t>gomez unai</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>vRNUBqy4</t>
+          <t>KEaIS3qg</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>moreno jorge</t>
+          <t>espinoza andoni</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>MJcnwOI5</t>
+          <t>jyzWX8yk</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>munoz luis</t>
+          <t>herrera ander</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>6DIWoQi4</t>
+          <t>nDleV6a5</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>ortuno alfredo</t>
+          <t>javier marton</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>xnPUpahj</t>
+          <t>rkIhAwQO</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>reyes jhafets</t>
+          <t>lekue inigo</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>nJwfryI5</t>
+          <t>4d3bB6Wo</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>ayton roman lucas</t>
+          <t>padilla alex</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>fFDutvUN</t>
+          <t>nPdiENxr</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>sanchez carmelo</t>
+          <t>serrano nico</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>KK2GPNcn</t>
+          <t>CSIEND11</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>vukcevic andrija</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
+          <t>vesga mikel</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>Cp7lcVjJ</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>williams nico</t>
+        </is>
+      </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>vFkqiEfF</t>
+          <t>WO3oyVW7</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>acin guillermo</t>
+          <t>almeida andre</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>GjsJwEtR</t>
+          <t>GEN8xHY4</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>alvarez cristian</t>
+          <t>cordoba iker</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>Mol2TYUm</t>
+          <t>Sv5sgVLE</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>azon ivan</t>
+          <t>correia thierry</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>6uXqLpX9</t>
+          <t>2axfsTHA</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>garcia francho</t>
+          <t>dimitrievski stole</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>E3pkEtFM</t>
+          <t>4UxxcIjS</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>gori</t>
+          <t>hernadis yarek gasiorowski</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>YBErmO6h</t>
+          <t>UVDJACJ9</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>lecoeuche quentin</t>
+          <t>gomez daniel</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>lGBLl2mm</t>
+          <t>2yyy00aj</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>luna marcos</t>
+          <t>guerra javi</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>6gQosNq6</t>
+          <t>WKSwzS4T</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>moya toni</t>
+          <t>jimenez raul</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>2RBw3D8c</t>
+          <t>4bjEksiR</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>sabater juan carlos</t>
+          <t>mari alberto</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>rPH2xAjh</t>
+          <t>Cp7lcVjJ</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>sans pau</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
+          <t>williams nico</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>Cp7lcVjJ</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>williams nico</t>
+        </is>
+      </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>MJcnwOI5</t>
+          <t>hxVl8TRJ</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>munoz luis</t>
+          <t>djalo alvaro</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>MJcnwOI5</t>
+          <t>b9174gL1</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>munoz luis</t>
+          <t>gomez unai</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>KnJdARG3</t>
+          <t>b9174gL1</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>teguia cedric</t>
+          <t>gomez unai</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>KK2GPNcn</t>
+          <t>hpZLKZVC</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>vukcevic andrija</t>
+          <t>sancet ohian</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>KK2GPNcn</t>
+          <t>CSIEND11</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>vukcevic andrija</t>
+          <t>vesga mikel</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>nFO9fFkl</t>
+          <t>CSIEND11</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>izquierdo jairo</t>
+          <t>vesga mikel</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>baZ7aMTa</t>
+          <t>bTKd7PI5</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>escriche daniel</t>
+          <t>guruzeta gorka</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>baZ7aMTa</t>
+          <t>nDleV6a5</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
-          <t>escriche daniel</t>
+          <t>javier marton</t>
         </is>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>nThR7Un8</t>
+          <t>nDleV6a5</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>guerrero sergio</t>
+          <t>javier marton</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
         <is>
-          <t>6DIWoQi4</t>
+          <t>t2Srcdis</t>
         </is>
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>ortuno alfredo</t>
+          <t>prados benat</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>6DIWoQi4</t>
+          <t>rkIhAwQO</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
         <is>
-          <t>ortuno alfredo</t>
+          <t>lekue inigo</t>
         </is>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>46haE6np</t>
+          <t>rkIhAwQO</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>valles gaston</t>
+          <t>lekue inigo</t>
         </is>
       </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>nJwfryI5</t>
+          <t>fR7uJqwO</t>
         </is>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>ayton roman lucas</t>
+          <t>boiro adama</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>nJwfryI5</t>
+          <t>WO3oyVW7</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>ayton roman lucas</t>
+          <t>almeida andre</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>IilHTmj9</t>
+          <t>WO3oyVW7</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>rios reina jose</t>
+          <t>almeida andre</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>Mol2TYUm</t>
+          <t>IXRaCzVt</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
         <is>
-          <t>azon ivan</t>
+          <t>mir rafael</t>
         </is>
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>Mol2TYUm</t>
+          <t>2yyy00aj</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
         <is>
-          <t>azon ivan</t>
+          <t>guerra javi</t>
         </is>
       </c>
       <c r="DV6" t="inlineStr">
         <is>
-          <t>ULQo1Vhr</t>
+          <t>2yyy00aj</t>
         </is>
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>bermejo sergio</t>
+          <t>guerra javi</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>rPH2xAjh</t>
+          <t>nosv3azp</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>sans pau</t>
+          <t>pepelu</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>rPH2xAjh</t>
+          <t>Grc4eSof</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>sans pau</t>
+          <t>tejon martin</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>xAKBBXpc</t>
+          <t>Grc4eSof</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>soberon mario</t>
+          <t>tejon martin</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>6uXqLpX9</t>
+          <t>SGjehmsG</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>garcia francho</t>
+          <t>lopez noguerol diego</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>6uXqLpX9</t>
+          <t>Sv5sgVLE</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>garcia francho</t>
+          <t>correia thierry</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>4jcnOm31</t>
+          <t>Sv5sgVLE</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
         <is>
-          <t>bare keidi</t>
+          <t>correia thierry</t>
         </is>
       </c>
       <c r="EJ6" t="inlineStr">
         <is>
-          <t>6gQosNq6</t>
+          <t>M5U2cN2q</t>
         </is>
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>moya toni</t>
+          <t>vazquez jesus</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>6gQosNq6</t>
+          <t>UVDJACJ9</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
         <is>
-          <t>moya toni</t>
+          <t>gomez daniel</t>
         </is>
       </c>
       <c r="EN6" t="inlineStr">
         <is>
-          <t>KQYMzB7t</t>
+          <t>UVDJACJ9</t>
         </is>
       </c>
       <c r="EO6" t="inlineStr">
         <is>
-          <t>aguado marc</t>
+          <t>gomez daniel</t>
         </is>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>lGBLl2mm</t>
+          <t>EP4vWYSf</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>luna marcos</t>
+          <t>duro hugo</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>lGBLl2mm</t>
+          <t>OCA7UnaC</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>luna marcos</t>
+          <t>berchiche yuri</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>6mb7wPdI</t>
+          <t>ChK2eOCj</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
         <is>
-          <t>bazdar samed</t>
-        </is>
-      </c>
-      <c r="EV6" t="inlineStr"/>
-      <c r="EW6" t="inlineStr"/>
-      <c r="EX6" t="inlineStr"/>
-      <c r="EY6" t="inlineStr"/>
-      <c r="EZ6" t="inlineStr"/>
-      <c r="FA6" t="inlineStr"/>
-      <c r="FB6" t="inlineStr"/>
-      <c r="FC6" t="inlineStr"/>
-      <c r="FD6" t="inlineStr"/>
-      <c r="FE6" t="inlineStr"/>
-      <c r="FF6" t="inlineStr"/>
-      <c r="FG6" t="inlineStr"/>
-      <c r="FH6" t="inlineStr"/>
-      <c r="FI6" t="inlineStr"/>
+          <t>paredes aitor</t>
+        </is>
+      </c>
+      <c r="EV6" t="inlineStr">
+        <is>
+          <t>2iri9TaP</t>
+        </is>
+      </c>
+      <c r="EW6" t="inlineStr">
+        <is>
+          <t>canos sergi</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t>O6bdhMA2</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t>castillejo samu</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>2gqO56Xu</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>diakhaby mouctar</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr">
+        <is>
+          <t>KbobTIgr</t>
+        </is>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t>domenech jaume</t>
+        </is>
+      </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>p0AiQXJi</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
+          <t>abajas rodrigo</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
+          <t>Grc4eSof</t>
+        </is>
+      </c>
+      <c r="FG6" t="inlineStr">
+        <is>
+          <t>tejon martin</t>
+        </is>
+      </c>
+      <c r="FH6" t="inlineStr">
+        <is>
+          <t>AqAnv17H</t>
+        </is>
+      </c>
+      <c r="FI6" t="inlineStr">
+        <is>
+          <t>inigo ruiz</t>
+        </is>
+      </c>
+      <c r="FJ6" t="inlineStr"/>
+      <c r="FK6" t="inlineStr"/>
+      <c r="FL6" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="FM6" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
+      <c r="FN6" t="inlineStr">
+        <is>
+          <t>xWguLPCU</t>
+        </is>
+      </c>
+      <c r="FO6" t="inlineStr">
+        <is>
+          <t>gaya jose</t>
+        </is>
+      </c>
+      <c r="FP6" t="inlineStr">
+        <is>
+          <t>Iefc5Fwo</t>
+        </is>
+      </c>
+      <c r="FQ6" t="inlineStr">
+        <is>
+          <t>ozkacar cenk</t>
+        </is>
+      </c>
+      <c r="FR6" t="inlineStr">
+        <is>
+          <t>bePNNa1r</t>
+        </is>
+      </c>
+      <c r="FS6" t="inlineStr">
+        <is>
+          <t>perez francisco</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MVf4O7Oa</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Moj39S61</t>
+          <t>jyH8E81E</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>alejandro gonzalo</t>
+          <t>hein karl</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lO6sobTG</t>
+          <t>4zgv0hGk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>chirino daijiro</t>
+          <t>perez luis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rZwPCDVc</t>
+          <t>6NytetE5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jimenez alberto</t>
+          <t>sanchez javier</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hIm8dpPN</t>
+          <t>G6IFcpHK</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>vertrouwd jozhua</t>
+          <t>boyomos flavien enzo</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>nwdj0Ls1</t>
+          <t>2g3Pa3qH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>mamah kenneth obinna</t>
+          <t>rosa lucas</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>fmjvOOXT</t>
+          <t>SCxfo9Zu</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>flakus bosilj david</t>
+          <t>kike</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Oz4LFsdm</t>
+          <t>dfLinARB</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>gil oscar</t>
+          <t>juric stanko</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>63JPjZot</t>
+          <t>f7bNFe72</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>seuntjens mats</t>
+          <t>amallah selim</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>hdzS6xVf</t>
+          <t>42y06OiE</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>sanchez raul</t>
+          <t>ndiaye amath</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>joO0HA3L</t>
+          <t>YqtgOOMN</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>aurelio douglas</t>
+          <t>sylla mamadou</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>MXMTbTjl</t>
+          <t>zw8vYjwk</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>de miguel jesus</t>
+          <t>moro raul</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>lA1Qa7LH</t>
+          <t>tAaD36mt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>escandell aaron</t>
+          <t>soriano juan</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Cjw1V4uo</t>
+          <t>6B7YK1Tu</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>ahijado lucas</t>
+          <t>rosier valentin</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>CxnAZJbo</t>
+          <t>EwStt8o4</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>luengo oier</t>
+          <t>saenz jorge</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>fgJYtAmE</t>
+          <t>6Nmx29Pj</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>calvo dani</t>
+          <t>gonzalez sergio</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>69aNbb67</t>
+          <t>6NFqRQVg</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>alhassane rahim</t>
+          <t>hernandez javi</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>vg9tJMbL</t>
+          <t>E5Et3VgM</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sibo kwasi</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>CMhGvpU0</t>
+          <t>E3s5eF5I</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>del moral alberto</t>
+          <t>cisse seydouba</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>GODeIoHH</t>
+          <t>WWHLyhpR</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>hassan haissem</t>
+          <t>chicco julian</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>YeImVH7d</t>
+          <t>SbettZSO</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>dotor carlos</t>
+          <t>neyou noupa yvan</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>l88RYMiD</t>
+          <t>0QAeQWxE</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>moyano francisco</t>
+          <t>franquesa enric</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>ljVRztTj</t>
+          <t>6yaQrJGS</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>alemao</t>
+          <t>de la fuente miguel</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>WKrXys11</t>
+          <t>bcJKuoR6</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>albert jose</t>
+          <t>chuki</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>b13gbSqm</t>
+          <t>EZg4jPUF</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>calatrava alex</t>
+          <t>comert eray</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>URckqU07</t>
+          <t>j5SMgGHu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>calavera josep</t>
+          <t>ferreira andre</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>KQL5Shet</t>
+          <t>UHqRA6g4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>cipenga brian</t>
+          <t>iglesias koke</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>OG6pnQq7</t>
+          <t>nqOnhuF9</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>punzano iker</t>
+          <t>latasa juan</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>fDbFeqY3</t>
+          <t>nBtLrBRF</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>schwake brian</t>
+          <t>machis darwin</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>Eg6LHAo8</t>
+          <t>dEgxh8oM</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>suero israel</t>
+          <t>marcos andre</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>23VZWq4k</t>
+          <t>IXreUcCq</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>suner pere marco</t>
+          <t>martin mario</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>CUPz0tB5</t>
+          <t>EN3EbULf</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>van den belt thomas</t>
+          <t>meseguer victor</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>WpAyP013</t>
+          <t>AJg8NPiE</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>villahermosa daniel</t>
+          <t>ruiz raul chasco</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>fw0yGQLQ</t>
+          <t>vkmiDN8F</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>willems jetro</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
+          <t>sanchez ivan</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>8S0B28YJ</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>torres david</t>
+        </is>
+      </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>ngBNZ9LM</t>
+          <t>4AaiuZpF</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>braat quentin</t>
+          <t>altimira adria</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>jsRoAy4E</t>
+          <t>zk34NV3A</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>suarez cardero alejandro</t>
+          <t>alvin</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>rVt0F12N</t>
+          <t>UkvndELE</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>cazorla santi</t>
+          <t>arambarri aritz</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>bD41lxAF</t>
+          <t>OAPggVhT</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>costas david</t>
+          <t>brasanac darko</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>KhzzCbCU</t>
+          <t>pO8Jn4Xm</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>de la fuente pau</t>
+          <t>dmitrovic marko</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>QwD9sQn9</t>
+          <t>EeUtTZld</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>lemos alvaro</t>
+          <t>garcia campos diego</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>O608W9Wj</t>
+          <t>pIpdGy2U</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>mascarenhas francisco</t>
+          <t>lopez roberto</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>GxH7SxPr</t>
+          <t>CKYnnUEo</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>paraschiv daniel george</t>
+          <t>munir el haddadi</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>fBb6eDAH</t>
+          <t>AufokyHE</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>pomares carlos</t>
+          <t>porozo jackson</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>nPkoWJvS</t>
+          <t>nqOnhuF9</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>sanchez borja</t>
+          <t>latasa juan</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>f3yV6bvH</t>
+          <t>nqOnhuF9</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>vazquez jaime</t>
+          <t>latasa juan</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>b13gbSqm</t>
+          <t>YqtgOOMN</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>calatrava alex</t>
+          <t>sylla mamadou</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>b13gbSqm</t>
+          <t>vkmiDN8F</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>calatrava alex</t>
+          <t>sanchez ivan</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>MXMTbTjl</t>
+          <t>vkmiDN8F</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>de miguel jesus</t>
+          <t>sanchez ivan</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>CUPz0tB5</t>
+          <t>42y06OiE</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>van den belt thomas</t>
+          <t>ndiaye amath</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>CUPz0tB5</t>
+          <t>EN3EbULf</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>van den belt thomas</t>
+          <t>meseguer victor</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Oz4LFsdm</t>
+          <t>EN3EbULf</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>gil oscar</t>
+          <t>meseguer victor</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>Eg6LHAo8</t>
+          <t>SCxfo9Zu</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>suero israel</t>
+          <t>kike</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>Eg6LHAo8</t>
+          <t>dEgxh8oM</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
-          <t>suero israel</t>
+          <t>marcos andre</t>
         </is>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>63JPjZot</t>
+          <t>dEgxh8oM</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>seuntjens mats</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr"/>
-      <c r="DG7" t="inlineStr"/>
-      <c r="DH7" t="inlineStr"/>
-      <c r="DI7" t="inlineStr"/>
-      <c r="DJ7" t="inlineStr"/>
-      <c r="DK7" t="inlineStr"/>
-      <c r="DL7" t="inlineStr"/>
-      <c r="DM7" t="inlineStr"/>
-      <c r="DN7" t="inlineStr"/>
-      <c r="DO7" t="inlineStr"/>
-      <c r="DP7" t="inlineStr"/>
-      <c r="DQ7" t="inlineStr"/>
+          <t>marcos andre</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>zw8vYjwk</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>moro raul</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>bcJKuoR6</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>chuki</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>bcJKuoR6</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>chuki</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>f7bNFe72</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>amallah selim</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>WWNny3e7</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>rodriguez oscar</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>WWNny3e7</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>rodriguez oscar</t>
+        </is>
+      </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>rVt0F12N</t>
+          <t>0QAeQWxE</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
         <is>
-          <t>cazorla santi</t>
+          <t>franquesa enric</t>
         </is>
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>rVt0F12N</t>
+          <t>pIpdGy2U</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
         <is>
-          <t>cazorla santi</t>
+          <t>lopez roberto</t>
         </is>
       </c>
       <c r="DV7" t="inlineStr">
         <is>
-          <t>YeImVH7d</t>
+          <t>pIpdGy2U</t>
         </is>
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>dotor carlos</t>
+          <t>lopez roberto</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>O608W9Wj</t>
+          <t>E5Et3VgM</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>mascarenhas francisco</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>O608W9Wj</t>
+          <t>OAPggVhT</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>mascarenhas francisco</t>
+          <t>brasanac darko</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>GODeIoHH</t>
+          <t>OAPggVhT</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>hassan haissem</t>
+          <t>brasanac darko</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>KhzzCbCU</t>
+          <t>E3s5eF5I</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>de la fuente pau</t>
+          <t>cisse seydouba</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>KhzzCbCU</t>
+          <t>CKYnnUEo</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>de la fuente pau</t>
+          <t>munir el haddadi</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>l88RYMiD</t>
+          <t>CKYnnUEo</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
         <is>
-          <t>moyano francisco</t>
+          <t>munir el haddadi</t>
         </is>
       </c>
       <c r="EJ7" t="inlineStr">
         <is>
-          <t>GxH7SxPr</t>
+          <t>WWHLyhpR</t>
         </is>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>paraschiv daniel george</t>
+          <t>chicco julian</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>GxH7SxPr</t>
+          <t>6qPig05P</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
         <is>
-          <t>paraschiv daniel george</t>
+          <t>tapia renato</t>
         </is>
       </c>
       <c r="EN7" t="inlineStr">
         <is>
-          <t>ljVRztTj</t>
+          <t>6qPig05P</t>
         </is>
       </c>
       <c r="EO7" t="inlineStr">
         <is>
-          <t>alemao</t>
+          <t>tapia renato</t>
         </is>
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>bD41lxAF</t>
+          <t>SbettZSO</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>costas david</t>
+          <t>neyou noupa yvan</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>bD41lxAF</t>
+          <t>bygTWQzR</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>costas david</t>
-        </is>
-      </c>
-      <c r="ET7" t="inlineStr">
-        <is>
-          <t>vg9tJMbL</t>
-        </is>
-      </c>
-      <c r="EU7" t="inlineStr">
-        <is>
-          <t>sibo kwasi</t>
-        </is>
-      </c>
+          <t>anuar</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
       <c r="EV7" t="inlineStr"/>
       <c r="EW7" t="inlineStr"/>
       <c r="EX7" t="inlineStr"/>
@@ -5893,12 +6209,2445 @@
       <c r="FA7" t="inlineStr"/>
       <c r="FB7" t="inlineStr"/>
       <c r="FC7" t="inlineStr"/>
-      <c r="FD7" t="inlineStr"/>
-      <c r="FE7" t="inlineStr"/>
-      <c r="FF7" t="inlineStr"/>
-      <c r="FG7" t="inlineStr"/>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>2cPwbh8J</t>
+        </is>
+      </c>
+      <c r="FE7" t="inlineStr">
+        <is>
+          <t>raba daniel</t>
+        </is>
+      </c>
+      <c r="FF7" t="inlineStr">
+        <is>
+          <t>WWNny3e7</t>
+        </is>
+      </c>
+      <c r="FG7" t="inlineStr">
+        <is>
+          <t>rodriguez oscar</t>
+        </is>
+      </c>
       <c r="FH7" t="inlineStr"/>
       <c r="FI7" t="inlineStr"/>
+      <c r="FJ7" t="inlineStr">
+        <is>
+          <t>6qPig05P</t>
+        </is>
+      </c>
+      <c r="FK7" t="inlineStr">
+        <is>
+          <t>tapia renato</t>
+        </is>
+      </c>
+      <c r="FL7" t="inlineStr"/>
+      <c r="FM7" t="inlineStr"/>
+      <c r="FN7" t="inlineStr"/>
+      <c r="FO7" t="inlineStr"/>
+      <c r="FP7" t="inlineStr"/>
+      <c r="FQ7" t="inlineStr"/>
+      <c r="FR7" t="inlineStr"/>
+      <c r="FS7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0v264VE8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cardenas dani</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CzBEqCjK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>balliu ivan</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>fNu1l3xc</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>lejeune florian</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>K2JPoFRo</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>mumin abdul</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>vHFG4hw9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>espino alfonso</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>dYFtDut6</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lopez unai</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>fcuYevNb</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>valentin oscar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>UiH85aKC</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>de frutos jorge</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>x2AuZhpr</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>palazon isaac</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>OMUGUEla</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>garcia alvaro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>fFlZRkvF</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>camello sergio</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>byxc46yl</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>ter stegen marc andre</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>v36QVRPu</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>kounde jules</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>UgTrNwCF</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>cubarsi pau</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>AHeWolAk</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>martinez inigo</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>nBVu0v9a</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>martin gerard</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>pf3IOiFD</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>bernal marc</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>baBG8QuI</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>pedri</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>lAt3vEub</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>yamal lamine</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>xtBsDPam</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>raphinha</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>AVAVLaLt</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>torres ferran</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>MVC8zHZD</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>lewandowski robert</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>8Wuyaqc4</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>batalla augusto</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>hGPnN7fG</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>chavarria pep</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>zRB7v9IT</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ciss pathe</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>2i6AHS2l</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>diaz pedro</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>x8BHeb6c</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>embarba adri</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>YqyAyBrB</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>eto o pineda etienne</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>21xu5Zng</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>balboa pelayo</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>raqVZ405</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>gumbau gerard</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>dln9VIHe</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>aridane</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>M5IbUyg1</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>nketa randy</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>Eo8SAMoI</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>ratiu andrei</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>42E71F4r</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>trejo oscar</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>IZm6H2pp</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>astralaga aranguren ander</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>6c0CXHVM</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>balde alejandro</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>tAhLmeJb</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>casado marc</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>xStHx61d</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>cuenca andres</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>OClkc0eN</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>dominguez sergi</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>0l4CHjYp</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>fort hector</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>2c2ipETG</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>marin fermin</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>2oVBOlPg</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>olmo dani</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>M1W3ZQSs</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>pena inaki</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>zRB7v9IT</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>ciss pathe</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>zRB7v9IT</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>ciss pathe</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>dYFtDut6</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>lopez unai</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>x8BHeb6c</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>embarba adri</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>x8BHeb6c</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>embarba adri</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>OMUGUEla</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>garcia alvaro</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>M5IbUyg1</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>nketa randy</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>M5IbUyg1</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>nketa randy</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>fFlZRkvF</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>camello sergio</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>raqVZ405</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>gumbau gerard</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>raqVZ405</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>gumbau gerard</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>UiH85aKC</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>de frutos jorge</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>hGPnN7fG</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t>chavarria pep</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>hGPnN7fG</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>chavarria pep</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>fcuYevNb</t>
+        </is>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>valentin oscar</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>2oVBOlPg</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>olmo dani</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>2oVBOlPg</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>olmo dani</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>AVAVLaLt</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>torres ferran</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>6c0CXHVM</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>balde alejandro</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>6c0CXHVM</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>balde alejandro</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>nBVu0v9a</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>martin gerard</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>2c2ipETG</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>marin fermin</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>2c2ipETG</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>marin fermin</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>baBG8QuI</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>pedri</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>QkMhPUdc</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>delgado pau victor</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>QkMhPUdc</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>delgado pau victor</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>lAt3vEub</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>yamal lamine</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr"/>
+      <c r="EM8" t="inlineStr"/>
+      <c r="EN8" t="inlineStr"/>
+      <c r="EO8" t="inlineStr"/>
+      <c r="EP8" t="inlineStr"/>
+      <c r="EQ8" t="inlineStr"/>
+      <c r="ER8" t="inlineStr">
+        <is>
+          <t>MVcspA2M</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>de tomas raul</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
+      <c r="EV8" t="inlineStr">
+        <is>
+          <t>M3sbJix9</t>
+        </is>
+      </c>
+      <c r="EW8" t="inlineStr">
+        <is>
+          <t>araujo ronald</t>
+        </is>
+      </c>
+      <c r="EX8" t="inlineStr">
+        <is>
+          <t>bmlJ8bjQ</t>
+        </is>
+      </c>
+      <c r="EY8" t="inlineStr">
+        <is>
+          <t>barbera victor</t>
+        </is>
+      </c>
+      <c r="EZ8" t="inlineStr">
+        <is>
+          <t>ShxiZhJI</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="FB8" t="inlineStr">
+        <is>
+          <t>A1F3rz9c</t>
+        </is>
+      </c>
+      <c r="FC8" t="inlineStr">
+        <is>
+          <t>de jong frenkie</t>
+        </is>
+      </c>
+      <c r="FD8" t="inlineStr">
+        <is>
+          <t>4WR4dTws</t>
+        </is>
+      </c>
+      <c r="FE8" t="inlineStr">
+        <is>
+          <t>torre carral pablo</t>
+        </is>
+      </c>
+      <c r="FF8" t="inlineStr">
+        <is>
+          <t>QkMhPUdc</t>
+        </is>
+      </c>
+      <c r="FG8" t="inlineStr">
+        <is>
+          <t>delgado pau victor</t>
+        </is>
+      </c>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+      <c r="FL8" t="inlineStr"/>
+      <c r="FM8" t="inlineStr"/>
+      <c r="FN8" t="inlineStr">
+        <is>
+          <t>dUPVnxzP</t>
+        </is>
+      </c>
+      <c r="FO8" t="inlineStr">
+        <is>
+          <t>fati ansu</t>
+        </is>
+      </c>
+      <c r="FP8" t="inlineStr">
+        <is>
+          <t>AyxD3I5C</t>
+        </is>
+      </c>
+      <c r="FQ8" t="inlineStr">
+        <is>
+          <t>garcia eric</t>
+        </is>
+      </c>
+      <c r="FR8" t="inlineStr">
+        <is>
+          <t>xrV9v8CU</t>
+        </is>
+      </c>
+      <c r="FS8" t="inlineStr">
+        <is>
+          <t>gavi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>x2RBbu6T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lA1Qa7LH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>escandell aaron</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CxnAZJbo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>luengo oier</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>bD41lxAF</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>costas david</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>fgJYtAmE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>calvo dani</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>69aNbb67</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>alhassane rahim</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>QZ5Y2SPf</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>chaira ilyas</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>CMhGvpU0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>del moral alberto</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rVt0F12N</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>cazorla santi</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>l88RYMiD</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>moyano francisco</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ljVRztTj</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>alemao</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>GODeIoHH</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>hassan haissem</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>IPkF6s5H</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>ezkieta jokin</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>hCaJleT0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>michelin clement</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>fogIyhDp</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hernando manu</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>vwcbjRMJ</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>montero francisco</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>YVGq2FQ6</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>garcia saul</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>OAI6QtxN</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>aldasoro aritz</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>jm5x4JNf</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>vencedor unai</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>jm3RjZt2</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>martin andres</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>xj86hQ3C</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>vicente inigo</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>jDKBJJ9H</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>pablo</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0AlVvNwC</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>arana gomez juan carlos</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>Cjw1V4uo</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>ahijado lucas</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>ngBNZ9LM</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>braat quentin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>jsRoAy4E</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>suarez cardero alejandro</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>zq5tx9ZS</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>colombatto santiago</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>KhzzCbCU</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>de la fuente pau</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>YeImVH7d</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>dotor carlos</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>QwD9sQn9</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>lemos alvaro</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>O608W9Wj</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>mascarenhas francisco</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>GxH7SxPr</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>paraschiv daniel george</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>fBb6eDAH</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>pomares carlos</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>fTaJnuP8</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>seoane jaime</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>vg9tJMbL</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>sibo kwasi</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>vwj8fVTt</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>camara suleiman</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>88fszyHn</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>carrascal marco</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>lAOXx9U7</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>castro urdin javier</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>nDpCW7DC</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>garcia mario</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>6Dgp85mc</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>gueye maguette</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>Ysb0B298</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>junior lago</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>xChow1PH</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>karrikaburu jon</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>tQ5ht3jI</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>moreno pol</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>v1Ti8Jup</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>parera miquel</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>Cjw1V4uo</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>ahijado lucas</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>Cjw1V4uo</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>ahijado lucas</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>CxnAZJbo</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>luengo oier</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>YeImVH7d</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>dotor carlos</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>YeImVH7d</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>dotor carlos</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>CMhGvpU0</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>del moral alberto</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>zq5tx9ZS</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>colombatto santiago</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>zq5tx9ZS</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>colombatto santiago</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>l88RYMiD</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>moyano francisco</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>O608W9Wj</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>mascarenhas francisco</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>O608W9Wj</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>mascarenhas francisco</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>rVt0F12N</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>cazorla santi</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>KhzzCbCU</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>de la fuente pau</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>KhzzCbCU</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>de la fuente pau</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>QZ5Y2SPf</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>chaira ilyas</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>Egjuac7e</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>sainz maza inigo</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>Egjuac7e</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>sainz maza inigo</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>jDKBJJ9H</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>pablo</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>xChow1PH</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>karrikaburu jon</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>xChow1PH</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>karrikaburu jon</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>0AlVvNwC</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>arana gomez juan carlos</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>vwj8fVTt</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>camara suleiman</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>vwj8fVTt</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>camara suleiman</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>jm3RjZt2</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>martin andres</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>lAOXx9U7</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>castro urdin javier</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>lAOXx9U7</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>castro urdin javier</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>fogIyhDp</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>hernando manu</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>IuIj7V6O</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>sangalli marco</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
+          <t>IuIj7V6O</t>
+        </is>
+      </c>
+      <c r="EO9" t="inlineStr">
+        <is>
+          <t>sangalli marco</t>
+        </is>
+      </c>
+      <c r="EP9" t="inlineStr">
+        <is>
+          <t>hCaJleT0</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t>michelin clement</t>
+        </is>
+      </c>
+      <c r="ER9" t="inlineStr"/>
+      <c r="ES9" t="inlineStr"/>
+      <c r="ET9" t="inlineStr"/>
+      <c r="EU9" t="inlineStr"/>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
+      <c r="EX9" t="inlineStr"/>
+      <c r="EY9" t="inlineStr"/>
+      <c r="EZ9" t="inlineStr"/>
+      <c r="FA9" t="inlineStr"/>
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>Egjuac7e</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
+          <t>sainz maza inigo</t>
+        </is>
+      </c>
+      <c r="FF9" t="inlineStr">
+        <is>
+          <t>IuIj7V6O</t>
+        </is>
+      </c>
+      <c r="FG9" t="inlineStr">
+        <is>
+          <t>sangalli marco</t>
+        </is>
+      </c>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="inlineStr"/>
+      <c r="FN9" t="inlineStr"/>
+      <c r="FO9" t="inlineStr"/>
+      <c r="FP9" t="inlineStr"/>
+      <c r="FQ9" t="inlineStr"/>
+      <c r="FR9" t="inlineStr"/>
+      <c r="FS9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8MZf2N64</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>jPxdddKn</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>zidane luca</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>bygZPyD7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sanchez ricard</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>YiUPEL9t</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>rubio miguel</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2PZuGsll</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>insua pablo</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>n5JmutJP</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>neva carlos</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Qq6pTCV6</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>tsitaishvili giorgi</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>lSKS5xcF</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>hongla martin</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>QZtXmJ94</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>villar gonzalo</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>E77oeEa6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>trigueros manuel</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>YiAqdTFb</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>boye lucas</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>AN4BmAif</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>uzuni myrto</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>lCAHqdrp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>jimenez dani</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>nyxEi6on</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>abad jose toni</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>GCW1cIvp</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>blasco jeremy</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>vkZyDCe0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>pulido ruben</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>fsjkK41s</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>pulido jorge</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>hG15cPG8</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>vilarrasa ignasi</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>WKZZtJEE</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>perez mateo javier</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>bca3igNk</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>sielva oscar</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>fmp1pdv1</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>munoz joaquin</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>riikyhEG</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>soko patrick</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>rF4Be8Yj</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>enrich sergio</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>AsdIWlXn</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>balde siren</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0EXj8XA8</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>brau miguel</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>WEjccUQr</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>corbeanu theodor</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>E3BsytEA</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>martinez marc</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>xdh9EmXK</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>miquel ignasi</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>6NWnm0oL</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>oscar naasei oppong</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>roNCubET</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>rodelas sergio</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>lvN1Z92B</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>ruiz sergio</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>UPLFNnyN</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>saenz ezquerra pablo</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>IVs2nF0f</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>sanchez ruben</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>YTgDvwwU</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>weissman shon</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>dWVXsr1m</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>williams loic</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>j7UjY8ZD</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>anglada hugo</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>hvwCqMdo</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>arguigue ayman</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>plM3yHRN</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>fita alex</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>OK9jn5Tm</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>gonzalez cabanes diego</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>8QF1BiDA</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>hernandez javier</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>I3ZFJ978</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>kortajarena iker</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>AiQraYCR</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>jordi</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>GE65dlKG</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>mier javi</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>WxeiCXE4</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>perez juan</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>YTgDvwwU</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>weissman shon</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>YTgDvwwU</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>weissman shon</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>QZtXmJ94</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>villar gonzalo</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>dWVXsr1m</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>williams loic</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>dWVXsr1m</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>williams loic</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>2PZuGsll</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>insua pablo</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>UPLFNnyN</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>saenz ezquerra pablo</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>UPLFNnyN</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>saenz ezquerra pablo</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>YiAqdTFb</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>boye lucas</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>lvN1Z92B</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>ruiz sergio</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>lvN1Z92B</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>ruiz sergio</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>E77oeEa6</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>trigueros manuel</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>IVs2nF0f</t>
+        </is>
+      </c>
+      <c r="DI10" t="inlineStr">
+        <is>
+          <t>sanchez ruben</t>
+        </is>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>IVs2nF0f</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>sanchez ruben</t>
+        </is>
+      </c>
+      <c r="DL10" t="inlineStr">
+        <is>
+          <t>Qq6pTCV6</t>
+        </is>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>tsitaishvili giorgi</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>OWvS7e5J</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>vallejo hugo</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>OWvS7e5J</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
+          <t>vallejo hugo</t>
+        </is>
+      </c>
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>riikyhEG</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>soko patrick</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>vu4cWvkc</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>valentin gerard</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>vu4cWvkc</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>valentin gerard</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>nyxEi6on</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>abad jose toni</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>AiQraYCR</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>jordi</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>AiQraYCR</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>jordi</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>rF4Be8Yj</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>enrich sergio</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>I3ZFJ978</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>kortajarena iker</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>I3ZFJ978</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>kortajarena iker</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>fmp1pdv1</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>munoz joaquin</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>GE65dlKG</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>mier javi</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr">
+        <is>
+          <t>GE65dlKG</t>
+        </is>
+      </c>
+      <c r="EO10" t="inlineStr">
+        <is>
+          <t>mier javi</t>
+        </is>
+      </c>
+      <c r="EP10" t="inlineStr">
+        <is>
+          <t>WKZZtJEE</t>
+        </is>
+      </c>
+      <c r="EQ10" t="inlineStr">
+        <is>
+          <t>perez mateo javier</t>
+        </is>
+      </c>
+      <c r="ER10" t="inlineStr"/>
+      <c r="ES10" t="inlineStr"/>
+      <c r="ET10" t="inlineStr"/>
+      <c r="EU10" t="inlineStr"/>
+      <c r="EV10" t="inlineStr"/>
+      <c r="EW10" t="inlineStr"/>
+      <c r="EX10" t="inlineStr"/>
+      <c r="EY10" t="inlineStr"/>
+      <c r="EZ10" t="inlineStr"/>
+      <c r="FA10" t="inlineStr"/>
+      <c r="FB10" t="inlineStr"/>
+      <c r="FC10" t="inlineStr"/>
+      <c r="FD10" t="inlineStr">
+        <is>
+          <t>2VnkplNm</t>
+        </is>
+      </c>
+      <c r="FE10" t="inlineStr">
+        <is>
+          <t>unzueta iker</t>
+        </is>
+      </c>
+      <c r="FF10" t="inlineStr">
+        <is>
+          <t>vu4cWvkc</t>
+        </is>
+      </c>
+      <c r="FG10" t="inlineStr">
+        <is>
+          <t>valentin gerard</t>
+        </is>
+      </c>
+      <c r="FH10" t="inlineStr"/>
+      <c r="FI10" t="inlineStr"/>
+      <c r="FJ10" t="inlineStr">
+        <is>
+          <t>OWvS7e5J</t>
+        </is>
+      </c>
+      <c r="FK10" t="inlineStr">
+        <is>
+          <t>vallejo hugo</t>
+        </is>
+      </c>
+      <c r="FL10" t="inlineStr"/>
+      <c r="FM10" t="inlineStr"/>
+      <c r="FN10" t="inlineStr"/>
+      <c r="FO10" t="inlineStr"/>
+      <c r="FP10" t="inlineStr"/>
+      <c r="FQ10" t="inlineStr"/>
+      <c r="FR10" t="inlineStr"/>
+      <c r="FS10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FK3"/>
+  <dimension ref="A1:FO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,2028 +871,6694 @@
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_away_11</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_11</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_12</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_12</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
       <c r="FH1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>67jtezzI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>lxnsUkIc</t>
+          <t>EJs3SlPl</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mamardashvili giorgi</t>
+          <t>fernando</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sv5sgVLE</t>
+          <t>hrUwhqn3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>correia thierry</t>
+          <t>centelles alex</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CIrZ775M</t>
+          <t>jDh6SEKj</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>tarrega cesar</t>
+          <t>radovanovic aleksandar</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4O15XViB</t>
+          <t>0KsyLPE4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>mosquera cristhian</t>
+          <t>chumi</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>p0AiQXJi</t>
+          <t>8EZ7QILP</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>abajas rodrigo</t>
+          <t>pubill pages marc</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2iri9TaP</t>
+          <t>U1OOFFBl</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>canos sergi</t>
+          <t>ribaudo nico</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>nosv3azp</t>
+          <t>nHPmbQaR</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>pepelu</t>
+          <t>lopy dion</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>jV6oTuS1</t>
+          <t>pCJBsskE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>barrenechea enzo</t>
+          <t>gonzalez edgar</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>h8cBI9v2</t>
+          <t>GIzJfhLr</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>rioja luis</t>
+          <t>arribas sergio</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>UVDJACJ9</t>
+          <t>fV4fAvB8</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>gomez daniel</t>
+          <t>suarez luis</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>EP4vWYSf</t>
+          <t>dILCwx5p</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>duro hugo</t>
+          <t>leo baptistao</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>25zBQ1q4</t>
+          <t>4Aa1KcL9</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>cillessen jasper</t>
+          <t>rivero cristian</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>tYi46reg</t>
+          <t>tt4Mm9ws</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>viti</t>
+          <t>rueda javier</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>fBI7cV4b</t>
+          <t>OAHrCN0T</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>alex suarez</t>
+          <t>aguilar lalo</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>AerDGNDO</t>
+          <t>Y9HNvyBJ</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>mckenna scott</t>
+          <t>martinez ros</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>xlaNl83K</t>
+          <t>lAgIB16T</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>munoz alex</t>
+          <t>alvaro</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6qyeYCYO</t>
+          <t>Y7vZ4xCl</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>januzaj adnan</t>
+          <t>morcillo jon</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>djA5LwVQ</t>
+          <t>4CIfCKQ5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>essugo dario</t>
+          <t>rodriguez riki</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>KE0WWa1e</t>
+          <t>zo61BrW3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>campana jose</t>
+          <t>marchan rai</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>OKNQawg3</t>
+          <t>tdCq3gMJ</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>kirian</t>
+          <t>agus medina</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>b5g6gWjn</t>
+          <t>lAyK4sZ3</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>moleiro alberto</t>
+          <t>quiles alberto</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>YaEnqMoU</t>
+          <t>0zIF6Wg2</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>silva fabio</t>
+          <t>fidel</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>WO3oyVW7</t>
+          <t>0M5sG7Bk</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>almeida andre</t>
+          <t>fettal rachad</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>xOixiUwd</t>
+          <t>lh0DDoRr</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>caufriez maximiliano</t>
+          <t>guedes guilherme</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2axfsTHA</t>
+          <t>fDlwwgkH</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>dimitrievski stole</t>
+          <t>iribarne bruno</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>KbobTIgr</t>
+          <t>Eks5aVRG</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>domenech jaume</t>
+          <t>kaiky</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>65F8DTep</t>
+          <t>8xxQPuzJ</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>foulquier dimitri</t>
+          <t>langa bruno alberto</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4UxxcIjS</t>
+          <t>Y9vWlK55</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>hernadis yarek gasiorowski</t>
+          <t>marezi</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>xWguLPCU</t>
+          <t>lfgji9jR</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>gaya jose</t>
+          <t>maximiano luis</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2yyy00aj</t>
+          <t>nN06Zcrh</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>guerra javi</t>
+          <t>melero gonzalo</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>Wpw94bj6</t>
+          <t>lEgtMYw4</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>guillamon hugo</t>
+          <t>pozo alejandro</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>SGjehmsG</t>
+          <t>OMxL6tQB</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>lopez noguerol diego</t>
+          <t>puigmal arnau</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>bePNNa1r</t>
+          <t>rHTsMGzn</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>perez francisco</t>
+          <t>sersif saif</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>Y5mwR9gL</t>
+          <t>UBj2E1Go</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>valera german</t>
+          <t>sanz paco</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>AkH99Ojn</t>
+          <t>4SRz95Sf</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>cardona marc</t>
+          <t>alcedo juan</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>UaHeoBot</t>
+          <t>04xrBl5d</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>fuster manuel</t>
+          <t>de la casa eduardo</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>fgqxKdwL</t>
+          <t>vwcobdxb</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>gonzalez fabio</t>
+          <t>garcia jon</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>xrJQVv9C</t>
+          <t>OCmIC7xi</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>herzog juanma</t>
+          <t>garcia juanma</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>nw5d39V0</t>
+          <t>0YMlqiSM</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>horkas dinko</t>
+          <t>raul</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>lQJaaIBC</t>
+          <t>pO1wPsLU</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>munoz javier</t>
+          <t>melendez alejandro</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>px36Cwpj</t>
+          <t>GtEDHjtF</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>loiodice enzo</t>
+          <t>moreno marcos</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>Cz3awDFR</t>
+          <t>ziGOv0PB</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>marmol mika</t>
+          <t>pacheco antonio</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>r92RZve6</t>
+          <t>C87DdLot</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>mata jaime</t>
+          <t>rubayo neco</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>rNFSg6i4</t>
+          <t>hxlYqfYQ</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>mcburnie oliver</t>
+          <t>villar javi</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>St8XPCaD</t>
+          <t>nN06Zcrh</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>pejino</t>
+          <t>melero gonzalo</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>pjIG0H3d</t>
+          <t>nN06Zcrh</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>ramirez benito</t>
+          <t>melero gonzalo</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>WO3oyVW7</t>
+          <t>jDh6SEKj</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>almeida andre</t>
+          <t>radovanovic aleksandar</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>WO3oyVW7</t>
+          <t>OMxL6tQB</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>almeida andre</t>
+          <t>puigmal arnau</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>jV6oTuS1</t>
+          <t>OMxL6tQB</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>barrenechea enzo</t>
+          <t>puigmal arnau</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>SGjehmsG</t>
+          <t>U1OOFFBl</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>lopez noguerol diego</t>
+          <t>ribaudo nico</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>SGjehmsG</t>
+          <t>0M5sG7Bk</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>lopez noguerol diego</t>
+          <t>fettal rachad</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>2iri9TaP</t>
+          <t>0M5sG7Bk</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>canos sergi</t>
+          <t>fettal rachad</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>xWguLPCU</t>
+          <t>GIzJfhLr</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>gaya jose</t>
+          <t>arribas sergio</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>xWguLPCU</t>
+          <t>Y9vWlK55</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>gaya jose</t>
+          <t>marezi</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>p0AiQXJi</t>
+          <t>Y9vWlK55</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>abajas rodrigo</t>
+          <t>marezi</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>65F8DTep</t>
+          <t>fV4fAvB8</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>foulquier dimitri</t>
+          <t>suarez luis</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>65F8DTep</t>
+          <t>Eks5aVRG</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>foulquier dimitri</t>
+          <t>kaiky</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>Sv5sgVLE</t>
+          <t>Eks5aVRG</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>correia thierry</t>
+          <t>kaiky</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>2yyy00aj</t>
+          <t>nHPmbQaR</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>guerra javi</t>
+          <t>lopy dion</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>2yyy00aj</t>
+          <t>GtEDHjtF</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>guerra javi</t>
+          <t>moreno marcos</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>UVDJACJ9</t>
+          <t>GtEDHjtF</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>gomez daniel</t>
+          <t>moreno marcos</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>lQJaaIBC</t>
+          <t>lAyK4sZ3</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>munoz javier</t>
+          <t>quiles alberto</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>lQJaaIBC</t>
+          <t>4SRz95Sf</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>munoz javier</t>
+          <t>alcedo juan</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>KE0WWa1e</t>
+          <t>4SRz95Sf</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>campana jose</t>
+          <t>alcedo juan</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>AkH99Ojn</t>
+          <t>tt4Mm9ws</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>cardona marc</t>
+          <t>rueda javier</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>AkH99Ojn</t>
+          <t>OCmIC7xi</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>cardona marc</t>
+          <t>garcia juanma</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>YaEnqMoU</t>
+          <t>OCmIC7xi</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>silva fabio</t>
+          <t>garcia juanma</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>rNFSg6i4</t>
+          <t>Y7vZ4xCl</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>mcburnie oliver</t>
+          <t>morcillo jon</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>rNFSg6i4</t>
+          <t>vwcobdxb</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>mcburnie oliver</t>
+          <t>garcia jon</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>6qyeYCYO</t>
+          <t>vwcobdxb</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>januzaj adnan</t>
+          <t>garcia jon</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>pjIG0H3d</t>
+          <t>OAHrCN0T</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>ramirez benito</t>
+          <t>aguilar lalo</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>pjIG0H3d</t>
+          <t>ziGOv0PB</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>ramirez benito</t>
+          <t>pacheco antonio</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>tYi46reg</t>
+          <t>ziGOv0PB</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>viti</t>
+          <t>pacheco antonio</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>xrJQVv9C</t>
+          <t>4CIfCKQ5</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>herzog juanma</t>
+          <t>rodriguez riki</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>xrJQVv9C</t>
+          <t>bVRknfbT</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>herzog juanma</t>
+          <t>robertone lucas</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>xlaNl83K</t>
+          <t>nsEvRNJH</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>munoz alex</t>
+          <t>costa jaume</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>2gqO56Xu</t>
+          <t>U3NYWaPL</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>diakhaby mouctar</t>
-        </is>
-      </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>IXRaCzVt</t>
-        </is>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>mir rafael</t>
-        </is>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>M5U2cN2q</t>
-        </is>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>vazquez jesus</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>jTdCpLmR</t>
-        </is>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>gil ivan</t>
-        </is>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>SjTBQO7b</t>
-        </is>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>park marvin</t>
-        </is>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>fapXP9VS</t>
-        </is>
-      </c>
-      <c r="FI2" t="inlineStr">
-        <is>
-          <t>ramirez sandro</t>
-        </is>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>hSNXqigO</t>
-        </is>
-      </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>sinkgraven daley</t>
-        </is>
-      </c>
+          <t>lazo jose carlos</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr"/>
+      <c r="FA2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="inlineStr"/>
+      <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
+      <c r="FH2" t="inlineStr"/>
+      <c r="FI2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
+      <c r="FL2" t="inlineStr"/>
+      <c r="FM2" t="inlineStr"/>
+      <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WWCsJtN0</t>
+          <t>CpD7BeKb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0YMlqiSM</t>
+          <t>E34WEy2D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>raul</t>
+          <t>fernandez andres</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tt4Mm9ws</t>
+          <t>bNOatO8R</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rueda javier</t>
+          <t>garcia andres</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vwcobdxb</t>
+          <t>Cn91dgeB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>garcia jon</t>
+          <t>elgezabal unai</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OAHrCN0T</t>
+          <t>O6MiTbze</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>aguilar lalo</t>
+          <t>de la fuente adrian</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4SRz95Sf</t>
+          <t>x0EyRyUD</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>alcedo juan</t>
+          <t>navarro marcos</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0zIF6Wg2</t>
+          <t>SIemT8iq</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>fidel</t>
+          <t>kochorashvili giorgi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4CIfCKQ5</t>
+          <t>UqPEcOA0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>rodriguez riki</t>
+          <t>martinez pablo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>pO1wPsLU</t>
+          <t>Eguxo4bb</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>melendez alejandro</t>
+          <t>alvarez carlos</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>OCmIC7xi</t>
+          <t>6s42ZkRu</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>garcia juanma</t>
+          <t>lozano sergio</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>lAyK4sZ3</t>
+          <t>jXCYJBqg</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>quiles alberto</t>
+          <t>morales jose</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>jXnN4QhP</t>
+          <t>lbxUqXq3</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>marin higinio</t>
+          <t>romero ivan</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>rPMUGw3h</t>
+          <t>OtuX2bMG</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>cantero ander</t>
+          <t>leite helton</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6aaUe854</t>
+          <t>UVspkTsq</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>pipa</t>
+          <t>petxa alex</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>hQpQJSqn</t>
+          <t>4b3CXnY3</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>cordoba aitor</t>
+          <t>vazquez perez pablo</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>S2nS0dZr</t>
+          <t>4AnCE6ed</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>lopez david</t>
+          <t>barcia dani</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>46wCqoNi</t>
+          <t>z3xcnF35</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>miguel florian</t>
+          <t>obrador rafael</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>UPMWp37R</t>
+          <t>n1QEm2xS</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>ojeda daniel</t>
+          <t>mella david</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4fkoGF10</t>
+          <t>bHQuQjuQ</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>navarro raul</t>
+          <t>patino charlie</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0poEwxl4</t>
+          <t>jeHmEmdJ</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>atienza miguel</t>
+          <t>villares diego</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>S8CD3sIU</t>
+          <t>pEIRfpB9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>cordoba inigo</t>
+          <t>soriano m</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>EPzCN58J</t>
+          <t>4zhDcXCG</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>nino fer</t>
+          <t>hernandez yeremay</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>v1g9lCm3</t>
+          <t>YsCMvAvd</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>curro sanchez</t>
+          <t>perez lucas</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>tdCq3gMJ</t>
+          <t>fc2WJMqH</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>agus medina</t>
+          <t>alcaniz edgar</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>04xrBl5d</t>
+          <t>Yqzk346P</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>de la casa eduardo</t>
+          <t>clemente oscar</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Y7vZ4xCl</t>
+          <t>hUTZz8kN</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>morcillo jon</t>
+          <t>cortina borja</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>GtEDHjtF</t>
+          <t>WURwLTen</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>moreno marcos</t>
+          <t>espi carlos</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>ziGOv0PB</t>
+          <t>40xtISfU</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>pacheco antonio</t>
+          <t>fabricio</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>UPPB60Pb</t>
+          <t>ln6I6cmp</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>pulpon joan</t>
+          <t>fernandez victor</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>zo61BrW3</t>
+          <t>OA13bbjO</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>marchan rai</t>
+          <t>selles david</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>4Aa1KcL9</t>
+          <t>h0k7PBq5</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>rivero cristian</t>
+          <t>vacas alfonso pastor</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>lAgIB16T</t>
+          <t>KK19HiR5</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>alvaro</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>Y9HNvyBJ</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>martinez ros</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>hxlYqfYQ</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>villar javi</t>
-        </is>
-      </c>
+          <t>grande xavier</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>AyAxdOaP</t>
+          <t>jy8D4VqS</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>arroyo anderson</t>
+          <t>alfaro alejandro</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>hQU1V6u9</t>
+          <t>21SuW5Vq</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>badiashile loic</t>
+          <t>ivan barbero</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>6kWRKUsC</t>
+          <t>INnNHikC</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>espiau edu</t>
+          <t>bouldini mohamed</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>rTFUvlCc</t>
+          <t>hM8jpBm7</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>exposito jimenez marcelo</t>
+          <t>davo</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>SvYjqpb0</t>
+          <t>8fZSyUbm</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>forns ian</t>
+          <t>escudero sergio</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>ljSkZFwn</t>
+          <t>UPakvWjd</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>gonzalez david</t>
+          <t>garcia pablo</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>KOBHwYGc</t>
+          <t>d8WbLTwp</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>lopez lisandro</t>
+          <t>herrera cristian</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>tSrz5SW1</t>
+          <t>I9kZL6aT</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>morante ivan</t>
+          <t>martinez pablo</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>8zZErFJT</t>
+          <t>QHP29Y9q</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>pascual hugo</t>
+          <t>navarro ximo</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>jDtJq91K</t>
+          <t>rX4BCOC6</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>rodriguez thomas</t>
+          <t>parreno german</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>nPkoWJvS</t>
+          <t>Yqzk346P</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>sanchez borja</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
+          <t>clemente oscar</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>Yqzk346P</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>clemente oscar</t>
+        </is>
+      </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>tdCq3gMJ</t>
+          <t>Eguxo4bb</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>agus medina</t>
+          <t>alvarez carlos</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>tdCq3gMJ</t>
+          <t>40xtISfU</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>agus medina</t>
+          <t>fabricio</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>jXnN4QhP</t>
+          <t>40xtISfU</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>marin higinio</t>
+          <t>fabricio</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>zo61BrW3</t>
+          <t>jXCYJBqg</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>marchan rai</t>
+          <t>morales jose</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>zo61BrW3</t>
+          <t>WURwLTen</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>marchan rai</t>
+          <t>espi carlos</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0zIF6Wg2</t>
+          <t>WURwLTen</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>fidel</t>
+          <t>espi carlos</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>lAgIB16T</t>
+          <t>lbxUqXq3</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>alvaro</t>
+          <t>romero ivan</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>lAgIB16T</t>
+          <t>KK19HiR5</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>alvaro</t>
+          <t>grande xavier</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>4CIfCKQ5</t>
+          <t>KK19HiR5</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>rodriguez riki</t>
+          <t>grande xavier</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>Y7vZ4xCl</t>
+          <t>UqPEcOA0</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>morcillo jon</t>
-        </is>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>Y7vZ4xCl</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>morcillo jon</t>
-        </is>
-      </c>
-      <c r="DL3" t="inlineStr">
-        <is>
-          <t>tt4Mm9ws</t>
-        </is>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>rueda javier</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr">
-        <is>
-          <t>GtEDHjtF</t>
-        </is>
-      </c>
-      <c r="DO3" t="inlineStr">
-        <is>
-          <t>moreno marcos</t>
-        </is>
-      </c>
+          <t>martinez pablo</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>GtEDHjtF</t>
+          <t>INnNHikC</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>moreno marcos</t>
+          <t>bouldini mohamed</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>OCmIC7xi</t>
+          <t>INnNHikC</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>garcia juanma</t>
+          <t>bouldini mohamed</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>nPkoWJvS</t>
+          <t>bHQuQjuQ</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>sanchez borja</t>
+          <t>patino charlie</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>nPkoWJvS</t>
+          <t>d8WbLTwp</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>sanchez borja</t>
+          <t>herrera cristian</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>UPMWp37R</t>
+          <t>d8WbLTwp</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>ojeda daniel</t>
+          <t>herrera cristian</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>tSrz5SW1</t>
+          <t>4zhDcXCG</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>morante ivan</t>
+          <t>hernandez yeremay</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>tSrz5SW1</t>
+          <t>QHP29Y9q</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>morante ivan</t>
+          <t>navarro ximo</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>0poEwxl4</t>
+          <t>QHP29Y9q</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>atienza miguel</t>
+          <t>navarro ximo</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>6kWRKUsC</t>
+          <t>UVspkTsq</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>espiau edu</t>
+          <t>petxa alex</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>6kWRKUsC</t>
+          <t>8fZSyUbm</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>espiau edu</t>
+          <t>escudero sergio</t>
         </is>
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>S8CD3sIU</t>
+          <t>8fZSyUbm</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>cordoba inigo</t>
+          <t>escudero sergio</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>ljSkZFwn</t>
+          <t>z3xcnF35</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>gonzalez david</t>
+          <t>obrador rafael</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>ljSkZFwn</t>
+          <t>21SuW5Vq</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>gonzalez david</t>
+          <t>ivan barbero</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>4fkoGF10</t>
+          <t>21SuW5Vq</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>navarro raul</t>
+          <t>ivan barbero</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>AyAxdOaP</t>
+          <t>YsCMvAvd</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>arroyo anderson</t>
+          <t>perez lucas</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>AyAxdOaP</t>
+          <t>biJcu016</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
         <is>
-          <t>arroyo anderson</t>
-        </is>
-      </c>
-      <c r="EV3" t="inlineStr">
-        <is>
-          <t>6aaUe854</t>
-        </is>
-      </c>
-      <c r="EW3" t="inlineStr">
-        <is>
-          <t>pipa</t>
-        </is>
-      </c>
-      <c r="EX3" t="inlineStr">
-        <is>
-          <t>nsEvRNJH</t>
-        </is>
-      </c>
-      <c r="EY3" t="inlineStr">
-        <is>
-          <t>costa jaume</t>
-        </is>
-      </c>
+          <t>algobia angel</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+      <c r="EX3" t="inlineStr"/>
+      <c r="EY3" t="inlineStr"/>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>U3NYWaPL</t>
+          <t>xfFOyHXH</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>lazo jose carlos</t>
-        </is>
-      </c>
-      <c r="FB3" t="inlineStr"/>
-      <c r="FC3" t="inlineStr"/>
+          <t>puerto eric</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>0Ca5CLYL</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>rama hugo</t>
+        </is>
+      </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>IijdLfIb</t>
+          <t>pWvRJqSt</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>brugue roger</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
         <is>
-          <t>KI3xYemP</t>
+          <t>vk0AZDyh</t>
         </is>
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>appin kevin</t>
-        </is>
-      </c>
-      <c r="FH3" t="inlineStr"/>
-      <c r="FI3" t="inlineStr"/>
-      <c r="FJ3" t="inlineStr"/>
-      <c r="FK3" t="inlineStr"/>
+          <t>cabello jorge</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t>nRwS5Ild</t>
+        </is>
+      </c>
+      <c r="FI3" t="inlineStr">
+        <is>
+          <t>iborra vicente</t>
+        </is>
+      </c>
+      <c r="FJ3" t="inlineStr">
+        <is>
+          <t>WpavKwjg</t>
+        </is>
+      </c>
+      <c r="FK3" t="inlineStr">
+        <is>
+          <t>pampin diego</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
+          <t>xhJNiaWc</t>
+        </is>
+      </c>
+      <c r="FM3" t="inlineStr">
+        <is>
+          <t>rey oriol</t>
+        </is>
+      </c>
+      <c r="FN3" t="inlineStr"/>
+      <c r="FO3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>U1eH0v6t</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G4b5p859</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>campos pablo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rqnIpvc8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>alcala pedro</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KrX5waGB</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>sipcic nikola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>juxRzfwF</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>kiko olivas</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>pSeqAJ0c</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>aguirregabiria martin</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MJcnwOI5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>munoz luis</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8xkqsBHk</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>musto marcelo daniel</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>nThR7Un8</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>guerrero sergio</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>KnJdARG3</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>teguia cedric</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>nFO9fFkl</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>izquierdo jairo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>46haE6np</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>valles gaston</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>pCDDvlwE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>san roman miguel</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>bqApK6mO</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>mario gaspar</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>SY7HnwqR</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>diaby bambo</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>EFLxG99f</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>affengruber david</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>8hRjcgC9</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>martin alex</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>fJhTE3Am</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>fernandez mercau nicolas</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>fXhTGGuq</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>hernandez gerard</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>ERmJI7HF</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>salvador cristian</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>l622RoNj</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>rashani elbasan</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>lhUwqUHS</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>plano oscar</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>QBUkVLpD</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>kaba sory</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>WMnz8BzK</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>andy</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>baZ7aMTa</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>escriche daniel</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>hxZkR0j0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>gonzalez hugo sotos</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>vRNUBqy4</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>moreno jorge</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>SMQVytwr</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>nono</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6DIWoQi4</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>ortuno alfredo</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>xnPUpahj</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>reyes jhafets</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>IilHTmj9</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>rios reina jose</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>nJwfryI5</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>ayton roman lucas</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>KK2GPNcn</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>vukcevic andrija</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>tzAxVrkH</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>alvarez agustin</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>jkeA7fag</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>barzic matia</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>8docB4Zn</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>bigas pedro</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>6uLxUVCT</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>dituro matias</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>27MtyaII</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>el ghezouani mourad</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>IylSu6Jk</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>febas aleix</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>44n8ClyK</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>gutierrez jose</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>YNiXFzek</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>mendoza rodrigo</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>U93anmS8</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>nunez alvaro</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>WnnjuJl7</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>rafael leonardo nunez mata</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>KK2GPNcn</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>vukcevic andrija</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>KK2GPNcn</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>vukcevic andrija</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>nFO9fFkl</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>izquierdo jairo</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>hxZkR0j0</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>gonzalez hugo sotos</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>hxZkR0j0</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>gonzalez hugo sotos</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>KnJdARG3</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>teguia cedric</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>WMnz8BzK</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>andy</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>WMnz8BzK</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>andy</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>nThR7Un8</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>guerrero sergio</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>6DIWoQi4</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>ortuno alfredo</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>6DIWoQi4</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>ortuno alfredo</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>46haE6np</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>valles gaston</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>8docB4Zn</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>bigas pedro</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>8docB4Zn</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>bigas pedro</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>SY7HnwqR</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>diaby bambo</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>IylSu6Jk</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>febas aleix</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>IylSu6Jk</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>febas aleix</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>fXhTGGuq</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>hernandez gerard</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>tzAxVrkH</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>alvarez agustin</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>tzAxVrkH</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>alvarez agustin</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>lhUwqUHS</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>plano oscar</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>YNiXFzek</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>mendoza rodrigo</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>YNiXFzek</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>mendoza rodrigo</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>8hRjcgC9</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>martin alex</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>WnnjuJl7</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>rafael leonardo nunez mata</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>WnnjuJl7</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>rafael leonardo nunez mata</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>ERmJI7HF</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>salvador cristian</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t>rTha6jsL</t>
+        </is>
+      </c>
+      <c r="EW4" t="inlineStr">
+        <is>
+          <t>clerc carlos</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t>G4s5mw5N</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>josan</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>fXlAtRep</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>salinas jose</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>fRxu5Qk7</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>alonso yago</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr"/>
+      <c r="FE4" t="inlineStr"/>
+      <c r="FF4" t="inlineStr"/>
+      <c r="FG4" t="inlineStr"/>
+      <c r="FH4" t="inlineStr"/>
+      <c r="FI4" t="inlineStr"/>
+      <c r="FJ4" t="inlineStr"/>
+      <c r="FK4" t="inlineStr"/>
+      <c r="FL4" t="inlineStr"/>
+      <c r="FM4" t="inlineStr"/>
+      <c r="FN4" t="inlineStr"/>
+      <c r="FO4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>GIJbDHkn</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IPkF6s5H</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ezkieta jokin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IuIj7V6O</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sangalli marco</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>fogIyhDp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hernando manu</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>lAOXx9U7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>castro urdin javier</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>YVGq2FQ6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>garcia saul</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Egjuac7e</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>sainz maza inigo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OAI6QtxN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>aldasoro aritz</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>vwj8fVTt</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>camara suleiman</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>xj86hQ3C</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>vicente inigo</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Ysb0B298</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>junior lago</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>xChow1PH</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>karrikaburu jon</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>WGae8d9E</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>marin carlos</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>S4KW2ean</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>albarran carlos</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>O6hVP1TB</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ruiz adrian</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>SGenrabG</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>marvel</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>8t3vtwdc</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>calderon jose</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>veLxs2Gg</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>sala alex</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ULtviY7o</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>ruiz isma</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>pEbUeTNb</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>zalazar kuki</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>j9FVq54i</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>carracedo cristian</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>trR2Luu5</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>casas antonio</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Qav8SAwf</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>rodriganez jacobo</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0AlVvNwC</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>arana gomez juan carlos</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>88fszyHn</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>carrascal marco</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>nDpCW7DC</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>garcia mario</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>6Dgp85mc</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>gueye maguette</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>I5Wp9VUq</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>jeremy arevalo</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>jm3RjZt2</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>martin andres</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>vwcbjRMJ</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>montero francisco</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>v1Ti8Jup</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>parera miquel</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>jDKBJJ9H</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>pablo</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>jm5x4JNf</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>vencedor unai</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>4EctXe5U</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>zenitagoia arana ekain</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>xAhhX5Vm</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>munoz carlos</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>OU1rIZsa</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>lopez alex</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>jwvNqlFq</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>antonio martinez jose</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>YsOcklca</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>obolskiy nikolay</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>Agk5MJwd</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>rodriguez genaro</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>IV8hD3Am</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>sintes xavi</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>CfBHradb</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>soonsup bell jude</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>KAc8u2f4</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>vila ramon</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>fu9bjNgL</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>aizagar ander yoldi</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>f5JqWchj</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>zidane theo</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>0AlVvNwC</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>arana gomez juan carlos</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>0AlVvNwC</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>arana gomez juan carlos</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>xChow1PH</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>karrikaburu jon</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>jm3RjZt2</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>martin andres</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>jm3RjZt2</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>martin andres</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>vwj8fVTt</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>camara suleiman</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>6Dgp85mc</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>gueye maguette</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>6Dgp85mc</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>gueye maguette</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>Egjuac7e</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>sainz maza inigo</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>4EctXe5U</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>zenitagoia arana ekain</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>4EctXe5U</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>zenitagoia arana ekain</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>xj86hQ3C</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
+          <t>vicente inigo</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>jDKBJJ9H</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>pablo</t>
+        </is>
+      </c>
+      <c r="DL5" t="inlineStr">
+        <is>
+          <t>jDKBJJ9H</t>
+        </is>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>pablo</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>Ysb0B298</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>junior lago</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>f5JqWchj</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>zidane theo</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>f5JqWchj</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>zidane theo</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>veLxs2Gg</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>sala alex</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>fu9bjNgL</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>aizagar ander yoldi</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>fu9bjNgL</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>aizagar ander yoldi</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>pEbUeTNb</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>zalazar kuki</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>xAhhX5Vm</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>munoz carlos</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>xAhhX5Vm</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>munoz carlos</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>S4KW2ean</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>albarran carlos</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>Agk5MJwd</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>rodriguez genaro</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>Agk5MJwd</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>rodriguez genaro</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>trR2Luu5</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>casas antonio</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>YsOcklca</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>obolskiy nikolay</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>YsOcklca</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>obolskiy nikolay</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t>j9FVq54i</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>carracedo cristian</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>drMfy7JB</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>mantilla alvaro</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+      <c r="EX5" t="inlineStr"/>
+      <c r="EY5" t="inlineStr"/>
+      <c r="EZ5" t="inlineStr"/>
+      <c r="FA5" t="inlineStr"/>
+      <c r="FB5" t="inlineStr"/>
+      <c r="FC5" t="inlineStr"/>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>hCaJleT0</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>michelin clement</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr"/>
+      <c r="FG5" t="inlineStr"/>
+      <c r="FH5" t="inlineStr"/>
+      <c r="FI5" t="inlineStr"/>
+      <c r="FJ5" t="inlineStr"/>
+      <c r="FK5" t="inlineStr"/>
+      <c r="FL5" t="inlineStr"/>
+      <c r="FM5" t="inlineStr"/>
+      <c r="FN5" t="inlineStr"/>
+      <c r="FO5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>06qkgE4U</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hY8G1T3f</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>daniel fuzato</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6FZTZse6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>carrillo alvaro</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>jZrmTaWb</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>arrillaga hodei</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kjc7Gst2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>chema</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>r9rn0Wtd</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>merquelanz martin</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>WANBOspq</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>alvarez sergio</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SYXL5EpQ</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>pereira matheus</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>OpN8BXQ8</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>villa toni</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>tY9B9R8R</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>corpas jose</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Y7dM1nsL</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>jon bautista orgilles</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SMRPNG5i</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>puertas antonio</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>CQmSCTxB</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>caro jose antonio</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>xbrr5N5M</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>zaldua joseba</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2cLeSIk1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>chust victor</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>GzloPZi6</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>antonio cristian</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>p2e5RJp3</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>kovacevic bojan</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0I0RtqEN</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>alejo ivan</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ferBlfmN</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>escalante gonzalo</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>SK8upGdH</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>fede</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>4rn7WXta</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>de la rosa jose antonio</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>YioE1eTi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>sobrino ruben</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>xnYg4l8i</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>ramos christopher</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>CIeqjmkH</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>alkain xeber</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>xOUihsv0</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>carrasco oscar</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>xfS51jmd</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>cubero sergio</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>4tgH7UUS</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>gutierrez cristian</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>lEesZsYr</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>hashimoto kento</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>6Rvb9XRN</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>madariaga ander</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>U97akWoJ</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>magunagoitia jonmi</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>f1i71kYp</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>nolaskoain peru</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>MNbqVtWt</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>pascual jorge</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>2BPxaq2B</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>raul gimenez</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>lUkrLco1</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>slavy</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>C69kFYEO</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>alarcon tomas</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>dKEu5Txk</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>alcaraz ruben</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>CUi1nPXC</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>isaac carcelen</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>ldvybSuH</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>fali</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>2aQwSdeL</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>fernandez carlos</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>dfeW7Mbo</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>gil david</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>rBgx4Uxm</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>n guessan rominigue kouame</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>GI2LU0X1</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>matos jose</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>YBQLPtt5</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>melendo oscar</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>IkbbTlTP</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>mwepu francisco</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>MNbqVtWt</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>pascual jorge</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>MNbqVtWt</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>pascual jorge</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>SMRPNG5i</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>puertas antonio</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>CIeqjmkH</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>alkain xeber</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>CIeqjmkH</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>alkain xeber</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>OpN8BXQ8</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>villa toni</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>6Rvb9XRN</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>madariaga ander</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>6Rvb9XRN</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>madariaga ander</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>r9rn0Wtd</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>merquelanz martin</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>f1i71kYp</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>nolaskoain peru</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>f1i71kYp</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>nolaskoain peru</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>Y7dM1nsL</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>jon bautista orgilles</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr"/>
+      <c r="DK6" t="inlineStr"/>
+      <c r="DL6" t="inlineStr"/>
+      <c r="DM6" t="inlineStr"/>
+      <c r="DN6" t="inlineStr"/>
+      <c r="DO6" t="inlineStr"/>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>2aQwSdeL</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>fernandez carlos</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>2aQwSdeL</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>fernandez carlos</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>4rn7WXta</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>de la rosa jose antonio</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>OGkTSXOg</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>ocampo brian</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>OGkTSXOg</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>ocampo brian</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>xnYg4l8i</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>ramos christopher</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>lAD5z2Ck</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>ontiveros javier</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>lAD5z2Ck</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>ontiveros javier</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>0I0RtqEN</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>alejo ivan</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>rBgx4Uxm</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>n guessan rominigue kouame</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>rBgx4Uxm</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>n guessan rominigue kouame</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>SK8upGdH</t>
+        </is>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>fede</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>YBQLPtt5</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>melendo oscar</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>YBQLPtt5</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>melendo oscar</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
+          <t>YioE1eTi</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>sobrino ruben</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>UkvndELE</t>
+        </is>
+      </c>
+      <c r="EU6" t="inlineStr">
+        <is>
+          <t>arambarri aritz</t>
+        </is>
+      </c>
+      <c r="EV6" t="inlineStr">
+        <is>
+          <t>6HSsexVf</t>
+        </is>
+      </c>
+      <c r="EW6" t="inlineStr">
+        <is>
+          <t>hernandez luis</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t>xCZzd0Tg</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t>jose mari</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>OGkTSXOg</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>ocampo brian</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr">
+        <is>
+          <t>lAD5z2Ck</t>
+        </is>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t>ontiveros javier</t>
+        </is>
+      </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>I5wpPbNu</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
+          <t>arbilla anaitz</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
+          <t>r1yFv4o6</t>
+        </is>
+      </c>
+      <c r="FG6" t="inlineStr">
+        <is>
+          <t>guruzeta jon</t>
+        </is>
+      </c>
+      <c r="FH6" t="inlineStr">
+        <is>
+          <t>tGcb9Pq1</t>
+        </is>
+      </c>
+      <c r="FI6" t="inlineStr">
+        <is>
+          <t>troncho angel</t>
+        </is>
+      </c>
+      <c r="FJ6" t="inlineStr"/>
+      <c r="FK6" t="inlineStr"/>
+      <c r="FL6" t="inlineStr"/>
+      <c r="FM6" t="inlineStr"/>
+      <c r="FN6" t="inlineStr">
+        <is>
+          <t>80VKCLhl</t>
+        </is>
+      </c>
+      <c r="FO6" t="inlineStr">
+        <is>
+          <t>roger</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bsmYdd55</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mg4L621f</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mackay ian</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OE8ypMGf</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mateu marc</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SQi6oCZp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>garcia victor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fRUEYwjU</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>monsalve nacho</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>xlqKh3ws</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>martos ivan</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SMT0xrSn</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>youness</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>WzjfmHbs</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>chapela ivan</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>dQNNg6WM</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>quintana nacho</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>nqRME05G</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ortuno diaz sergio</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SCL2q4g1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>jorquera joel</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Agghrm2F</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>ortuno juanto</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2RWVJ0mS</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>poussin gaetan</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>EctXf3CQ</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>calero ivan</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>ADwlmnw6</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>marmol lluis</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>EmPrz6R5</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>kosa sebastian</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>lAyKpN7f</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>clemente enrique</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>CGbL8vih</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>aketxe ager</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>KQYMzB7t</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>aguado marc</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>4jcnOm31</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>bare keidi</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>6uXqLpX9</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>garcia francho</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Mol2TYUm</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>azon ivan</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>6mb7wPdI</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>bazdar samed</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>6TptgFVm</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>bernal alex</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>S8We5DrO</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>diouri mohamed</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>xMgaLcde</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>fajardo jose</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>fP50jBbo</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>gamez francisco</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>OrrBEaDo</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>geraldes chico</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>zaB6bU4A</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>dominguez alan godoy</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>plLDgpFg</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>grigore ricardo</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0KsY9323</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>martin dani</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>U3NEfc8n</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>montes christian</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>ph2LnYwp</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>ogbuehi sixtus</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>AD0qhhph</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>ropero unai</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>nTh80kX9</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>timor david</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>GjsJwEtR</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>alvarez cristian</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>UuKvqHl9</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>ares djalo malcom adu</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>ULQo1Vhr</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>bermejo sergio</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>YBWGCHeU</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>femenias joan</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>YHD6rlQB</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>jair</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>EPkF4hUA</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>liso adrian</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>lGBLl2mm</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>luna marcos</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>4bjEksiR</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>mari alberto</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>6gQosNq6</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>moya toni</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>A3xabU4T</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>nieto carlos</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>6TptgFVm</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>bernal alex</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>6TptgFVm</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>bernal alex</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>dQNNg6WM</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>quintana nacho</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>OrrBEaDo</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>geraldes chico</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>OrrBEaDo</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>geraldes chico</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>nqRME05G</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>ortuno diaz sergio</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>AD0qhhph</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>ropero unai</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>AD0qhhph</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>ropero unai</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>Agghrm2F</t>
+        </is>
+      </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>ortuno juanto</t>
+        </is>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>S8We5DrO</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>diouri mohamed</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>S8We5DrO</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>diouri mohamed</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>SCL2q4g1</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>jorquera joel</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>ph2LnYwp</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>ogbuehi sixtus</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>ph2LnYwp</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>ogbuehi sixtus</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>xlqKh3ws</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>martos ivan</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>4bjEksiR</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>mari alberto</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>4bjEksiR</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>mari alberto</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>Mol2TYUm</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>azon ivan</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>EPkF4hUA</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>liso adrian</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>EPkF4hUA</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>liso adrian</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>6mb7wPdI</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>bazdar samed</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>lGBLl2mm</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>luna marcos</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>lGBLl2mm</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>luna marcos</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>6uXqLpX9</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>garcia francho</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>ULQo1Vhr</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>bermejo sergio</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>ULQo1Vhr</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>bermejo sergio</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>CGbL8vih</t>
+        </is>
+      </c>
+      <c r="EM7" t="inlineStr">
+        <is>
+          <t>aketxe ager</t>
+        </is>
+      </c>
+      <c r="EN7" t="inlineStr">
+        <is>
+          <t>6gQosNq6</t>
+        </is>
+      </c>
+      <c r="EO7" t="inlineStr">
+        <is>
+          <t>moya toni</t>
+        </is>
+      </c>
+      <c r="EP7" t="inlineStr">
+        <is>
+          <t>6gQosNq6</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t>moya toni</t>
+        </is>
+      </c>
+      <c r="ER7" t="inlineStr">
+        <is>
+          <t>KQYMzB7t</t>
+        </is>
+      </c>
+      <c r="ES7" t="inlineStr">
+        <is>
+          <t>aguado marc</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
+      <c r="EV7" t="inlineStr">
+        <is>
+          <t>xAKBBXpc</t>
+        </is>
+      </c>
+      <c r="EW7" t="inlineStr">
+        <is>
+          <t>soberon mario</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
+        <is>
+          <t>MsLEXo2J</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
+          <t>tasende dani</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
+          <t>rPH2xAjh</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
+          <t>sans pau</t>
+        </is>
+      </c>
+      <c r="FB7" t="inlineStr">
+        <is>
+          <t>2yO22dZF</t>
+        </is>
+      </c>
+      <c r="FC7" t="inlineStr">
+        <is>
+          <t>vital bernardo</t>
+        </is>
+      </c>
+      <c r="FD7" t="inlineStr"/>
+      <c r="FE7" t="inlineStr"/>
+      <c r="FF7" t="inlineStr"/>
+      <c r="FG7" t="inlineStr"/>
+      <c r="FH7" t="inlineStr"/>
+      <c r="FI7" t="inlineStr"/>
+      <c r="FJ7" t="inlineStr"/>
+      <c r="FK7" t="inlineStr"/>
+      <c r="FL7" t="inlineStr"/>
+      <c r="FM7" t="inlineStr"/>
+      <c r="FN7" t="inlineStr"/>
+      <c r="FO7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xSbPbIzg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Moj39S61</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>alejandro gonzalo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>lO6sobTG</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>chirino daijiro</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>rZwPCDVc</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>jimenez alberto</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>fw0yGQLQ</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>willems jetro</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>b13gbSqm</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>calatrava alex</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>WpAyP013</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>villahermosa daniel</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>CUPz0tB5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>van den belt thomas</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Eg6LHAo8</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>suero israel</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>63JPjZot</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>seuntjens mats</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>hdzS6xVf</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>sanchez raul</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>nwdj0Ls1</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>mamah kenneth obinna</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>jezDYWzN</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>marino diego</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>IVs2nF0f</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>sanchez ruben</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>YiUPEL9t</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rubio miguel</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>xdh9EmXK</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>miquel ignasi</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>dWVXsr1m</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>williams loic</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>C4WwYAD1</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>jozwiak kamil</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>lSKS5xcF</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>hongla martin</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>lvN1Z92B</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>ruiz sergio</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>WI4CI2SI</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>reinier</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>YiAqdTFb</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>boye lucas</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>AN4BmAif</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>uzuni myrto</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>WKrXys11</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>albert jose</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>joO0HA3L</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>aurelio douglas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>fmjvOOXT</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>flakus bosilj david</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>URckqU07</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>calavera josep</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>KQL5Shet</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>cipenga brian</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>MXMTbTjl</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>de miguel jesus</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>Oz4LFsdm</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>gil oscar</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>dbLe6eik</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>duenas sergio</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>voyxM5cO</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>ruiz salva</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>fDbFeqY3</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>schwake brian</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>23VZWq4k</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>suner pere marco</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>hIm8dpPN</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>vertrouwd jozhua</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>AsdIWlXn</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>balde siren</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>0EXj8XA8</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>brau miguel</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>WEjccUQr</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>corbeanu theodor</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>zy4xa73j</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>lama manu</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>E3BsytEA</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>martinez marc</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>UPLFNnyN</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>saenz ezquerra pablo</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>bygZPyD7</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>sanchez ricard</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>E77oeEa6</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>trigueros manuel</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>Qq6pTCV6</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>tsitaishvili giorgi</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>QZtXmJ94</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>villar gonzalo</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>joO0HA3L</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>aurelio douglas</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>joO0HA3L</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>aurelio douglas</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>WpAyP013</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>villahermosa daniel</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>voyxM5cO</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>ruiz salva</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>voyxM5cO</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>ruiz salva</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>63JPjZot</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>seuntjens mats</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>MXMTbTjl</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>de miguel jesus</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>MXMTbTjl</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>de miguel jesus</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>nwdj0Ls1</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>mamah kenneth obinna</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>fmjvOOXT</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>flakus bosilj david</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>fmjvOOXT</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>flakus bosilj david</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>fw0yGQLQ</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t>willems jetro</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>URckqU07</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>calavera josep</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>URckqU07</t>
+        </is>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>calavera josep</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>Eg6LHAo8</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>suero israel</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>0EXj8XA8</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>brau miguel</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>0EXj8XA8</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>brau miguel</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>dWVXsr1m</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>williams loic</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>Qq6pTCV6</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>tsitaishvili giorgi</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>Qq6pTCV6</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>tsitaishvili giorgi</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>C4WwYAD1</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>jozwiak kamil</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>UPLFNnyN</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>saenz ezquerra pablo</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>UPLFNnyN</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>saenz ezquerra pablo</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>WI4CI2SI</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>reinier</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>bygZPyD7</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>sanchez ricard</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>bygZPyD7</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>sanchez ricard</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t>IVs2nF0f</t>
+        </is>
+      </c>
+      <c r="EM8" t="inlineStr">
+        <is>
+          <t>sanchez ruben</t>
+        </is>
+      </c>
+      <c r="EN8" t="inlineStr">
+        <is>
+          <t>YTgDvwwU</t>
+        </is>
+      </c>
+      <c r="EO8" t="inlineStr">
+        <is>
+          <t>weissman shon</t>
+        </is>
+      </c>
+      <c r="EP8" t="inlineStr">
+        <is>
+          <t>YTgDvwwU</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t>weissman shon</t>
+        </is>
+      </c>
+      <c r="ER8" t="inlineStr">
+        <is>
+          <t>YiAqdTFb</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>boye lucas</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>6VNfXK68</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t>lottin albert</t>
+        </is>
+      </c>
+      <c r="EV8" t="inlineStr">
+        <is>
+          <t>n5JmutJP</t>
+        </is>
+      </c>
+      <c r="EW8" t="inlineStr">
+        <is>
+          <t>neva carlos</t>
+        </is>
+      </c>
+      <c r="EX8" t="inlineStr"/>
+      <c r="EY8" t="inlineStr"/>
+      <c r="EZ8" t="inlineStr">
+        <is>
+          <t>YTgDvwwU</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
+          <t>weissman shon</t>
+        </is>
+      </c>
+      <c r="FB8" t="inlineStr">
+        <is>
+          <t>jPxdddKn</t>
+        </is>
+      </c>
+      <c r="FC8" t="inlineStr">
+        <is>
+          <t>zidane luca</t>
+        </is>
+      </c>
+      <c r="FD8" t="inlineStr"/>
+      <c r="FE8" t="inlineStr"/>
+      <c r="FF8" t="inlineStr"/>
+      <c r="FG8" t="inlineStr"/>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+      <c r="FL8" t="inlineStr"/>
+      <c r="FM8" t="inlineStr"/>
+      <c r="FN8" t="inlineStr"/>
+      <c r="FO8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QFRek53d</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lA1Qa7LH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>escandell aaron</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>QwD9sQn9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lemos alvaro</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>bD41lxAF</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>costas david</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>fgJYtAmE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>calvo dani</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>69aNbb67</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>alhassane rahim</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>zq5tx9ZS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>colombatto santiago</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>rVt0F12N</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>cazorla santi</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>QZ5Y2SPf</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>chaira ilyas</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>fTaJnuP8</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>seoane jaime</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>GODeIoHH</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>hassan haissem</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ljVRztTj</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>alemao</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8Ui4Uj3f</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>fernandez raul</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Iw3Th1z9</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>alonso sosa julio</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>IsnTW9M8</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>gutierrez juan</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>pGFgjhdA</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>postigo sergio</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>O2ZB51wk</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>tomeo pablo</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>n7WLyvsf</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>gonzalez victor parada</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>A16UgbkJ</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>bassinga aboubacar</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>faenCRar</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>gorrotxategi jon</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>dli7hlod</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>homenchenko santiago</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>SSL080TM</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>panichelli joaquin</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>U5V6iENe</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>martin ander</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>Cjw1V4uo</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>ahijado lucas</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>jsRoAy4E</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>suarez cardero alejandro</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>CMhGvpU0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>del moral alberto</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>O608W9Wj</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>mascarenhas francisco</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>l88RYMiD</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>moyano francisco</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>UwTPIAGm</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>narvaez miguel</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>GxH7SxPr</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>paraschiv daniel george</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>vg9tJMbL</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>sibo kwasi</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>f3yV6bvH</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>vazquez jaime</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>QV5a8bMc</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>dadie alberto</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>I71fjzT2</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>eguiluz unai</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>E1UCv80p</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>urko iruretagoiena</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>d4Ngmj4o</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>lachuer mathis</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>v5HKEYQm</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>lopez luis</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>rFSzAZrl</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>reina alberto</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>rBfMulYr</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>rincon lumbreras hugo</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>WGvUbvMF</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>casals</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>QkiaT3F6</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>tachi</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>f3yV6bvH</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>vazquez jaime</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>f3yV6bvH</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>vazquez jaime</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>bD41lxAF</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>costas david</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>l88RYMiD</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>moyano francisco</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>l88RYMiD</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>moyano francisco</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>QZ5Y2SPf</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>chaira ilyas</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>CMhGvpU0</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>del moral alberto</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>CMhGvpU0</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>del moral alberto</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>fTaJnuP8</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>seoane jaime</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>GxH7SxPr</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>paraschiv daniel george</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>GxH7SxPr</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>paraschiv daniel george</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>ljVRztTj</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>alemao</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>jsRoAy4E</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>suarez cardero alejandro</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>jsRoAy4E</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>suarez cardero alejandro</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>rVt0F12N</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>cazorla santi</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>I71fjzT2</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>eguiluz unai</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>I71fjzT2</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>eguiluz unai</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>pGFgjhdA</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>postigo sergio</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>WGvUbvMF</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>casals</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>WGvUbvMF</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>casals</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>A16UgbkJ</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>bassinga aboubacar</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>rBfMulYr</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>rincon lumbreras hugo</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>rBfMulYr</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>rincon lumbreras hugo</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>n7WLyvsf</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>gonzalez victor parada</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>d4Ngmj4o</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>lachuer mathis</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>d4Ngmj4o</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>lachuer mathis</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>faenCRar</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>gorrotxategi jon</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
+          <t>E1UCv80p</t>
+        </is>
+      </c>
+      <c r="EO9" t="inlineStr">
+        <is>
+          <t>urko iruretagoiena</t>
+        </is>
+      </c>
+      <c r="EP9" t="inlineStr">
+        <is>
+          <t>E1UCv80p</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t>urko iruretagoiena</t>
+        </is>
+      </c>
+      <c r="ER9" t="inlineStr">
+        <is>
+          <t>SSL080TM</t>
+        </is>
+      </c>
+      <c r="ES9" t="inlineStr">
+        <is>
+          <t>panichelli joaquin</t>
+        </is>
+      </c>
+      <c r="ET9" t="inlineStr">
+        <is>
+          <t>CxnAZJbo</t>
+        </is>
+      </c>
+      <c r="EU9" t="inlineStr">
+        <is>
+          <t>luengo oier</t>
+        </is>
+      </c>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
+      <c r="EX9" t="inlineStr"/>
+      <c r="EY9" t="inlineStr"/>
+      <c r="EZ9" t="inlineStr"/>
+      <c r="FA9" t="inlineStr"/>
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>fBb6eDAH</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
+          <t>pomares carlos</t>
+        </is>
+      </c>
+      <c r="FF9" t="inlineStr"/>
+      <c r="FG9" t="inlineStr"/>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="inlineStr"/>
+      <c r="FN9" t="inlineStr"/>
+      <c r="FO9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
